--- a/app/templates/informes/Informes agregado/GE_GRUESO/1-INF.-N-000-26-AG28-G.E.GRUESO-ASTM-C127-25-V04.xlsx
+++ b/app/templates/informes/Informes agregado/GE_GRUESO/1-INF.-N-000-26-AG28-G.E.GRUESO-ASTM-C127-25-V04.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="6" rupBuild="24332"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="6" rupBuild="27928"/>
   <workbookPr codeName="ThisWorkbook"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="G:\Mi unidad\3.0 Formatos e informes\2026\1.0 Informe de ensayo\1.2 Informe agregados\INFORME ACREDITADO-E ISO\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Lenovo\Documents\crmnew\api-geofal-crm\app\templates\informes\Informes agregado\GE_GRUESO\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{859EFE8D-BF39-4910-9BD7-BAD9FBFEED7D}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{623D70CC-5D18-425B-A8DD-92E3A6D37543}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" tabRatio="723" activeTab="2" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" tabRatio="723" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="FORMATO PEG" sheetId="97" r:id="rId1"/>
@@ -3533,6 +3533,254 @@
     <xf numFmtId="0" fontId="7" fillId="0" borderId="10" xfId="6" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="8" xfId="6" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+      <protection hidden="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="2" xfId="6" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+      <protection hidden="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="9" xfId="6" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+      <protection hidden="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="0" borderId="11" xfId="6" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="center" vertical="center"/>
+      <protection hidden="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="0" borderId="12" xfId="6" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="center" vertical="center"/>
+      <protection hidden="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="0" borderId="10" xfId="6" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="center" vertical="center"/>
+      <protection hidden="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="0" borderId="11" xfId="6" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+      <protection hidden="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="0" borderId="12" xfId="6" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+      <protection hidden="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="0" borderId="10" xfId="6" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+      <protection hidden="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="6" borderId="0" xfId="2" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="6" borderId="11" xfId="2" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="6" borderId="10" xfId="2" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="6" borderId="12" xfId="2" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="4" xfId="6" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+      <protection hidden="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="3" xfId="6" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+      <protection hidden="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="5" xfId="6" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+      <protection hidden="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="0" borderId="1" xfId="6" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+      <protection hidden="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="13" fillId="6" borderId="0" xfId="6" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="180" fontId="13" fillId="0" borderId="0" xfId="6" applyNumberFormat="1" applyFont="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="center" vertical="center"/>
+      <protection hidden="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="41" fillId="0" borderId="11" xfId="6" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="41" fillId="0" borderId="10" xfId="6" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="42" fillId="0" borderId="1" xfId="6" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="0" borderId="11" xfId="6" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment vertical="center"/>
+      <protection hidden="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="0" borderId="12" xfId="6" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment vertical="center"/>
+      <protection hidden="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="0" borderId="10" xfId="6" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment vertical="center"/>
+      <protection hidden="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="11" xfId="6" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="left" vertical="center"/>
+      <protection hidden="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="10" xfId="6" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="left" vertical="center"/>
+      <protection hidden="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="2" borderId="11" xfId="6" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+      <protection hidden="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="2" borderId="12" xfId="6" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+      <protection hidden="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="2" borderId="10" xfId="6" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+      <protection hidden="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="0" borderId="11" xfId="6" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="center" vertical="center"/>
+      <protection hidden="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="0" borderId="10" xfId="6" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="center" vertical="center"/>
+      <protection hidden="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="28" fillId="0" borderId="1" xfId="2" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="0" borderId="1" xfId="3" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="2" borderId="4" xfId="6" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+      <protection hidden="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="2" borderId="3" xfId="6" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+      <protection hidden="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="2" borderId="5" xfId="6" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+      <protection hidden="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="2" borderId="8" xfId="6" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+      <protection hidden="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="2" borderId="2" xfId="6" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+      <protection hidden="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="2" borderId="9" xfId="6" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+      <protection hidden="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="0" borderId="4" xfId="6" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="center" vertical="center"/>
+      <protection hidden="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="0" borderId="5" xfId="6" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="center" vertical="center"/>
+      <protection hidden="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="0" borderId="8" xfId="6" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="center" vertical="center"/>
+      <protection hidden="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="0" borderId="9" xfId="6" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="center" vertical="center"/>
+      <protection hidden="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="44" fillId="0" borderId="11" xfId="6" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="center" vertical="center"/>
+      <protection hidden="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="44" fillId="0" borderId="10" xfId="6" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="center" vertical="center"/>
+      <protection hidden="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="0" borderId="11" xfId="6" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+      <protection hidden="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="0" borderId="12" xfId="6" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+      <protection hidden="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="0" borderId="10" xfId="6" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+      <protection hidden="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="0" xfId="6" applyFont="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="left" vertical="center" wrapText="1" indent="1"/>
+      <protection hidden="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="1" xfId="6" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="center" vertical="center"/>
+      <protection hidden="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="14" fillId="0" borderId="11" xfId="6" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="14" fillId="0" borderId="12" xfId="6" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="14" fillId="0" borderId="10" xfId="6" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="14" fillId="0" borderId="1" xfId="6" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="0" borderId="11" xfId="2" quotePrefix="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="0" borderId="12" xfId="2" quotePrefix="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="0" borderId="10" xfId="2" quotePrefix="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="0" borderId="1" xfId="6" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="left" vertical="center"/>
+      <protection hidden="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="1" xfId="3" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="0" borderId="1" xfId="3" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="0" borderId="1" xfId="6" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="0" borderId="1" xfId="6" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="center" vertical="center"/>
+      <protection hidden="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="0" borderId="11" xfId="3" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="0" borderId="12" xfId="3" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="0" borderId="10" xfId="3" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="0" borderId="12" xfId="6" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="center" vertical="center"/>
+      <protection hidden="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="0" borderId="0" xfId="7" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
     <xf numFmtId="0" fontId="14" fillId="0" borderId="0" xfId="6" applyFont="1" applyAlignment="1" applyProtection="1">
       <alignment horizontal="center" vertical="center"/>
       <protection hidden="1"/>
@@ -3554,254 +3802,6 @@
     <xf numFmtId="0" fontId="28" fillId="0" borderId="0" xfId="2" applyFont="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="9" fillId="0" borderId="0" xfId="7" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="0" borderId="1" xfId="3" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="9" fillId="0" borderId="1" xfId="3" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="9" fillId="0" borderId="1" xfId="6" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="11" fillId="0" borderId="1" xfId="6" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="center" vertical="center"/>
-      <protection hidden="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="9" fillId="0" borderId="1" xfId="6" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="left" vertical="center"/>
-      <protection hidden="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="9" fillId="0" borderId="11" xfId="3" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="9" fillId="0" borderId="12" xfId="3" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="9" fillId="0" borderId="10" xfId="3" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="11" fillId="0" borderId="11" xfId="6" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="center" vertical="center"/>
-      <protection hidden="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="11" fillId="0" borderId="12" xfId="6" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="center" vertical="center"/>
-      <protection hidden="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="11" fillId="0" borderId="10" xfId="6" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="center" vertical="center"/>
-      <protection hidden="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="14" fillId="0" borderId="11" xfId="6" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="14" fillId="0" borderId="12" xfId="6" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="14" fillId="0" borderId="10" xfId="6" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="14" fillId="0" borderId="1" xfId="6" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="9" fillId="0" borderId="11" xfId="6" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-      <protection hidden="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="9" fillId="0" borderId="12" xfId="6" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-      <protection hidden="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="9" fillId="0" borderId="10" xfId="6" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-      <protection hidden="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="0" borderId="0" xfId="6" applyFont="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="left" vertical="center" wrapText="1" indent="1"/>
-      <protection hidden="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="1" xfId="6" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="center" vertical="center"/>
-      <protection hidden="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="9" fillId="0" borderId="11" xfId="2" quotePrefix="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="9" fillId="0" borderId="12" xfId="2" quotePrefix="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="9" fillId="0" borderId="10" xfId="2" quotePrefix="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="9" fillId="0" borderId="11" xfId="6" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment vertical="center"/>
-      <protection hidden="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="9" fillId="0" borderId="12" xfId="6" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment vertical="center"/>
-      <protection hidden="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="9" fillId="0" borderId="10" xfId="6" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment vertical="center"/>
-      <protection hidden="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="0" borderId="11" xfId="6" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="left" vertical="center"/>
-      <protection hidden="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="0" borderId="10" xfId="6" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="left" vertical="center"/>
-      <protection hidden="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="9" fillId="2" borderId="11" xfId="6" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-      <protection hidden="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="9" fillId="2" borderId="12" xfId="6" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-      <protection hidden="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="9" fillId="2" borderId="10" xfId="6" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-      <protection hidden="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="28" fillId="0" borderId="1" xfId="2" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="9" fillId="0" borderId="1" xfId="3" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="9" fillId="2" borderId="4" xfId="6" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-      <protection hidden="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="9" fillId="2" borderId="3" xfId="6" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-      <protection hidden="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="9" fillId="2" borderId="5" xfId="6" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-      <protection hidden="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="9" fillId="2" borderId="8" xfId="6" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-      <protection hidden="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="9" fillId="2" borderId="2" xfId="6" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-      <protection hidden="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="9" fillId="2" borderId="9" xfId="6" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-      <protection hidden="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="11" fillId="0" borderId="4" xfId="6" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="center" vertical="center"/>
-      <protection hidden="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="11" fillId="0" borderId="5" xfId="6" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="center" vertical="center"/>
-      <protection hidden="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="11" fillId="0" borderId="8" xfId="6" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="center" vertical="center"/>
-      <protection hidden="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="11" fillId="0" borderId="9" xfId="6" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="center" vertical="center"/>
-      <protection hidden="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="44" fillId="0" borderId="11" xfId="6" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="center" vertical="center"/>
-      <protection hidden="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="44" fillId="0" borderId="10" xfId="6" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="center" vertical="center"/>
-      <protection hidden="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="13" fillId="6" borderId="0" xfId="6" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="180" fontId="13" fillId="0" borderId="0" xfId="6" applyNumberFormat="1" applyFont="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="center" vertical="center"/>
-      <protection hidden="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="41" fillId="0" borderId="11" xfId="6" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="41" fillId="0" borderId="10" xfId="6" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="42" fillId="0" borderId="1" xfId="6" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="10" fillId="6" borderId="0" xfId="2" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="8" xfId="6" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-      <protection hidden="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="2" xfId="6" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-      <protection hidden="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="9" xfId="6" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-      <protection hidden="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="12" fillId="0" borderId="11" xfId="6" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="center" vertical="center"/>
-      <protection hidden="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="12" fillId="0" borderId="12" xfId="6" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="center" vertical="center"/>
-      <protection hidden="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="12" fillId="0" borderId="10" xfId="6" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="center" vertical="center"/>
-      <protection hidden="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="10" fillId="0" borderId="11" xfId="6" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-      <protection hidden="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="10" fillId="0" borderId="12" xfId="6" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-      <protection hidden="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="10" fillId="0" borderId="10" xfId="6" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-      <protection hidden="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="10" fillId="6" borderId="11" xfId="2" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="10" fillId="6" borderId="10" xfId="2" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="10" fillId="6" borderId="12" xfId="2" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="4" xfId="6" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-      <protection hidden="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="3" xfId="6" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-      <protection hidden="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="5" xfId="6" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-      <protection hidden="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="10" fillId="0" borderId="1" xfId="6" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-      <protection hidden="1"/>
-    </xf>
     <xf numFmtId="0" fontId="9" fillId="0" borderId="0" xfId="4" quotePrefix="1" applyFont="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
@@ -3847,53 +3847,6 @@
     </xf>
     <xf numFmtId="0" fontId="9" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="14" fillId="0" borderId="4" xfId="3" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="14" fillId="0" borderId="3" xfId="3" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="14" fillId="0" borderId="5" xfId="3" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="1" fontId="9" fillId="0" borderId="12" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="center" vertical="center"/>
-      <protection locked="0"/>
-    </xf>
-    <xf numFmtId="1" fontId="9" fillId="0" borderId="10" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="center" vertical="center"/>
-      <protection locked="0"/>
-    </xf>
-    <xf numFmtId="3" fontId="33" fillId="4" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="175" fontId="9" fillId="2" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="center" vertical="center"/>
-      <protection locked="0"/>
-    </xf>
-    <xf numFmtId="0" fontId="9" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="center" vertical="center"/>
-      <protection locked="0"/>
-    </xf>
-    <xf numFmtId="0" fontId="33" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="center" vertical="center"/>
-      <protection locked="0"/>
-    </xf>
-    <xf numFmtId="0" fontId="14" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="center" vertical="center"/>
-      <protection locked="0"/>
-    </xf>
-    <xf numFmtId="0" fontId="14" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="14" fontId="33" fillId="4" borderId="11" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="center" vertical="center"/>
-      <protection locked="0"/>
-    </xf>
-    <xf numFmtId="14" fontId="33" fillId="4" borderId="10" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="center" vertical="center"/>
-      <protection locked="0"/>
     </xf>
     <xf numFmtId="0" fontId="9" fillId="2" borderId="11" xfId="3" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
@@ -3934,29 +3887,52 @@
     <xf numFmtId="165" fontId="9" fillId="0" borderId="10" xfId="3" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="20" fillId="0" borderId="11" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="20" fillId="0" borderId="10" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="51" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="176" fontId="20" fillId="0" borderId="11" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="176" fontId="20" fillId="0" borderId="10" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="176" fontId="3" fillId="2" borderId="11" xfId="3" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="176" fontId="3" fillId="2" borderId="10" xfId="3" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="2" borderId="0" xfId="3" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
+    <xf numFmtId="0" fontId="14" fillId="0" borderId="4" xfId="3" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="14" fillId="0" borderId="3" xfId="3" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="14" fillId="0" borderId="5" xfId="3" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="1" fontId="9" fillId="0" borderId="12" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="center" vertical="center"/>
+      <protection locked="0"/>
+    </xf>
+    <xf numFmtId="1" fontId="9" fillId="0" borderId="10" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="center" vertical="center"/>
+      <protection locked="0"/>
+    </xf>
+    <xf numFmtId="3" fontId="33" fillId="4" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="175" fontId="9" fillId="2" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="center" vertical="center"/>
+      <protection locked="0"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="center" vertical="center"/>
+      <protection locked="0"/>
+    </xf>
+    <xf numFmtId="0" fontId="33" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="center" vertical="center"/>
+      <protection locked="0"/>
+    </xf>
+    <xf numFmtId="0" fontId="14" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="center" vertical="center"/>
+      <protection locked="0"/>
+    </xf>
+    <xf numFmtId="0" fontId="14" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="14" fontId="33" fillId="4" borderId="11" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="center" vertical="center"/>
+      <protection locked="0"/>
+    </xf>
+    <xf numFmtId="14" fontId="33" fillId="4" borderId="10" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="center" vertical="center"/>
+      <protection locked="0"/>
     </xf>
     <xf numFmtId="0" fontId="4" fillId="2" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
@@ -4007,6 +3983,30 @@
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="3" fillId="2" borderId="16" xfId="3" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="0" borderId="11" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="0" borderId="10" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="51" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="176" fontId="20" fillId="0" borderId="11" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="176" fontId="20" fillId="0" borderId="10" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="176" fontId="3" fillId="2" borderId="11" xfId="3" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="176" fontId="3" fillId="2" borderId="10" xfId="3" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="2" borderId="0" xfId="3" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="3" fillId="2" borderId="1" xfId="3" applyFill="1" applyBorder="1" applyAlignment="1">
@@ -6193,8 +6193,8 @@
       </xdr:nvGrpSpPr>
       <xdr:grpSpPr>
         <a:xfrm>
-          <a:off x="523875" y="3228975"/>
-          <a:ext cx="3629349" cy="1445939"/>
+          <a:off x="523875" y="3232785"/>
+          <a:ext cx="3739839" cy="1445939"/>
           <a:chOff x="5010150" y="3781425"/>
           <a:chExt cx="3734124" cy="1445939"/>
         </a:xfrm>
@@ -6415,7 +6415,7 @@
 </file>
 
 <file path=xl/externalLinks/externalLink1.xml><?xml version="1.0" encoding="utf-8"?>
-<externalLink xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" mc:Ignorable="x14">
+<externalLink xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:xxl21="http://schemas.microsoft.com/office/spreadsheetml/2021/extlinks2021" mc:Ignorable="x14 xxl21">
   <externalBook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId1">
     <sheetNames>
       <sheetName val="-------"/>
@@ -6474,7 +6474,7 @@
 </file>
 
 <file path=xl/externalLinks/externalLink2.xml><?xml version="1.0" encoding="utf-8"?>
-<externalLink xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" mc:Ignorable="x14">
+<externalLink xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:xxl21="http://schemas.microsoft.com/office/spreadsheetml/2021/extlinks2021" mc:Ignorable="x14 xxl21">
   <externalBook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId1">
     <sheetNames>
       <sheetName val="datos de ecuacion del anillo"/>
@@ -6593,7 +6593,7 @@
 </file>
 
 <file path=xl/externalLinks/externalLink3.xml><?xml version="1.0" encoding="utf-8"?>
-<externalLink xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" mc:Ignorable="x14">
+<externalLink xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:xxl21="http://schemas.microsoft.com/office/spreadsheetml/2021/extlinks2021" mc:Ignorable="x14 xxl21">
   <externalBook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId1">
     <sheetNames>
       <sheetName val="-------"/>
@@ -6644,7 +6644,7 @@
 </file>
 
 <file path=xl/externalLinks/externalLink4.xml><?xml version="1.0" encoding="utf-8"?>
-<externalLink xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" mc:Ignorable="x14">
+<externalLink xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:xxl21="http://schemas.microsoft.com/office/spreadsheetml/2021/extlinks2021" mc:Ignorable="x14 xxl21">
   <externalBook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId1">
     <sheetNames>
       <sheetName val="-------"/>
@@ -6696,7 +6696,7 @@
 </file>
 
 <file path=xl/externalLinks/externalLink5.xml><?xml version="1.0" encoding="utf-8"?>
-<externalLink xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" mc:Ignorable="x14">
+<externalLink xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:xxl21="http://schemas.microsoft.com/office/spreadsheetml/2021/extlinks2021" mc:Ignorable="x14 xxl21">
   <externalBook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId1">
     <sheetNames>
       <sheetName val="BGA"/>
@@ -6728,7 +6728,7 @@
 </file>
 
 <file path=xl/externalLinks/externalLink6.xml><?xml version="1.0" encoding="utf-8"?>
-<externalLink xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" mc:Ignorable="x14">
+<externalLink xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:xxl21="http://schemas.microsoft.com/office/spreadsheetml/2021/extlinks2021" mc:Ignorable="x14 xxl21">
   <externalBook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId1">
     <sheetNames>
       <sheetName val="-------"/>
@@ -8382,32 +8382,32 @@
     <pageSetUpPr fitToPage="1"/>
   </sheetPr>
   <dimension ref="A1:AB55"/>
-  <sheetFormatPr baseColWidth="10" defaultColWidth="8.85546875" defaultRowHeight="15" x14ac:dyDescent="0.2"/>
+  <sheetFormatPr baseColWidth="10" defaultColWidth="8.88671875" defaultRowHeight="14.4" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="1" style="387" customWidth="1"/>
-    <col min="2" max="2" width="6.28515625" style="387" customWidth="1"/>
-    <col min="3" max="3" width="9.42578125" style="387" customWidth="1"/>
-    <col min="4" max="4" width="12.85546875" style="387" customWidth="1"/>
-    <col min="5" max="5" width="10.28515625" style="387" customWidth="1"/>
-    <col min="6" max="6" width="10.7109375" style="387" customWidth="1"/>
-    <col min="7" max="7" width="0.7109375" style="387" customWidth="1"/>
+    <col min="2" max="2" width="6.33203125" style="387" customWidth="1"/>
+    <col min="3" max="3" width="9.44140625" style="387" customWidth="1"/>
+    <col min="4" max="4" width="12.88671875" style="387" customWidth="1"/>
+    <col min="5" max="5" width="10.33203125" style="387" customWidth="1"/>
+    <col min="6" max="6" width="10.6640625" style="387" customWidth="1"/>
+    <col min="7" max="7" width="0.6640625" style="387" customWidth="1"/>
     <col min="8" max="8" width="10" style="387" customWidth="1"/>
-    <col min="9" max="9" width="4.140625" style="387" customWidth="1"/>
-    <col min="10" max="10" width="0.85546875" style="387" customWidth="1"/>
+    <col min="9" max="9" width="4.109375" style="387" customWidth="1"/>
+    <col min="10" max="10" width="0.88671875" style="387" customWidth="1"/>
     <col min="11" max="11" width="7" style="387" customWidth="1"/>
-    <col min="12" max="12" width="7.140625" style="387" customWidth="1"/>
-    <col min="13" max="13" width="0.7109375" style="387" customWidth="1"/>
-    <col min="14" max="14" width="13.42578125" style="387" customWidth="1"/>
-    <col min="15" max="15" width="15.5703125" style="387" customWidth="1"/>
-    <col min="16" max="16" width="8.85546875" style="387"/>
-    <col min="17" max="17" width="9.7109375" style="387" customWidth="1"/>
-    <col min="18" max="18" width="11.7109375" style="387" customWidth="1"/>
-    <col min="19" max="20" width="8.85546875" style="387"/>
-    <col min="21" max="21" width="10.5703125" style="387" customWidth="1"/>
-    <col min="22" max="16384" width="8.85546875" style="387"/>
+    <col min="12" max="12" width="7.109375" style="387" customWidth="1"/>
+    <col min="13" max="13" width="0.6640625" style="387" customWidth="1"/>
+    <col min="14" max="14" width="13.44140625" style="387" customWidth="1"/>
+    <col min="15" max="15" width="15.5546875" style="387" customWidth="1"/>
+    <col min="16" max="16" width="8.88671875" style="387"/>
+    <col min="17" max="17" width="9.6640625" style="387" customWidth="1"/>
+    <col min="18" max="18" width="11.6640625" style="387" customWidth="1"/>
+    <col min="19" max="20" width="8.88671875" style="387"/>
+    <col min="21" max="21" width="10.5546875" style="387" customWidth="1"/>
+    <col min="22" max="16384" width="8.88671875" style="387"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:21" s="324" customFormat="1" ht="15" customHeight="1" thickTop="1" x14ac:dyDescent="0.2">
+    <row r="1" spans="1:21" s="324" customFormat="1" ht="15" customHeight="1" thickTop="1" x14ac:dyDescent="0.25">
       <c r="A1" s="320"/>
       <c r="B1" s="321"/>
       <c r="C1" s="321"/>
@@ -8424,7 +8424,7 @@
       <c r="N1" s="322"/>
       <c r="O1" s="323"/>
     </row>
-    <row r="2" spans="1:21" s="324" customFormat="1" ht="15" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="2" spans="1:21" s="324" customFormat="1" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A2" s="325"/>
       <c r="B2" s="326"/>
       <c r="C2" s="326"/>
@@ -8445,7 +8445,7 @@
       </c>
       <c r="U2" s="400"/>
     </row>
-    <row r="3" spans="1:21" s="324" customFormat="1" ht="15" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="3" spans="1:21" s="324" customFormat="1" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A3" s="325"/>
       <c r="B3" s="326"/>
       <c r="C3" s="326"/>
@@ -8466,7 +8466,7 @@
       </c>
       <c r="U3" s="401"/>
     </row>
-    <row r="4" spans="1:21" s="324" customFormat="1" ht="15" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="4" spans="1:21" s="324" customFormat="1" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A4" s="325"/>
       <c r="B4" s="326"/>
       <c r="C4" s="326"/>
@@ -8493,7 +8493,7 @@
       </c>
       <c r="U4" s="401"/>
     </row>
-    <row r="5" spans="1:21" s="324" customFormat="1" ht="15" customHeight="1" thickBot="1" x14ac:dyDescent="0.25">
+    <row r="5" spans="1:21" s="324" customFormat="1" ht="15" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A5" s="330"/>
       <c r="B5" s="331"/>
       <c r="C5" s="331"/>
@@ -8520,7 +8520,7 @@
       </c>
       <c r="U5" s="401"/>
     </row>
-    <row r="6" spans="1:21" s="324" customFormat="1" ht="12" customHeight="1" thickTop="1" x14ac:dyDescent="0.2">
+    <row r="6" spans="1:21" s="324" customFormat="1" ht="12" customHeight="1" thickTop="1" x14ac:dyDescent="0.25">
       <c r="A6" s="333"/>
       <c r="B6" s="333"/>
       <c r="C6" s="333"/>
@@ -8545,24 +8545,24 @@
       <c r="T6" s="402"/>
       <c r="U6" s="403"/>
     </row>
-    <row r="7" spans="1:21" s="324" customFormat="1" ht="15.95" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A7" s="467" t="s">
+    <row r="7" spans="1:21" s="324" customFormat="1" ht="15.9" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A7" s="432" t="s">
         <v>0</v>
       </c>
-      <c r="B7" s="467"/>
-      <c r="C7" s="467"/>
-      <c r="D7" s="467"/>
-      <c r="E7" s="467"/>
-      <c r="F7" s="467"/>
-      <c r="G7" s="467"/>
-      <c r="H7" s="467"/>
-      <c r="I7" s="467"/>
-      <c r="J7" s="467"/>
-      <c r="K7" s="467"/>
-      <c r="L7" s="467"/>
-      <c r="M7" s="467"/>
-      <c r="N7" s="467"/>
-      <c r="O7" s="467"/>
+      <c r="B7" s="432"/>
+      <c r="C7" s="432"/>
+      <c r="D7" s="432"/>
+      <c r="E7" s="432"/>
+      <c r="F7" s="432"/>
+      <c r="G7" s="432"/>
+      <c r="H7" s="432"/>
+      <c r="I7" s="432"/>
+      <c r="J7" s="432"/>
+      <c r="K7" s="432"/>
+      <c r="L7" s="432"/>
+      <c r="M7" s="432"/>
+      <c r="N7" s="432"/>
+      <c r="O7" s="432"/>
       <c r="Q7" s="334" t="s">
         <v>137</v>
       </c>
@@ -8574,24 +8574,24 @@
       </c>
       <c r="U7" s="403"/>
     </row>
-    <row r="8" spans="1:21" s="324" customFormat="1" ht="15.95" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A8" s="468" t="s">
+    <row r="8" spans="1:21" s="324" customFormat="1" ht="15.9" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A8" s="433" t="s">
         <v>181</v>
       </c>
-      <c r="B8" s="468"/>
-      <c r="C8" s="468"/>
-      <c r="D8" s="468"/>
-      <c r="E8" s="468"/>
-      <c r="F8" s="468"/>
-      <c r="G8" s="468"/>
-      <c r="H8" s="468"/>
-      <c r="I8" s="468"/>
-      <c r="J8" s="468"/>
-      <c r="K8" s="468"/>
-      <c r="L8" s="468"/>
-      <c r="M8" s="468"/>
-      <c r="N8" s="468"/>
-      <c r="O8" s="468"/>
+      <c r="B8" s="433"/>
+      <c r="C8" s="433"/>
+      <c r="D8" s="433"/>
+      <c r="E8" s="433"/>
+      <c r="F8" s="433"/>
+      <c r="G8" s="433"/>
+      <c r="H8" s="433"/>
+      <c r="I8" s="433"/>
+      <c r="J8" s="433"/>
+      <c r="K8" s="433"/>
+      <c r="L8" s="433"/>
+      <c r="M8" s="433"/>
+      <c r="N8" s="433"/>
+      <c r="O8" s="433"/>
       <c r="Q8" s="334" t="s">
         <v>136</v>
       </c>
@@ -8603,7 +8603,7 @@
       </c>
       <c r="U8" s="404"/>
     </row>
-    <row r="9" spans="1:21" s="324" customFormat="1" ht="15.95" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="9" spans="1:21" s="324" customFormat="1" ht="15.9" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A9" s="335"/>
       <c r="B9" s="335"/>
       <c r="C9" s="335"/>
@@ -8629,27 +8629,27 @@
       </c>
       <c r="U9" s="403"/>
     </row>
-    <row r="10" spans="1:21" s="324" customFormat="1" ht="15.95" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="10" spans="1:21" s="324" customFormat="1" ht="15.9" customHeight="1" x14ac:dyDescent="0.25">
       <c r="C10" s="337"/>
       <c r="E10" s="338" t="s">
         <v>182</v>
       </c>
-      <c r="F10" s="469" t="s">
+      <c r="F10" s="434" t="s">
         <v>183</v>
       </c>
-      <c r="G10" s="470"/>
+      <c r="G10" s="435"/>
       <c r="H10" s="338" t="s">
         <v>184</v>
       </c>
-      <c r="I10" s="471" t="s">
+      <c r="I10" s="436" t="s">
         <v>185</v>
       </c>
-      <c r="J10" s="471"/>
-      <c r="K10" s="471"/>
+      <c r="J10" s="436"/>
+      <c r="K10" s="436"/>
       <c r="L10" s="337"/>
-      <c r="M10" s="472"/>
-      <c r="N10" s="472"/>
-      <c r="O10" s="472"/>
+      <c r="M10" s="424"/>
+      <c r="N10" s="424"/>
+      <c r="O10" s="424"/>
       <c r="P10" s="339"/>
       <c r="Q10" s="340" t="s">
         <v>132</v>
@@ -8660,22 +8660,22 @@
       <c r="T10" s="402"/>
       <c r="U10" s="403"/>
     </row>
-    <row r="11" spans="1:21" s="324" customFormat="1" ht="15.95" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="11" spans="1:21" s="324" customFormat="1" ht="15.9" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A11" s="341"/>
-      <c r="B11" s="472"/>
-      <c r="C11" s="472"/>
-      <c r="D11" s="472"/>
+      <c r="B11" s="424"/>
+      <c r="C11" s="424"/>
+      <c r="D11" s="424"/>
       <c r="E11" s="342"/>
-      <c r="F11" s="482"/>
-      <c r="G11" s="483"/>
+      <c r="F11" s="425"/>
+      <c r="G11" s="426"/>
       <c r="H11" s="343"/>
-      <c r="I11" s="482"/>
-      <c r="J11" s="484"/>
-      <c r="K11" s="483"/>
+      <c r="I11" s="425"/>
+      <c r="J11" s="427"/>
+      <c r="K11" s="426"/>
       <c r="L11" s="337"/>
-      <c r="M11" s="472"/>
-      <c r="N11" s="472"/>
-      <c r="O11" s="472"/>
+      <c r="M11" s="424"/>
+      <c r="N11" s="424"/>
+      <c r="O11" s="424"/>
       <c r="P11" s="339"/>
       <c r="Q11" s="340" t="s">
         <v>59</v>
@@ -8688,7 +8688,7 @@
       </c>
       <c r="U11" s="403"/>
     </row>
-    <row r="12" spans="1:21" s="324" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="12" spans="1:21" s="324" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A12" s="341"/>
       <c r="B12" s="337"/>
       <c r="C12" s="344"/>
@@ -8716,24 +8716,24 @@
       </c>
       <c r="U12" s="404"/>
     </row>
-    <row r="13" spans="1:21" s="324" customFormat="1" ht="14.25" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A13" s="485" t="s">
+    <row r="13" spans="1:21" s="324" customFormat="1" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A13" s="428" t="s">
         <v>186</v>
       </c>
-      <c r="B13" s="486"/>
-      <c r="C13" s="486"/>
-      <c r="D13" s="486"/>
-      <c r="E13" s="486"/>
-      <c r="F13" s="486"/>
-      <c r="G13" s="486"/>
-      <c r="H13" s="486"/>
-      <c r="I13" s="486"/>
-      <c r="J13" s="486"/>
-      <c r="K13" s="486"/>
-      <c r="L13" s="486"/>
-      <c r="M13" s="486"/>
-      <c r="N13" s="486"/>
-      <c r="O13" s="487"/>
+      <c r="B13" s="429"/>
+      <c r="C13" s="429"/>
+      <c r="D13" s="429"/>
+      <c r="E13" s="429"/>
+      <c r="F13" s="429"/>
+      <c r="G13" s="429"/>
+      <c r="H13" s="429"/>
+      <c r="I13" s="429"/>
+      <c r="J13" s="429"/>
+      <c r="K13" s="429"/>
+      <c r="L13" s="429"/>
+      <c r="M13" s="429"/>
+      <c r="N13" s="429"/>
+      <c r="O13" s="430"/>
       <c r="P13" s="339"/>
       <c r="Q13" s="340" t="s">
         <v>131</v>
@@ -8746,24 +8746,24 @@
       </c>
       <c r="U13" s="404"/>
     </row>
-    <row r="14" spans="1:21" s="324" customFormat="1" ht="15" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A14" s="473" t="s">
+    <row r="14" spans="1:21" s="324" customFormat="1" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A14" s="415" t="s">
         <v>187</v>
       </c>
-      <c r="B14" s="474"/>
-      <c r="C14" s="474"/>
-      <c r="D14" s="474"/>
-      <c r="E14" s="474"/>
-      <c r="F14" s="474"/>
-      <c r="G14" s="474"/>
-      <c r="H14" s="474"/>
-      <c r="I14" s="474"/>
-      <c r="J14" s="474"/>
-      <c r="K14" s="474"/>
-      <c r="L14" s="474"/>
-      <c r="M14" s="474"/>
-      <c r="N14" s="474"/>
-      <c r="O14" s="475"/>
+      <c r="B14" s="416"/>
+      <c r="C14" s="416"/>
+      <c r="D14" s="416"/>
+      <c r="E14" s="416"/>
+      <c r="F14" s="416"/>
+      <c r="G14" s="416"/>
+      <c r="H14" s="416"/>
+      <c r="I14" s="416"/>
+      <c r="J14" s="416"/>
+      <c r="K14" s="416"/>
+      <c r="L14" s="416"/>
+      <c r="M14" s="416"/>
+      <c r="N14" s="416"/>
+      <c r="O14" s="417"/>
       <c r="P14" s="339"/>
       <c r="Q14" s="340" t="s">
         <v>175</v>
@@ -8774,7 +8774,7 @@
       <c r="T14" s="402"/>
       <c r="U14" s="403"/>
     </row>
-    <row r="15" spans="1:21" s="324" customFormat="1" ht="15" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="15" spans="1:21" s="324" customFormat="1" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A15" s="346"/>
       <c r="B15" s="346"/>
       <c r="C15" s="346"/>
@@ -8802,25 +8802,25 @@
       </c>
       <c r="U15" s="405"/>
     </row>
-    <row r="16" spans="1:21" s="324" customFormat="1" ht="15" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="16" spans="1:21" s="324" customFormat="1" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A16" s="346"/>
-      <c r="B16" s="476" t="s">
+      <c r="B16" s="418" t="s">
         <v>188</v>
       </c>
-      <c r="C16" s="477"/>
-      <c r="D16" s="477"/>
-      <c r="E16" s="477"/>
-      <c r="F16" s="478"/>
+      <c r="C16" s="419"/>
+      <c r="D16" s="419"/>
+      <c r="E16" s="419"/>
+      <c r="F16" s="420"/>
       <c r="G16" s="346"/>
-      <c r="H16" s="479" t="s">
+      <c r="H16" s="421" t="s">
         <v>189</v>
       </c>
-      <c r="I16" s="480"/>
-      <c r="J16" s="481"/>
-      <c r="K16" s="488" t="s">
+      <c r="I16" s="422"/>
+      <c r="J16" s="423"/>
+      <c r="K16" s="431" t="s">
         <v>190</v>
       </c>
-      <c r="L16" s="488"/>
+      <c r="L16" s="431"/>
       <c r="M16" s="346"/>
       <c r="N16" s="346"/>
       <c r="O16" s="346"/>
@@ -8833,23 +8833,23 @@
       </c>
       <c r="U16" s="405"/>
     </row>
-    <row r="17" spans="1:22" s="324" customFormat="1" ht="19.899999999999999" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="17" spans="1:22" s="324" customFormat="1" ht="19.95" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A17" s="346"/>
-      <c r="B17" s="445" t="s">
+      <c r="B17" s="437" t="s">
         <v>192</v>
       </c>
-      <c r="C17" s="446"/>
-      <c r="D17" s="447"/>
+      <c r="C17" s="438"/>
+      <c r="D17" s="439"/>
       <c r="E17" s="392"/>
       <c r="F17" s="393"/>
       <c r="G17" s="346"/>
-      <c r="H17" s="450" t="s">
+      <c r="H17" s="442" t="s">
         <v>193</v>
       </c>
-      <c r="I17" s="451"/>
-      <c r="J17" s="452"/>
-      <c r="K17" s="430"/>
-      <c r="L17" s="432"/>
+      <c r="I17" s="443"/>
+      <c r="J17" s="444"/>
+      <c r="K17" s="445"/>
+      <c r="L17" s="446"/>
       <c r="M17" s="346"/>
       <c r="N17" s="346"/>
       <c r="O17" s="346"/>
@@ -8860,82 +8860,82 @@
       </c>
       <c r="U17" s="406"/>
     </row>
-    <row r="18" spans="1:22" s="324" customFormat="1" ht="19.899999999999999" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="18" spans="1:22" s="324" customFormat="1" ht="19.95" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A18" s="346"/>
-      <c r="B18" s="445" t="s">
+      <c r="B18" s="437" t="s">
         <v>194</v>
       </c>
-      <c r="C18" s="446"/>
-      <c r="D18" s="447"/>
-      <c r="E18" s="448" t="s">
+      <c r="C18" s="438"/>
+      <c r="D18" s="439"/>
+      <c r="E18" s="440" t="s">
         <v>227</v>
       </c>
-      <c r="F18" s="449"/>
+      <c r="F18" s="441"/>
       <c r="G18" s="346"/>
-      <c r="H18" s="450" t="s">
+      <c r="H18" s="442" t="s">
         <v>195</v>
       </c>
-      <c r="I18" s="451"/>
-      <c r="J18" s="452"/>
-      <c r="K18" s="430"/>
-      <c r="L18" s="432"/>
+      <c r="I18" s="443"/>
+      <c r="J18" s="444"/>
+      <c r="K18" s="445"/>
+      <c r="L18" s="446"/>
       <c r="M18" s="346"/>
       <c r="N18" s="346"/>
       <c r="O18" s="346"/>
       <c r="P18" s="339"/>
       <c r="Q18" s="339"/>
     </row>
-    <row r="19" spans="1:22" s="324" customFormat="1" ht="24" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="19" spans="1:22" s="324" customFormat="1" ht="24" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A19" s="346"/>
-      <c r="B19" s="445" t="s">
+      <c r="B19" s="437" t="s">
         <v>196</v>
       </c>
-      <c r="C19" s="446"/>
-      <c r="D19" s="447"/>
-      <c r="E19" s="448" t="s">
+      <c r="C19" s="438"/>
+      <c r="D19" s="439"/>
+      <c r="E19" s="440" t="s">
         <v>227</v>
       </c>
-      <c r="F19" s="449"/>
+      <c r="F19" s="441"/>
       <c r="G19" s="346"/>
-      <c r="H19" s="450" t="s">
+      <c r="H19" s="442" t="s">
         <v>197</v>
       </c>
-      <c r="I19" s="451"/>
-      <c r="J19" s="452"/>
-      <c r="K19" s="430"/>
-      <c r="L19" s="432"/>
+      <c r="I19" s="443"/>
+      <c r="J19" s="444"/>
+      <c r="K19" s="445"/>
+      <c r="L19" s="446"/>
       <c r="M19" s="346"/>
       <c r="N19" s="346"/>
       <c r="O19" s="346"/>
       <c r="P19" s="339"/>
       <c r="Q19" s="339"/>
     </row>
-    <row r="20" spans="1:22" s="324" customFormat="1" ht="18" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="20" spans="1:22" s="324" customFormat="1" ht="18" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A20" s="346"/>
-      <c r="B20" s="445" t="s">
+      <c r="B20" s="437" t="s">
         <v>198</v>
       </c>
-      <c r="C20" s="446"/>
-      <c r="D20" s="447"/>
-      <c r="E20" s="448" t="s">
+      <c r="C20" s="438"/>
+      <c r="D20" s="439"/>
+      <c r="E20" s="440" t="s">
         <v>227</v>
       </c>
-      <c r="F20" s="449"/>
+      <c r="F20" s="441"/>
       <c r="G20" s="346"/>
-      <c r="H20" s="455" t="s">
+      <c r="H20" s="449" t="s">
         <v>199</v>
       </c>
-      <c r="I20" s="456"/>
-      <c r="J20" s="457"/>
-      <c r="K20" s="461"/>
-      <c r="L20" s="462"/>
+      <c r="I20" s="450"/>
+      <c r="J20" s="451"/>
+      <c r="K20" s="455"/>
+      <c r="L20" s="456"/>
       <c r="M20" s="346"/>
       <c r="N20" s="346"/>
       <c r="O20" s="346"/>
       <c r="P20" s="339"/>
       <c r="Q20" s="339"/>
     </row>
-    <row r="21" spans="1:22" s="324" customFormat="1" ht="7.15" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="21" spans="1:22" s="324" customFormat="1" ht="7.2" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A21" s="346"/>
       <c r="B21" s="346"/>
       <c r="C21" s="346"/>
@@ -8943,64 +8943,64 @@
       <c r="E21" s="346"/>
       <c r="F21" s="346"/>
       <c r="G21" s="346"/>
-      <c r="H21" s="458"/>
-      <c r="I21" s="459"/>
-      <c r="J21" s="460"/>
-      <c r="K21" s="463"/>
-      <c r="L21" s="464"/>
+      <c r="H21" s="452"/>
+      <c r="I21" s="453"/>
+      <c r="J21" s="454"/>
+      <c r="K21" s="457"/>
+      <c r="L21" s="458"/>
       <c r="M21" s="346"/>
       <c r="N21" s="346"/>
       <c r="O21" s="346"/>
       <c r="P21" s="339"/>
       <c r="Q21" s="339"/>
     </row>
-    <row r="22" spans="1:22" s="324" customFormat="1" ht="19.899999999999999" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="22" spans="1:22" s="324" customFormat="1" ht="19.95" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A22" s="346"/>
-      <c r="B22" s="445" t="s">
+      <c r="B22" s="437" t="s">
         <v>200</v>
       </c>
-      <c r="C22" s="446"/>
-      <c r="D22" s="447"/>
-      <c r="E22" s="465"/>
-      <c r="F22" s="466"/>
+      <c r="C22" s="438"/>
+      <c r="D22" s="439"/>
+      <c r="E22" s="459"/>
+      <c r="F22" s="460"/>
       <c r="G22" s="346"/>
-      <c r="H22" s="450" t="s">
+      <c r="H22" s="442" t="s">
         <v>201</v>
       </c>
-      <c r="I22" s="451"/>
-      <c r="J22" s="452"/>
-      <c r="K22" s="450"/>
-      <c r="L22" s="452"/>
+      <c r="I22" s="443"/>
+      <c r="J22" s="444"/>
+      <c r="K22" s="442"/>
+      <c r="L22" s="444"/>
       <c r="M22" s="346"/>
       <c r="N22" s="346"/>
       <c r="O22" s="346"/>
       <c r="P22" s="339"/>
       <c r="Q22" s="339"/>
     </row>
-    <row r="23" spans="1:22" s="324" customFormat="1" ht="27.75" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="23" spans="1:22" s="324" customFormat="1" ht="27.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A23" s="346"/>
-      <c r="B23" s="445" t="s">
+      <c r="B23" s="437" t="s">
         <v>202</v>
       </c>
-      <c r="C23" s="446"/>
-      <c r="D23" s="447"/>
-      <c r="E23" s="465"/>
-      <c r="F23" s="466"/>
+      <c r="C23" s="438"/>
+      <c r="D23" s="439"/>
+      <c r="E23" s="459"/>
+      <c r="F23" s="460"/>
       <c r="G23" s="346"/>
-      <c r="H23" s="437" t="s">
+      <c r="H23" s="461" t="s">
         <v>203</v>
       </c>
-      <c r="I23" s="438"/>
-      <c r="J23" s="439"/>
-      <c r="K23" s="437"/>
-      <c r="L23" s="439"/>
+      <c r="I23" s="462"/>
+      <c r="J23" s="463"/>
+      <c r="K23" s="461"/>
+      <c r="L23" s="463"/>
       <c r="M23" s="346"/>
       <c r="N23" s="346"/>
       <c r="O23" s="346"/>
       <c r="P23" s="339"/>
       <c r="Q23" s="339"/>
     </row>
-    <row r="24" spans="1:22" s="324" customFormat="1" ht="15" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="24" spans="1:22" s="324" customFormat="1" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A24" s="346"/>
       <c r="B24" s="349" t="s">
         <v>204</v>
@@ -9016,12 +9016,12 @@
       <c r="K24" s="346"/>
       <c r="L24" s="346"/>
       <c r="M24" s="346"/>
-      <c r="N24" s="440"/>
-      <c r="O24" s="440"/>
+      <c r="N24" s="464"/>
+      <c r="O24" s="464"/>
       <c r="P24" s="339"/>
       <c r="Q24" s="339"/>
     </row>
-    <row r="25" spans="1:22" s="324" customFormat="1" ht="10.5" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="25" spans="1:22" s="324" customFormat="1" ht="10.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A25" s="346"/>
       <c r="B25" s="351"/>
       <c r="C25" s="351"/>
@@ -9040,53 +9040,53 @@
       <c r="P25" s="339"/>
       <c r="Q25" s="339"/>
     </row>
-    <row r="26" spans="1:22" s="324" customFormat="1" ht="23.25" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="26" spans="1:22" s="324" customFormat="1" ht="23.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A26" s="346"/>
-      <c r="B26" s="453" t="s">
+      <c r="B26" s="447" t="s">
         <v>25</v>
       </c>
-      <c r="C26" s="453"/>
-      <c r="D26" s="453"/>
-      <c r="E26" s="453"/>
-      <c r="F26" s="453"/>
-      <c r="G26" s="453"/>
-      <c r="H26" s="453"/>
-      <c r="I26" s="453"/>
+      <c r="C26" s="447"/>
+      <c r="D26" s="447"/>
+      <c r="E26" s="447"/>
+      <c r="F26" s="447"/>
+      <c r="G26" s="447"/>
+      <c r="H26" s="447"/>
+      <c r="I26" s="447"/>
       <c r="J26" s="346"/>
-      <c r="K26" s="454" t="s">
+      <c r="K26" s="448" t="s">
         <v>205</v>
       </c>
-      <c r="L26" s="454"/>
-      <c r="M26" s="454"/>
-      <c r="N26" s="454"/>
+      <c r="L26" s="448"/>
+      <c r="M26" s="448"/>
+      <c r="N26" s="448"/>
       <c r="O26" s="352"/>
       <c r="P26" s="339"/>
       <c r="Q26" s="339"/>
     </row>
-    <row r="27" spans="1:22" s="324" customFormat="1" ht="23.25" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="27" spans="1:22" s="324" customFormat="1" ht="23.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A27" s="346"/>
-      <c r="B27" s="442" t="s">
+      <c r="B27" s="470" t="s">
         <v>206</v>
       </c>
-      <c r="C27" s="443"/>
-      <c r="D27" s="443"/>
-      <c r="E27" s="443"/>
-      <c r="F27" s="443"/>
-      <c r="G27" s="444"/>
+      <c r="C27" s="471"/>
+      <c r="D27" s="471"/>
+      <c r="E27" s="471"/>
+      <c r="F27" s="471"/>
+      <c r="G27" s="472"/>
       <c r="H27" s="413"/>
       <c r="I27" s="414"/>
       <c r="J27" s="346"/>
-      <c r="K27" s="426" t="s">
+      <c r="K27" s="473" t="s">
         <v>207</v>
       </c>
-      <c r="L27" s="426"/>
-      <c r="M27" s="426"/>
-      <c r="N27" s="426"/>
+      <c r="L27" s="473"/>
+      <c r="M27" s="473"/>
+      <c r="N27" s="473"/>
       <c r="O27" s="352"/>
       <c r="P27" s="339"/>
       <c r="Q27" s="339"/>
     </row>
-    <row r="28" spans="1:22" s="324" customFormat="1" ht="23.25" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="28" spans="1:22" s="324" customFormat="1" ht="23.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A28" s="346"/>
       <c r="B28" s="353" t="s">
         <v>208</v>
@@ -9099,17 +9099,17 @@
       <c r="H28" s="392"/>
       <c r="I28" s="393"/>
       <c r="J28" s="346"/>
-      <c r="K28" s="426" t="s">
+      <c r="K28" s="473" t="s">
         <v>209</v>
       </c>
-      <c r="L28" s="426"/>
-      <c r="M28" s="426"/>
-      <c r="N28" s="426"/>
+      <c r="L28" s="473"/>
+      <c r="M28" s="473"/>
+      <c r="N28" s="473"/>
       <c r="O28" s="352"/>
       <c r="P28" s="339"/>
       <c r="Q28" s="339"/>
     </row>
-    <row r="29" spans="1:22" s="324" customFormat="1" ht="23.25" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="29" spans="1:22" s="324" customFormat="1" ht="23.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A29" s="346"/>
       <c r="B29" s="353" t="s">
         <v>210</v>
@@ -9122,17 +9122,17 @@
       <c r="H29" s="392"/>
       <c r="I29" s="393"/>
       <c r="J29" s="346"/>
-      <c r="K29" s="426" t="s">
+      <c r="K29" s="473" t="s">
         <v>211</v>
       </c>
-      <c r="L29" s="426"/>
-      <c r="M29" s="426"/>
-      <c r="N29" s="426"/>
+      <c r="L29" s="473"/>
+      <c r="M29" s="473"/>
+      <c r="N29" s="473"/>
       <c r="O29" s="352"/>
       <c r="P29" s="339"/>
       <c r="Q29" s="339"/>
     </row>
-    <row r="30" spans="1:22" s="324" customFormat="1" ht="8.25" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="30" spans="1:22" s="324" customFormat="1" ht="8.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A30" s="346"/>
       <c r="B30" s="346"/>
       <c r="C30" s="346"/>
@@ -9151,28 +9151,28 @@
       <c r="P30" s="339"/>
       <c r="Q30" s="339"/>
     </row>
-    <row r="31" spans="1:22" s="324" customFormat="1" ht="18" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="31" spans="1:22" s="324" customFormat="1" ht="18" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A31" s="346"/>
-      <c r="B31" s="441" t="s">
+      <c r="B31" s="465" t="s">
         <v>212</v>
       </c>
-      <c r="C31" s="441"/>
-      <c r="D31" s="441"/>
-      <c r="E31" s="441"/>
-      <c r="F31" s="441"/>
-      <c r="G31" s="441"/>
-      <c r="H31" s="441"/>
-      <c r="I31" s="441"/>
-      <c r="J31" s="441"/>
-      <c r="K31" s="441"/>
-      <c r="L31" s="441"/>
-      <c r="M31" s="441"/>
-      <c r="N31" s="441"/>
-      <c r="O31" s="441"/>
+      <c r="C31" s="465"/>
+      <c r="D31" s="465"/>
+      <c r="E31" s="465"/>
+      <c r="F31" s="465"/>
+      <c r="G31" s="465"/>
+      <c r="H31" s="465"/>
+      <c r="I31" s="465"/>
+      <c r="J31" s="465"/>
+      <c r="K31" s="465"/>
+      <c r="L31" s="465"/>
+      <c r="M31" s="465"/>
+      <c r="N31" s="465"/>
+      <c r="O31" s="465"/>
       <c r="P31" s="339"/>
       <c r="Q31" s="339"/>
     </row>
-    <row r="32" spans="1:22" s="324" customFormat="1" ht="8.25" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="32" spans="1:22" s="324" customFormat="1" ht="8.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B32" s="356"/>
       <c r="C32" s="347"/>
       <c r="D32" s="347"/>
@@ -9192,34 +9192,34 @@
       <c r="U32" s="357"/>
       <c r="V32" s="357"/>
     </row>
-    <row r="33" spans="1:28" s="324" customFormat="1" ht="18" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="B33" s="433" t="s">
+    <row r="33" spans="1:28" s="324" customFormat="1" ht="18" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="B33" s="466" t="s">
         <v>38</v>
       </c>
-      <c r="C33" s="434"/>
-      <c r="D33" s="434"/>
-      <c r="E33" s="434"/>
-      <c r="F33" s="434"/>
-      <c r="G33" s="434"/>
-      <c r="H33" s="434"/>
-      <c r="I33" s="434"/>
-      <c r="J33" s="434"/>
-      <c r="K33" s="435"/>
+      <c r="C33" s="467"/>
+      <c r="D33" s="467"/>
+      <c r="E33" s="467"/>
+      <c r="F33" s="467"/>
+      <c r="G33" s="467"/>
+      <c r="H33" s="467"/>
+      <c r="I33" s="467"/>
+      <c r="J33" s="467"/>
+      <c r="K33" s="468"/>
       <c r="L33" s="358" t="s">
         <v>213</v>
       </c>
-      <c r="M33" s="436" t="s">
+      <c r="M33" s="469" t="s">
         <v>18</v>
       </c>
-      <c r="N33" s="436"/>
-      <c r="O33" s="436"/>
+      <c r="N33" s="469"/>
+      <c r="O33" s="469"/>
       <c r="Q33" s="339"/>
       <c r="R33" s="359"/>
       <c r="T33" s="357"/>
       <c r="U33" s="357"/>
       <c r="V33" s="357"/>
     </row>
-    <row r="34" spans="1:28" s="324" customFormat="1" ht="18" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="34" spans="1:28" s="324" customFormat="1" ht="18" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B34" s="360" t="s">
         <v>42</v>
       </c>
@@ -9245,7 +9245,7 @@
       <c r="U34" s="357"/>
       <c r="V34" s="357"/>
     </row>
-    <row r="35" spans="1:28" s="324" customFormat="1" ht="18" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="35" spans="1:28" s="324" customFormat="1" ht="18" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B35" s="360" t="s">
         <v>45</v>
       </c>
@@ -9271,7 +9271,7 @@
       <c r="U35" s="357"/>
       <c r="V35" s="357"/>
     </row>
-    <row r="36" spans="1:28" s="324" customFormat="1" ht="18" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="36" spans="1:28" s="324" customFormat="1" ht="18" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B36" s="360" t="s">
         <v>47</v>
       </c>
@@ -9297,44 +9297,44 @@
       <c r="U36" s="357"/>
       <c r="V36" s="357"/>
     </row>
-    <row r="37" spans="1:28" s="324" customFormat="1" ht="18" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="B37" s="422" t="s">
+    <row r="37" spans="1:28" s="324" customFormat="1" ht="18" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="B37" s="474" t="s">
         <v>49</v>
       </c>
-      <c r="C37" s="423" t="s">
+      <c r="C37" s="475" t="s">
         <v>50</v>
       </c>
-      <c r="D37" s="423"/>
-      <c r="E37" s="423"/>
-      <c r="F37" s="423"/>
-      <c r="G37" s="423"/>
-      <c r="H37" s="423"/>
-      <c r="I37" s="423"/>
-      <c r="J37" s="423"/>
-      <c r="K37" s="423"/>
-      <c r="L37" s="424" t="s">
+      <c r="D37" s="475"/>
+      <c r="E37" s="475"/>
+      <c r="F37" s="475"/>
+      <c r="G37" s="475"/>
+      <c r="H37" s="475"/>
+      <c r="I37" s="475"/>
+      <c r="J37" s="475"/>
+      <c r="K37" s="475"/>
+      <c r="L37" s="476" t="s">
         <v>44</v>
       </c>
-      <c r="M37" s="425"/>
-      <c r="N37" s="425"/>
+      <c r="M37" s="477"/>
+      <c r="N37" s="477"/>
       <c r="O37" s="367"/>
       <c r="R37" s="364"/>
       <c r="T37" s="365"/>
       <c r="U37" s="357"/>
       <c r="V37" s="357"/>
     </row>
-    <row r="38" spans="1:28" s="324" customFormat="1" ht="18" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="B38" s="422"/>
-      <c r="C38" s="423"/>
-      <c r="D38" s="423"/>
-      <c r="E38" s="423"/>
-      <c r="F38" s="423"/>
-      <c r="G38" s="423"/>
-      <c r="H38" s="423"/>
-      <c r="I38" s="423"/>
-      <c r="J38" s="423"/>
-      <c r="K38" s="423"/>
-      <c r="L38" s="424"/>
+    <row r="38" spans="1:28" s="324" customFormat="1" ht="18" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="B38" s="474"/>
+      <c r="C38" s="475"/>
+      <c r="D38" s="475"/>
+      <c r="E38" s="475"/>
+      <c r="F38" s="475"/>
+      <c r="G38" s="475"/>
+      <c r="H38" s="475"/>
+      <c r="I38" s="475"/>
+      <c r="J38" s="475"/>
+      <c r="K38" s="475"/>
+      <c r="L38" s="476"/>
       <c r="M38" s="388" t="s">
         <v>215</v>
       </c>
@@ -9345,7 +9345,7 @@
       <c r="U38" s="357"/>
       <c r="V38" s="357"/>
     </row>
-    <row r="39" spans="1:28" s="324" customFormat="1" ht="18" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="39" spans="1:28" s="324" customFormat="1" ht="18" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B39" s="368" t="s">
         <v>216</v>
       </c>
@@ -9354,27 +9354,27 @@
       <c r="U39" s="357"/>
       <c r="V39" s="357"/>
     </row>
-    <row r="40" spans="1:28" s="324" customFormat="1" ht="18" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="B40" s="433" t="s">
+    <row r="40" spans="1:28" s="324" customFormat="1" ht="18" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="B40" s="466" t="s">
         <v>38</v>
       </c>
-      <c r="C40" s="434"/>
-      <c r="D40" s="434"/>
-      <c r="E40" s="434"/>
-      <c r="F40" s="434"/>
-      <c r="G40" s="434"/>
-      <c r="H40" s="434"/>
-      <c r="I40" s="434"/>
-      <c r="J40" s="434"/>
-      <c r="K40" s="435"/>
+      <c r="C40" s="467"/>
+      <c r="D40" s="467"/>
+      <c r="E40" s="467"/>
+      <c r="F40" s="467"/>
+      <c r="G40" s="467"/>
+      <c r="H40" s="467"/>
+      <c r="I40" s="467"/>
+      <c r="J40" s="467"/>
+      <c r="K40" s="468"/>
       <c r="L40" s="358" t="s">
         <v>213</v>
       </c>
-      <c r="M40" s="436" t="s">
+      <c r="M40" s="469" t="s">
         <v>18</v>
       </c>
-      <c r="N40" s="436"/>
-      <c r="O40" s="436"/>
+      <c r="N40" s="469"/>
+      <c r="O40" s="469"/>
       <c r="Q40" s="339"/>
       <c r="R40" s="359"/>
       <c r="S40" s="357"/>
@@ -9382,27 +9382,27 @@
       <c r="U40" s="357"/>
       <c r="V40" s="357"/>
     </row>
-    <row r="41" spans="1:28" s="324" customFormat="1" ht="18" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="41" spans="1:28" s="324" customFormat="1" ht="18" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B41" s="360" t="s">
         <v>42</v>
       </c>
-      <c r="C41" s="427" t="s">
+      <c r="C41" s="478" t="s">
         <v>43</v>
       </c>
-      <c r="D41" s="428"/>
-      <c r="E41" s="428"/>
-      <c r="F41" s="428"/>
-      <c r="G41" s="428"/>
-      <c r="H41" s="428"/>
-      <c r="I41" s="428"/>
-      <c r="J41" s="428"/>
-      <c r="K41" s="429"/>
+      <c r="D41" s="479"/>
+      <c r="E41" s="479"/>
+      <c r="F41" s="479"/>
+      <c r="G41" s="479"/>
+      <c r="H41" s="479"/>
+      <c r="I41" s="479"/>
+      <c r="J41" s="479"/>
+      <c r="K41" s="480"/>
       <c r="L41" s="61" t="s">
         <v>44</v>
       </c>
-      <c r="M41" s="425"/>
-      <c r="N41" s="425"/>
-      <c r="O41" s="425"/>
+      <c r="M41" s="477"/>
+      <c r="N41" s="477"/>
+      <c r="O41" s="477"/>
       <c r="Q41" s="339"/>
       <c r="R41" s="359"/>
       <c r="S41" s="357"/>
@@ -9410,27 +9410,27 @@
       <c r="U41" s="357"/>
       <c r="V41" s="357"/>
     </row>
-    <row r="42" spans="1:28" s="324" customFormat="1" ht="18" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="42" spans="1:28" s="324" customFormat="1" ht="18" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B42" s="360" t="s">
         <v>45</v>
       </c>
-      <c r="C42" s="427" t="s">
+      <c r="C42" s="478" t="s">
         <v>46</v>
       </c>
-      <c r="D42" s="428"/>
-      <c r="E42" s="428"/>
-      <c r="F42" s="428"/>
-      <c r="G42" s="428"/>
-      <c r="H42" s="428"/>
-      <c r="I42" s="428"/>
-      <c r="J42" s="428"/>
-      <c r="K42" s="429"/>
+      <c r="D42" s="479"/>
+      <c r="E42" s="479"/>
+      <c r="F42" s="479"/>
+      <c r="G42" s="479"/>
+      <c r="H42" s="479"/>
+      <c r="I42" s="479"/>
+      <c r="J42" s="479"/>
+      <c r="K42" s="480"/>
       <c r="L42" s="61" t="s">
         <v>44</v>
       </c>
-      <c r="M42" s="425"/>
-      <c r="N42" s="425"/>
-      <c r="O42" s="425"/>
+      <c r="M42" s="477"/>
+      <c r="N42" s="477"/>
+      <c r="O42" s="477"/>
       <c r="Q42" s="339"/>
       <c r="R42" s="359"/>
       <c r="S42" s="357"/>
@@ -9438,27 +9438,27 @@
       <c r="U42" s="357"/>
       <c r="V42" s="357"/>
     </row>
-    <row r="43" spans="1:28" s="324" customFormat="1" ht="18" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="43" spans="1:28" s="324" customFormat="1" ht="18" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B43" s="360" t="s">
         <v>47</v>
       </c>
-      <c r="C43" s="427" t="s">
+      <c r="C43" s="478" t="s">
         <v>214</v>
       </c>
-      <c r="D43" s="428"/>
-      <c r="E43" s="428"/>
-      <c r="F43" s="428"/>
-      <c r="G43" s="428"/>
-      <c r="H43" s="428"/>
-      <c r="I43" s="428"/>
-      <c r="J43" s="428"/>
-      <c r="K43" s="429"/>
+      <c r="D43" s="479"/>
+      <c r="E43" s="479"/>
+      <c r="F43" s="479"/>
+      <c r="G43" s="479"/>
+      <c r="H43" s="479"/>
+      <c r="I43" s="479"/>
+      <c r="J43" s="479"/>
+      <c r="K43" s="480"/>
       <c r="L43" s="366" t="s">
         <v>44</v>
       </c>
-      <c r="M43" s="430"/>
-      <c r="N43" s="431"/>
-      <c r="O43" s="432"/>
+      <c r="M43" s="445"/>
+      <c r="N43" s="481"/>
+      <c r="O43" s="446"/>
       <c r="Q43" s="339"/>
       <c r="R43" s="359"/>
       <c r="S43" s="357"/>
@@ -9466,26 +9466,26 @@
       <c r="U43" s="357"/>
       <c r="V43" s="357"/>
     </row>
-    <row r="44" spans="1:28" s="324" customFormat="1" ht="18" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="B44" s="422" t="s">
+    <row r="44" spans="1:28" s="324" customFormat="1" ht="18" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="B44" s="474" t="s">
         <v>49</v>
       </c>
-      <c r="C44" s="423" t="s">
+      <c r="C44" s="475" t="s">
         <v>50</v>
       </c>
-      <c r="D44" s="423"/>
-      <c r="E44" s="423"/>
-      <c r="F44" s="423"/>
-      <c r="G44" s="423"/>
-      <c r="H44" s="423"/>
-      <c r="I44" s="423"/>
-      <c r="J44" s="423"/>
-      <c r="K44" s="423"/>
-      <c r="L44" s="424" t="s">
+      <c r="D44" s="475"/>
+      <c r="E44" s="475"/>
+      <c r="F44" s="475"/>
+      <c r="G44" s="475"/>
+      <c r="H44" s="475"/>
+      <c r="I44" s="475"/>
+      <c r="J44" s="475"/>
+      <c r="K44" s="475"/>
+      <c r="L44" s="476" t="s">
         <v>44</v>
       </c>
-      <c r="M44" s="425"/>
-      <c r="N44" s="425"/>
+      <c r="M44" s="477"/>
+      <c r="N44" s="477"/>
       <c r="O44" s="367"/>
       <c r="R44" s="359"/>
       <c r="S44" s="357"/>
@@ -9493,36 +9493,36 @@
       <c r="U44" s="357"/>
       <c r="V44" s="357"/>
     </row>
-    <row r="45" spans="1:28" s="324" customFormat="1" ht="18" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="B45" s="422"/>
-      <c r="C45" s="423"/>
-      <c r="D45" s="423"/>
-      <c r="E45" s="423"/>
-      <c r="F45" s="423"/>
-      <c r="G45" s="423"/>
-      <c r="H45" s="423"/>
-      <c r="I45" s="423"/>
-      <c r="J45" s="423"/>
-      <c r="K45" s="423"/>
-      <c r="L45" s="424"/>
-      <c r="M45" s="426" t="s">
+    <row r="45" spans="1:28" s="324" customFormat="1" ht="18" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="B45" s="474"/>
+      <c r="C45" s="475"/>
+      <c r="D45" s="475"/>
+      <c r="E45" s="475"/>
+      <c r="F45" s="475"/>
+      <c r="G45" s="475"/>
+      <c r="H45" s="475"/>
+      <c r="I45" s="475"/>
+      <c r="J45" s="475"/>
+      <c r="K45" s="475"/>
+      <c r="L45" s="476"/>
+      <c r="M45" s="473" t="s">
         <v>215</v>
       </c>
-      <c r="N45" s="426"/>
-      <c r="O45" s="426"/>
+      <c r="N45" s="473"/>
+      <c r="O45" s="473"/>
       <c r="Q45" s="339"/>
-      <c r="S45" s="420"/>
-      <c r="T45" s="420"/>
-      <c r="U45" s="420"/>
-      <c r="V45" s="420"/>
-      <c r="W45" s="420"/>
+      <c r="S45" s="488"/>
+      <c r="T45" s="488"/>
+      <c r="U45" s="488"/>
+      <c r="V45" s="488"/>
+      <c r="W45" s="488"/>
       <c r="X45" s="370"/>
-      <c r="Y45" s="415"/>
-      <c r="Z45" s="415"/>
-      <c r="AA45" s="415"/>
-      <c r="AB45" s="415"/>
-    </row>
-    <row r="46" spans="1:28" s="324" customFormat="1" ht="9.75" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="Y45" s="483"/>
+      <c r="Z45" s="483"/>
+      <c r="AA45" s="483"/>
+      <c r="AB45" s="483"/>
+    </row>
+    <row r="46" spans="1:28" s="324" customFormat="1" ht="9.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="K46" s="372"/>
       <c r="L46" s="373"/>
       <c r="M46" s="374"/>
@@ -9540,37 +9540,37 @@
       <c r="AA46" s="371"/>
       <c r="AB46" s="371"/>
     </row>
-    <row r="47" spans="1:28" s="324" customFormat="1" ht="24.75" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="47" spans="1:28" s="324" customFormat="1" ht="24.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A47" s="53"/>
-      <c r="B47" s="416" t="s">
+      <c r="B47" s="484" t="s">
         <v>217</v>
       </c>
-      <c r="C47" s="416"/>
-      <c r="D47" s="416"/>
-      <c r="E47" s="416"/>
-      <c r="F47" s="416"/>
-      <c r="G47" s="416"/>
-      <c r="H47" s="416"/>
-      <c r="I47" s="416"/>
-      <c r="J47" s="416"/>
-      <c r="K47" s="416"/>
-      <c r="L47" s="416"/>
-      <c r="M47" s="416"/>
-      <c r="N47" s="416"/>
-      <c r="O47" s="416"/>
+      <c r="C47" s="484"/>
+      <c r="D47" s="484"/>
+      <c r="E47" s="484"/>
+      <c r="F47" s="484"/>
+      <c r="G47" s="484"/>
+      <c r="H47" s="484"/>
+      <c r="I47" s="484"/>
+      <c r="J47" s="484"/>
+      <c r="K47" s="484"/>
+      <c r="L47" s="484"/>
+      <c r="M47" s="484"/>
+      <c r="N47" s="484"/>
+      <c r="O47" s="484"/>
       <c r="Q47" s="339"/>
-      <c r="S47" s="417"/>
-      <c r="T47" s="418"/>
-      <c r="U47" s="418"/>
-      <c r="V47" s="418"/>
+      <c r="S47" s="485"/>
+      <c r="T47" s="486"/>
+      <c r="U47" s="486"/>
+      <c r="V47" s="486"/>
       <c r="W47" s="373"/>
       <c r="X47" s="370"/>
-      <c r="Y47" s="419"/>
-      <c r="Z47" s="419"/>
+      <c r="Y47" s="487"/>
+      <c r="Z47" s="487"/>
       <c r="AA47" s="375"/>
       <c r="AB47" s="375"/>
     </row>
-    <row r="48" spans="1:28" s="324" customFormat="1" ht="21" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="48" spans="1:28" s="324" customFormat="1" ht="21" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A48" s="376" t="s">
         <v>30</v>
       </c>
@@ -9591,7 +9591,7 @@
       <c r="P48" s="339"/>
       <c r="Q48" s="339"/>
     </row>
-    <row r="49" spans="1:17" s="324" customFormat="1" ht="37.5" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="49" spans="1:17" s="324" customFormat="1" ht="37.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B49" s="377"/>
       <c r="C49" s="378"/>
       <c r="D49" s="378"/>
@@ -9600,7 +9600,7 @@
       <c r="P49" s="339"/>
       <c r="Q49" s="339"/>
     </row>
-    <row r="50" spans="1:17" s="324" customFormat="1" ht="21" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="50" spans="1:17" s="324" customFormat="1" ht="21" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A50" s="381"/>
       <c r="B50" s="377"/>
       <c r="C50" s="378"/>
@@ -9619,7 +9619,7 @@
       <c r="P50" s="339"/>
       <c r="Q50" s="339"/>
     </row>
-    <row r="51" spans="1:17" s="324" customFormat="1" ht="21" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="51" spans="1:17" s="324" customFormat="1" ht="21" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A51" s="381"/>
       <c r="G51" s="382"/>
       <c r="H51" s="382"/>
@@ -9633,7 +9633,7 @@
       <c r="P51" s="339"/>
       <c r="Q51" s="339"/>
     </row>
-    <row r="52" spans="1:17" s="324" customFormat="1" ht="15.95" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="52" spans="1:17" s="324" customFormat="1" ht="15.9" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A52" s="385" t="s">
         <v>31</v>
       </c>
@@ -9654,7 +9654,7 @@
       <c r="P52" s="339"/>
       <c r="Q52" s="339"/>
     </row>
-    <row r="53" spans="1:17" s="324" customFormat="1" ht="15.95" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="53" spans="1:17" s="324" customFormat="1" ht="15.9" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A53" s="347" t="s">
         <v>218</v>
       </c>
@@ -9675,25 +9675,25 @@
       <c r="P53" s="339"/>
       <c r="Q53" s="339"/>
     </row>
-    <row r="54" spans="1:17" s="324" customFormat="1" ht="6.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="55" spans="1:17" s="324" customFormat="1" ht="30.75" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A55" s="421" t="s">
+    <row r="54" spans="1:17" s="324" customFormat="1" ht="6.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="55" spans="1:17" s="324" customFormat="1" ht="30.75" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A55" s="482" t="s">
         <v>220</v>
       </c>
-      <c r="B55" s="421"/>
-      <c r="C55" s="421"/>
-      <c r="D55" s="421"/>
-      <c r="E55" s="421"/>
-      <c r="F55" s="421"/>
-      <c r="G55" s="421"/>
-      <c r="H55" s="421"/>
-      <c r="I55" s="421"/>
-      <c r="J55" s="421"/>
-      <c r="K55" s="421"/>
-      <c r="L55" s="421"/>
-      <c r="M55" s="421"/>
-      <c r="N55" s="421"/>
-      <c r="O55" s="421"/>
+      <c r="B55" s="482"/>
+      <c r="C55" s="482"/>
+      <c r="D55" s="482"/>
+      <c r="E55" s="482"/>
+      <c r="F55" s="482"/>
+      <c r="G55" s="482"/>
+      <c r="H55" s="482"/>
+      <c r="I55" s="482"/>
+      <c r="J55" s="482"/>
+      <c r="K55" s="482"/>
+      <c r="L55" s="482"/>
+      <c r="M55" s="482"/>
+      <c r="N55" s="482"/>
+      <c r="O55" s="482"/>
     </row>
   </sheetData>
   <sheetProtection algorithmName="SHA-512" hashValue="p/p19vWrteK21R1hmk+ElTgYjVXoOZVGuGwRP4wn8zBvsCq/fZMxmr11hqz65vFsSUzJhzZD83JjvmqBrsog8A==" saltValue="Kj9jOF/EYNXPn2HAYjciOA==" spinCount="100000" sheet="1" objects="1" scenarios="1"/>
@@ -9702,27 +9702,40 @@
     <protectedRange sqref="C10:C11 D11" name="Rango3_3_1_1_1_1_1_2_1"/>
   </protectedRanges>
   <mergeCells count="71">
-    <mergeCell ref="A14:O14"/>
-    <mergeCell ref="B16:F16"/>
-    <mergeCell ref="H16:J16"/>
-    <mergeCell ref="B11:D11"/>
-    <mergeCell ref="F11:G11"/>
-    <mergeCell ref="I11:K11"/>
-    <mergeCell ref="M11:O11"/>
-    <mergeCell ref="A13:O13"/>
-    <mergeCell ref="K16:L16"/>
-    <mergeCell ref="A7:O7"/>
-    <mergeCell ref="A8:O8"/>
-    <mergeCell ref="F10:G10"/>
-    <mergeCell ref="I10:K10"/>
-    <mergeCell ref="M10:O10"/>
-    <mergeCell ref="B18:D18"/>
-    <mergeCell ref="E18:F18"/>
-    <mergeCell ref="H18:J18"/>
-    <mergeCell ref="K18:L18"/>
-    <mergeCell ref="B17:D17"/>
-    <mergeCell ref="H17:J17"/>
-    <mergeCell ref="K17:L17"/>
+    <mergeCell ref="Y45:Z45"/>
+    <mergeCell ref="AA45:AB45"/>
+    <mergeCell ref="B47:O47"/>
+    <mergeCell ref="S47:V47"/>
+    <mergeCell ref="Y47:Z47"/>
+    <mergeCell ref="S45:W45"/>
+    <mergeCell ref="A55:O55"/>
+    <mergeCell ref="B44:B45"/>
+    <mergeCell ref="C44:K45"/>
+    <mergeCell ref="L44:L45"/>
+    <mergeCell ref="M44:N44"/>
+    <mergeCell ref="M45:O45"/>
+    <mergeCell ref="C41:K41"/>
+    <mergeCell ref="M41:O41"/>
+    <mergeCell ref="C42:K42"/>
+    <mergeCell ref="M42:O42"/>
+    <mergeCell ref="C43:K43"/>
+    <mergeCell ref="M43:O43"/>
+    <mergeCell ref="B37:B38"/>
+    <mergeCell ref="C37:K38"/>
+    <mergeCell ref="L37:L38"/>
+    <mergeCell ref="M37:N37"/>
+    <mergeCell ref="B40:K40"/>
+    <mergeCell ref="M40:O40"/>
+    <mergeCell ref="H23:J23"/>
+    <mergeCell ref="K23:L23"/>
+    <mergeCell ref="N24:O24"/>
+    <mergeCell ref="B31:O31"/>
+    <mergeCell ref="B33:K33"/>
+    <mergeCell ref="M33:O33"/>
+    <mergeCell ref="B27:G27"/>
+    <mergeCell ref="K27:N27"/>
+    <mergeCell ref="K28:N28"/>
+    <mergeCell ref="K29:N29"/>
     <mergeCell ref="B19:D19"/>
     <mergeCell ref="E19:F19"/>
     <mergeCell ref="H19:J19"/>
@@ -9739,40 +9752,27 @@
     <mergeCell ref="K22:L22"/>
     <mergeCell ref="B23:D23"/>
     <mergeCell ref="E23:F23"/>
-    <mergeCell ref="H23:J23"/>
-    <mergeCell ref="K23:L23"/>
-    <mergeCell ref="N24:O24"/>
-    <mergeCell ref="B31:O31"/>
-    <mergeCell ref="B33:K33"/>
-    <mergeCell ref="M33:O33"/>
-    <mergeCell ref="B27:G27"/>
-    <mergeCell ref="K27:N27"/>
-    <mergeCell ref="K28:N28"/>
-    <mergeCell ref="K29:N29"/>
-    <mergeCell ref="B37:B38"/>
-    <mergeCell ref="C37:K38"/>
-    <mergeCell ref="L37:L38"/>
-    <mergeCell ref="M37:N37"/>
-    <mergeCell ref="B40:K40"/>
-    <mergeCell ref="M40:O40"/>
-    <mergeCell ref="C41:K41"/>
-    <mergeCell ref="M41:O41"/>
-    <mergeCell ref="C42:K42"/>
-    <mergeCell ref="M42:O42"/>
-    <mergeCell ref="C43:K43"/>
-    <mergeCell ref="M43:O43"/>
-    <mergeCell ref="A55:O55"/>
-    <mergeCell ref="B44:B45"/>
-    <mergeCell ref="C44:K45"/>
-    <mergeCell ref="L44:L45"/>
-    <mergeCell ref="M44:N44"/>
-    <mergeCell ref="M45:O45"/>
-    <mergeCell ref="Y45:Z45"/>
-    <mergeCell ref="AA45:AB45"/>
-    <mergeCell ref="B47:O47"/>
-    <mergeCell ref="S47:V47"/>
-    <mergeCell ref="Y47:Z47"/>
-    <mergeCell ref="S45:W45"/>
+    <mergeCell ref="B18:D18"/>
+    <mergeCell ref="E18:F18"/>
+    <mergeCell ref="H18:J18"/>
+    <mergeCell ref="K18:L18"/>
+    <mergeCell ref="B17:D17"/>
+    <mergeCell ref="H17:J17"/>
+    <mergeCell ref="K17:L17"/>
+    <mergeCell ref="A7:O7"/>
+    <mergeCell ref="A8:O8"/>
+    <mergeCell ref="F10:G10"/>
+    <mergeCell ref="I10:K10"/>
+    <mergeCell ref="M10:O10"/>
+    <mergeCell ref="A14:O14"/>
+    <mergeCell ref="B16:F16"/>
+    <mergeCell ref="H16:J16"/>
+    <mergeCell ref="B11:D11"/>
+    <mergeCell ref="F11:G11"/>
+    <mergeCell ref="I11:K11"/>
+    <mergeCell ref="M11:O11"/>
+    <mergeCell ref="A13:O13"/>
+    <mergeCell ref="K16:L16"/>
   </mergeCells>
   <conditionalFormatting sqref="B36">
     <cfRule type="cellIs" priority="2" stopIfTrue="1" operator="between">
@@ -9797,21 +9797,21 @@
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
   <sheetPr codeName="Hoja2"/>
   <dimension ref="A2:N48"/>
-  <sheetFormatPr baseColWidth="10" defaultColWidth="10.28515625" defaultRowHeight="15" x14ac:dyDescent="0.2"/>
+  <sheetFormatPr baseColWidth="10" defaultColWidth="10.33203125" defaultRowHeight="13.8" x14ac:dyDescent="0.25"/>
   <cols>
-    <col min="1" max="1" width="10.7109375" style="17" customWidth="1"/>
+    <col min="1" max="1" width="10.6640625" style="17" customWidth="1"/>
     <col min="2" max="2" width="2" style="17" customWidth="1"/>
-    <col min="3" max="3" width="4.28515625" style="17" customWidth="1"/>
-    <col min="4" max="4" width="1.140625" style="17" customWidth="1"/>
-    <col min="5" max="8" width="12.7109375" style="17" customWidth="1"/>
+    <col min="3" max="3" width="4.33203125" style="17" customWidth="1"/>
+    <col min="4" max="4" width="1.109375" style="17" customWidth="1"/>
+    <col min="5" max="8" width="12.6640625" style="17" customWidth="1"/>
     <col min="9" max="9" width="5" style="17" customWidth="1"/>
-    <col min="10" max="10" width="10.85546875" style="17" customWidth="1"/>
-    <col min="11" max="11" width="1.5703125" style="17" customWidth="1"/>
-    <col min="12" max="12" width="13.5703125" style="17" customWidth="1"/>
-    <col min="13" max="16384" width="10.28515625" style="17"/>
+    <col min="10" max="10" width="10.88671875" style="17" customWidth="1"/>
+    <col min="11" max="11" width="1.5546875" style="17" customWidth="1"/>
+    <col min="12" max="12" width="13.5546875" style="17" customWidth="1"/>
+    <col min="13" max="16384" width="10.33203125" style="17"/>
   </cols>
   <sheetData>
-    <row r="2" spans="1:12" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="2" spans="1:12" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A2" s="491" t="s">
         <v>0</v>
       </c>
@@ -9827,7 +9827,7 @@
       <c r="K2" s="491"/>
       <c r="L2" s="491"/>
     </row>
-    <row r="3" spans="1:12" ht="15.95" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="3" spans="1:12" ht="15.9" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A3" s="498">
         <v>0</v>
       </c>
@@ -9843,8 +9843,8 @@
       <c r="K3" s="498"/>
       <c r="L3" s="498"/>
     </row>
-    <row r="4" spans="1:12" ht="15.95" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="5" spans="1:12" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="4" spans="1:12" ht="15.9" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="5" spans="1:12" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A5" s="118" t="s">
         <v>1</v>
       </c>
@@ -9871,7 +9871,7 @@
         <v>170</v>
       </c>
     </row>
-    <row r="6" spans="1:12" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="6" spans="1:12" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A6" s="118" t="s">
         <v>4</v>
       </c>
@@ -9899,7 +9899,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="7" spans="1:12" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="7" spans="1:12" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A7" s="118" t="s">
         <v>5</v>
       </c>
@@ -9927,7 +9927,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="8" spans="1:12" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="8" spans="1:12" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A8" s="118" t="s">
         <v>7</v>
       </c>
@@ -9955,7 +9955,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="9" spans="1:12" ht="15.95" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="9" spans="1:12" ht="15.9" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A9" s="53" t="s">
         <v>8</v>
       </c>
@@ -9971,7 +9971,7 @@
       <c r="K9" s="23"/>
       <c r="L9" s="18"/>
     </row>
-    <row r="10" spans="1:12" ht="3.75" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="10" spans="1:12" ht="3.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A10" s="112"/>
       <c r="B10" s="52"/>
       <c r="C10" s="52"/>
@@ -9985,7 +9985,7 @@
       <c r="K10" s="23"/>
       <c r="L10" s="18"/>
     </row>
-    <row r="11" spans="1:12" ht="15.6" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="11" spans="1:12" ht="15.6" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A11" s="492" t="s">
         <v>169</v>
       </c>
@@ -10001,7 +10001,7 @@
       <c r="K11" s="493"/>
       <c r="L11" s="494"/>
     </row>
-    <row r="12" spans="1:12" ht="15.6" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="12" spans="1:12" ht="15.6" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A12" s="495" t="s">
         <v>179</v>
       </c>
@@ -10017,7 +10017,7 @@
       <c r="K12" s="496"/>
       <c r="L12" s="497"/>
     </row>
-    <row r="13" spans="1:12" ht="6" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="13" spans="1:12" ht="6" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A13" s="28"/>
       <c r="B13" s="29"/>
       <c r="C13" s="29"/>
@@ -10031,7 +10031,7 @@
       <c r="K13" s="32"/>
       <c r="L13" s="33"/>
     </row>
-    <row r="14" spans="1:12" ht="16.5" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="14" spans="1:12" ht="16.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A14" s="34" t="s">
         <v>9</v>
       </c>
@@ -10047,7 +10047,7 @@
       <c r="K14" s="159"/>
       <c r="L14" s="35"/>
     </row>
-    <row r="15" spans="1:12" ht="16.5" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="15" spans="1:12" ht="16.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A15" s="36" t="s">
         <v>10</v>
       </c>
@@ -10075,7 +10075,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="16" spans="1:12" ht="16.5" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="16" spans="1:12" ht="16.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A16" s="36" t="s">
         <v>12</v>
       </c>
@@ -10103,7 +10103,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="17" spans="1:13" ht="16.5" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="17" spans="1:13" ht="16.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A17" s="36" t="s">
         <v>165</v>
       </c>
@@ -10135,7 +10135,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="18" spans="1:13" ht="16.5" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="18" spans="1:13" ht="16.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A18" s="36" t="s">
         <v>15</v>
       </c>
@@ -10152,7 +10152,7 @@
       <c r="K18" s="155"/>
       <c r="L18" s="14"/>
     </row>
-    <row r="19" spans="1:13" ht="9" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="19" spans="1:13" ht="9" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A19" s="37"/>
       <c r="B19" s="54"/>
       <c r="C19" s="54"/>
@@ -10166,7 +10166,7 @@
       <c r="K19" s="133"/>
       <c r="L19" s="161"/>
     </row>
-    <row r="20" spans="1:13" ht="13.5" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="20" spans="1:13" ht="13.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A20" s="41"/>
       <c r="B20" s="42"/>
       <c r="C20" s="42"/>
@@ -10180,7 +10180,7 @@
       <c r="K20" s="42"/>
       <c r="L20" s="43"/>
     </row>
-    <row r="21" spans="1:13" ht="19.5" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="21" spans="1:13" ht="19.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A21" s="41"/>
       <c r="B21" s="500" t="s">
         <v>16</v>
@@ -10200,7 +10200,7 @@
       <c r="K21" s="42"/>
       <c r="L21" s="43"/>
     </row>
-    <row r="22" spans="1:13" ht="19.5" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="22" spans="1:13" ht="19.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A22" s="41"/>
       <c r="B22" s="302" t="s">
         <v>19</v>
@@ -10221,7 +10221,7 @@
       <c r="K22" s="44"/>
       <c r="L22" s="43"/>
     </row>
-    <row r="23" spans="1:13" ht="19.5" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="23" spans="1:13" ht="19.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A23" s="41"/>
       <c r="B23" s="236" t="s">
         <v>21</v>
@@ -10242,7 +10242,7 @@
       <c r="K23" s="44"/>
       <c r="L23" s="43"/>
     </row>
-    <row r="24" spans="1:13" ht="19.5" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="24" spans="1:13" ht="19.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A24" s="41"/>
       <c r="B24" s="236" t="s">
         <v>22</v>
@@ -10263,7 +10263,7 @@
       <c r="K24" s="44"/>
       <c r="L24" s="43"/>
     </row>
-    <row r="25" spans="1:13" ht="19.5" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="25" spans="1:13" ht="19.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A25" s="41"/>
       <c r="B25" s="303" t="s">
         <v>23</v>
@@ -10284,7 +10284,7 @@
       <c r="K25" s="44"/>
       <c r="L25" s="43"/>
     </row>
-    <row r="26" spans="1:13" ht="8.25" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="26" spans="1:13" ht="8.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A26" s="41"/>
       <c r="B26" s="42"/>
       <c r="C26" s="42"/>
@@ -10298,7 +10298,7 @@
       <c r="K26" s="42"/>
       <c r="L26" s="43"/>
     </row>
-    <row r="27" spans="1:13" ht="9" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="27" spans="1:13" ht="9" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A27" s="45"/>
       <c r="B27" s="47"/>
       <c r="C27" s="47"/>
@@ -10312,7 +10312,7 @@
       <c r="K27" s="47"/>
       <c r="L27" s="48"/>
     </row>
-    <row r="28" spans="1:13" ht="13.15" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="28" spans="1:13" ht="13.2" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A28" s="57"/>
       <c r="B28" s="57"/>
       <c r="C28" s="57"/>
@@ -10326,7 +10326,7 @@
       <c r="K28" s="58"/>
       <c r="L28" s="58"/>
     </row>
-    <row r="29" spans="1:13" ht="12.75" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="29" spans="1:13" ht="12.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A29" s="113" t="s">
         <v>25</v>
       </c>
@@ -10342,7 +10342,7 @@
       <c r="K29" s="114"/>
       <c r="L29" s="114"/>
     </row>
-    <row r="30" spans="1:13" ht="17.25" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="30" spans="1:13" ht="17.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A30" s="59" t="s">
         <v>26</v>
       </c>
@@ -10360,7 +10360,7 @@
       <c r="K30" s="412"/>
       <c r="L30" s="49"/>
     </row>
-    <row r="31" spans="1:13" ht="17.25" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="31" spans="1:13" ht="17.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A31" s="59" t="s">
         <v>27</v>
       </c>
@@ -10378,7 +10378,7 @@
       <c r="K31" s="49"/>
       <c r="L31" s="49"/>
     </row>
-    <row r="32" spans="1:13" ht="17.25" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="32" spans="1:13" ht="17.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A32" s="59" t="s">
         <v>28</v>
       </c>
@@ -10390,13 +10390,13 @@
       <c r="G32" s="21"/>
       <c r="H32" s="21"/>
       <c r="J32" s="131">
-        <f>+'FORMATO PEG'!H29</f>
+        <f>+'FORMATO PEG'!H28</f>
         <v>0</v>
       </c>
       <c r="K32" s="49"/>
       <c r="L32" s="49"/>
     </row>
-    <row r="33" spans="1:14" ht="17.25" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="33" spans="1:14" ht="17.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A33" s="59"/>
       <c r="B33" s="21"/>
       <c r="C33" s="21"/>
@@ -10409,7 +10409,7 @@
       <c r="K33" s="49"/>
       <c r="L33" s="49"/>
     </row>
-    <row r="34" spans="1:14" ht="18.75" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="34" spans="1:14" ht="18.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A34" s="113" t="s">
         <v>29</v>
       </c>
@@ -10423,7 +10423,7 @@
       <c r="K34" s="49"/>
       <c r="L34" s="49"/>
     </row>
-    <row r="35" spans="1:14" ht="15.6" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="35" spans="1:14" ht="15.6" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A35" s="499" t="s">
         <v>228</v>
       </c>
@@ -10439,7 +10439,7 @@
       <c r="K35" s="499"/>
       <c r="L35" s="499"/>
     </row>
-    <row r="36" spans="1:14" ht="36" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="36" spans="1:14" ht="36" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A36" s="489" t="s">
         <v>229</v>
       </c>
@@ -10455,7 +10455,7 @@
       <c r="K36" s="489"/>
       <c r="L36" s="489"/>
     </row>
-    <row r="37" spans="1:14" ht="16.899999999999999" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="37" spans="1:14" ht="16.95" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A37" s="489" t="s">
         <v>230</v>
       </c>
@@ -10471,7 +10471,7 @@
       <c r="K37" s="489"/>
       <c r="L37" s="489"/>
     </row>
-    <row r="38" spans="1:14" ht="25.15" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="38" spans="1:14" ht="25.2" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A38" s="489" t="s">
         <v>231</v>
       </c>
@@ -10487,7 +10487,7 @@
       <c r="K38" s="489"/>
       <c r="L38" s="489"/>
     </row>
-    <row r="39" spans="1:14" ht="27" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="39" spans="1:14" ht="27" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A39" s="490" t="s">
         <v>232</v>
       </c>
@@ -10505,7 +10505,7 @@
       <c r="M39" s="315"/>
       <c r="N39" s="315"/>
     </row>
-    <row r="40" spans="1:14" ht="8.4499999999999993" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="40" spans="1:14" ht="8.4" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A40" s="59"/>
       <c r="B40" s="27"/>
       <c r="C40" s="27"/>
@@ -10620,7 +10620,7 @@
         <v>32</v>
       </c>
     </row>
-    <row r="48" spans="1:14" ht="15.95" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="48" spans="1:14" ht="15.9" customHeight="1" x14ac:dyDescent="0.25"/>
   </sheetData>
   <sheetProtection algorithmName="SHA-512" hashValue="TKsx5PlgylLWyGYhfocC8sgaNILNxRuol5A4x1XI9JyUeqee8tSS9KoSmDITLxV4Su1P+Gma+vEO9dJggaQ2ew==" saltValue="ECM8i66Pfuo8Nh0Pu63qbQ==" spinCount="100000" sheet="1" objects="1" scenarios="1"/>
   <protectedRanges>
@@ -10663,44 +10663,44 @@
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0100-000000000000}">
   <dimension ref="A1:T28"/>
-  <sheetFormatPr baseColWidth="10" defaultColWidth="10.28515625" defaultRowHeight="12" x14ac:dyDescent="0.2"/>
+  <sheetFormatPr baseColWidth="10" defaultColWidth="10.33203125" defaultRowHeight="11.4" x14ac:dyDescent="0.25"/>
   <cols>
-    <col min="1" max="1" width="4.5703125" style="20" customWidth="1"/>
-    <col min="2" max="2" width="10.140625" style="20" customWidth="1"/>
-    <col min="3" max="3" width="9.42578125" style="20" customWidth="1"/>
-    <col min="4" max="4" width="7.42578125" style="20" customWidth="1"/>
-    <col min="5" max="5" width="6.42578125" style="20" customWidth="1"/>
-    <col min="6" max="6" width="5.7109375" style="20" customWidth="1"/>
-    <col min="7" max="7" width="5.5703125" style="20" customWidth="1"/>
-    <col min="8" max="8" width="5.42578125" style="20" customWidth="1"/>
-    <col min="9" max="14" width="11.140625" style="20" customWidth="1"/>
-    <col min="15" max="15" width="6.7109375" style="20" customWidth="1"/>
-    <col min="16" max="16" width="12.140625" style="20" customWidth="1"/>
-    <col min="17" max="17" width="15.28515625" style="20" customWidth="1"/>
-    <col min="18" max="18" width="9.5703125" style="20" customWidth="1"/>
-    <col min="19" max="16384" width="10.28515625" style="20"/>
+    <col min="1" max="1" width="4.5546875" style="20" customWidth="1"/>
+    <col min="2" max="2" width="10.109375" style="20" customWidth="1"/>
+    <col min="3" max="3" width="9.44140625" style="20" customWidth="1"/>
+    <col min="4" max="4" width="7.44140625" style="20" customWidth="1"/>
+    <col min="5" max="5" width="6.44140625" style="20" customWidth="1"/>
+    <col min="6" max="6" width="5.6640625" style="20" customWidth="1"/>
+    <col min="7" max="7" width="5.5546875" style="20" customWidth="1"/>
+    <col min="8" max="8" width="5.44140625" style="20" customWidth="1"/>
+    <col min="9" max="14" width="11.109375" style="20" customWidth="1"/>
+    <col min="15" max="15" width="6.6640625" style="20" customWidth="1"/>
+    <col min="16" max="16" width="12.109375" style="20" customWidth="1"/>
+    <col min="17" max="17" width="15.33203125" style="20" customWidth="1"/>
+    <col min="18" max="18" width="9.5546875" style="20" customWidth="1"/>
+    <col min="19" max="16384" width="10.33203125" style="20"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:20" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A1" s="504" t="s">
+    <row r="1" spans="1:20" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A1" s="516" t="s">
         <v>180</v>
       </c>
-      <c r="B1" s="505"/>
-      <c r="C1" s="505"/>
-      <c r="D1" s="505"/>
-      <c r="E1" s="505"/>
-      <c r="F1" s="505"/>
-      <c r="G1" s="505"/>
-      <c r="H1" s="505"/>
-      <c r="I1" s="505"/>
-      <c r="J1" s="505"/>
-      <c r="K1" s="505"/>
-      <c r="L1" s="505"/>
-      <c r="M1" s="505"/>
-      <c r="N1" s="506"/>
+      <c r="B1" s="517"/>
+      <c r="C1" s="517"/>
+      <c r="D1" s="517"/>
+      <c r="E1" s="517"/>
+      <c r="F1" s="517"/>
+      <c r="G1" s="517"/>
+      <c r="H1" s="517"/>
+      <c r="I1" s="517"/>
+      <c r="J1" s="517"/>
+      <c r="K1" s="517"/>
+      <c r="L1" s="517"/>
+      <c r="M1" s="517"/>
+      <c r="N1" s="518"/>
       <c r="O1" s="64"/>
     </row>
-    <row r="2" spans="1:20" ht="15.95" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="2" spans="1:20" ht="15.9" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A2" s="167" t="s">
         <v>33</v>
       </c>
@@ -10718,7 +10718,7 @@
       <c r="M2" s="71"/>
       <c r="N2" s="72"/>
     </row>
-    <row r="3" spans="1:20" ht="15.95" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="3" spans="1:20" ht="15.9" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A3" s="169" t="s">
         <v>34</v>
       </c>
@@ -10733,7 +10733,7 @@
       <c r="M3" s="65"/>
       <c r="N3" s="73"/>
     </row>
-    <row r="4" spans="1:20" ht="15.95" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="4" spans="1:20" ht="15.9" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A4" s="169" t="s">
         <v>35</v>
       </c>
@@ -10759,7 +10759,7 @@
       <c r="M4" s="65"/>
       <c r="N4" s="73"/>
     </row>
-    <row r="5" spans="1:20" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="5" spans="1:20" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A5" s="170" t="s">
         <v>36</v>
       </c>
@@ -10780,7 +10780,7 @@
       <c r="M5" s="74"/>
       <c r="N5" s="75"/>
     </row>
-    <row r="6" spans="1:20" ht="6" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="6" spans="1:20" ht="6" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A6" s="106"/>
       <c r="C6" s="107"/>
       <c r="D6" s="108"/>
@@ -10795,31 +10795,31 @@
       <c r="M6" s="65"/>
       <c r="N6" s="65"/>
     </row>
-    <row r="7" spans="1:20" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="7" spans="1:20" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A7" s="106"/>
       <c r="B7" s="177" t="s">
         <v>139</v>
       </c>
       <c r="C7" s="178"/>
       <c r="D7" s="179"/>
-      <c r="E7" s="515" t="s">
+      <c r="E7" s="527" t="s">
         <v>20</v>
       </c>
-      <c r="F7" s="516"/>
+      <c r="F7" s="528"/>
       <c r="G7" s="65"/>
       <c r="H7" s="177" t="s">
         <v>156</v>
       </c>
       <c r="I7" s="178"/>
       <c r="J7" s="180"/>
-      <c r="K7" s="520" t="s">
+      <c r="K7" s="507" t="s">
         <v>20</v>
       </c>
-      <c r="L7" s="521"/>
+      <c r="L7" s="508"/>
       <c r="M7" s="65"/>
       <c r="N7" s="65"/>
     </row>
-    <row r="8" spans="1:20" ht="6.75" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="8" spans="1:20" ht="6.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A8" s="106"/>
       <c r="C8" s="107"/>
       <c r="D8" s="108"/>
@@ -10834,22 +10834,22 @@
       <c r="M8" s="65"/>
       <c r="N8" s="65"/>
     </row>
-    <row r="9" spans="1:20" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="9" spans="1:20" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A9" s="106"/>
-      <c r="B9" s="511" t="s">
+      <c r="B9" s="523" t="s">
         <v>146</v>
       </c>
-      <c r="C9" s="511"/>
-      <c r="D9" s="510" t="e">
+      <c r="C9" s="523"/>
+      <c r="D9" s="522" t="e">
         <f>+INDEX(P13:Q23,MATCH(E7,P13:P23,0),2)</f>
         <v>#N/A</v>
       </c>
-      <c r="E9" s="510"/>
-      <c r="F9" s="512" t="e">
+      <c r="E9" s="522"/>
+      <c r="F9" s="524" t="e">
         <f>+IF(I13/1000&gt;D9,"Cumple","No Cumple")</f>
         <v>#N/A</v>
       </c>
-      <c r="G9" s="512"/>
+      <c r="G9" s="524"/>
       <c r="H9" s="65"/>
       <c r="J9" s="193" t="s">
         <v>161</v>
@@ -10859,7 +10859,7 @@
       </c>
       <c r="O9" s="146"/>
     </row>
-    <row r="10" spans="1:20" ht="6.75" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="10" spans="1:20" ht="6.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A10" s="106"/>
       <c r="B10" s="173"/>
       <c r="C10" s="173"/>
@@ -10870,31 +10870,31 @@
       <c r="H10" s="65"/>
       <c r="O10" s="146"/>
     </row>
-    <row r="11" spans="1:20" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A11" s="514" t="s">
+    <row r="11" spans="1:20" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A11" s="526" t="s">
         <v>38</v>
       </c>
-      <c r="B11" s="514"/>
-      <c r="C11" s="514"/>
-      <c r="D11" s="514"/>
-      <c r="E11" s="514"/>
-      <c r="F11" s="514"/>
-      <c r="G11" s="514"/>
-      <c r="H11" s="514" t="s">
+      <c r="B11" s="526"/>
+      <c r="C11" s="526"/>
+      <c r="D11" s="526"/>
+      <c r="E11" s="526"/>
+      <c r="F11" s="526"/>
+      <c r="G11" s="526"/>
+      <c r="H11" s="526" t="s">
         <v>39</v>
       </c>
-      <c r="I11" s="513" t="s">
+      <c r="I11" s="525" t="s">
         <v>128</v>
       </c>
-      <c r="J11" s="513"/>
-      <c r="K11" s="513" t="s">
+      <c r="J11" s="525"/>
+      <c r="K11" s="525" t="s">
         <v>129</v>
       </c>
-      <c r="L11" s="513"/>
-      <c r="M11" s="513" t="s">
+      <c r="L11" s="525"/>
+      <c r="M11" s="525" t="s">
         <v>130</v>
       </c>
-      <c r="N11" s="513"/>
+      <c r="N11" s="525"/>
       <c r="O11" s="147"/>
       <c r="P11" s="176" t="s">
         <v>153</v>
@@ -10903,15 +10903,15 @@
         <v>152</v>
       </c>
     </row>
-    <row r="12" spans="1:20" ht="20.45" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A12" s="514"/>
-      <c r="B12" s="514"/>
-      <c r="C12" s="514"/>
-      <c r="D12" s="514"/>
-      <c r="E12" s="514"/>
-      <c r="F12" s="514"/>
-      <c r="G12" s="514"/>
-      <c r="H12" s="514"/>
+    <row r="12" spans="1:20" ht="20.399999999999999" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A12" s="526"/>
+      <c r="B12" s="526"/>
+      <c r="C12" s="526"/>
+      <c r="D12" s="526"/>
+      <c r="E12" s="526"/>
+      <c r="F12" s="526"/>
+      <c r="G12" s="526"/>
+      <c r="H12" s="526"/>
       <c r="I12" s="110" t="s">
         <v>40</v>
       </c>
@@ -10938,7 +10938,7 @@
         <v>154</v>
       </c>
     </row>
-    <row r="13" spans="1:20" ht="23.25" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="13" spans="1:20" ht="23.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A13" s="183"/>
       <c r="B13" s="184" t="s">
         <v>140</v>
@@ -10949,15 +10949,15 @@
       <c r="F13" s="185"/>
       <c r="G13" s="186"/>
       <c r="H13" s="183"/>
-      <c r="I13" s="509">
+      <c r="I13" s="521">
         <f>+'FORMATO PEG'!O27</f>
         <v>0</v>
       </c>
-      <c r="J13" s="509"/>
-      <c r="K13" s="509"/>
-      <c r="L13" s="509"/>
-      <c r="M13" s="509"/>
-      <c r="N13" s="509"/>
+      <c r="J13" s="521"/>
+      <c r="K13" s="521"/>
+      <c r="L13" s="521"/>
+      <c r="M13" s="521"/>
+      <c r="N13" s="521"/>
       <c r="O13" s="148"/>
       <c r="P13" s="163" t="s">
         <v>138</v>
@@ -10966,7 +10966,7 @@
         <v>40</v>
       </c>
     </row>
-    <row r="14" spans="1:20" ht="23.25" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="14" spans="1:20" ht="23.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A14" s="183"/>
       <c r="B14" s="166" t="s">
         <v>147</v>
@@ -11008,21 +11008,21 @@
         <v>25</v>
       </c>
     </row>
-    <row r="15" spans="1:20" ht="23.25" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="15" spans="1:20" ht="23.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A15" s="183"/>
       <c r="B15" s="166" t="s">
         <v>148</v>
       </c>
       <c r="C15" s="185"/>
-      <c r="D15" s="522" t="s">
+      <c r="D15" s="509" t="s">
         <v>141</v>
       </c>
-      <c r="E15" s="522"/>
-      <c r="F15" s="507" t="e">
+      <c r="E15" s="509"/>
+      <c r="F15" s="519" t="e">
         <f>+SUM(J15,L15,N15)</f>
         <v>#DIV/0!</v>
       </c>
-      <c r="G15" s="508"/>
+      <c r="G15" s="520"/>
       <c r="H15" s="183" t="s">
         <v>24</v>
       </c>
@@ -11050,7 +11050,7 @@
       </c>
       <c r="T15" s="304"/>
     </row>
-    <row r="16" spans="1:20" ht="23.25" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="16" spans="1:20" ht="23.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A16" s="61" t="s">
         <v>42</v>
       </c>
@@ -11091,18 +11091,18 @@
         <v>12</v>
       </c>
     </row>
-    <row r="17" spans="1:17" ht="23.25" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="17" spans="1:17" ht="23.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A17" s="61" t="s">
         <v>45</v>
       </c>
-      <c r="B17" s="427" t="s">
+      <c r="B17" s="478" t="s">
         <v>46</v>
       </c>
-      <c r="C17" s="428"/>
-      <c r="D17" s="428"/>
-      <c r="E17" s="428"/>
-      <c r="F17" s="428"/>
-      <c r="G17" s="429"/>
+      <c r="C17" s="479"/>
+      <c r="D17" s="479"/>
+      <c r="E17" s="479"/>
+      <c r="F17" s="479"/>
+      <c r="G17" s="480"/>
       <c r="H17" s="142" t="s">
         <v>44</v>
       </c>
@@ -11132,18 +11132,18 @@
         <v>8</v>
       </c>
     </row>
-    <row r="18" spans="1:17" ht="23.25" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="18" spans="1:17" ht="23.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A18" s="61" t="s">
         <v>47</v>
       </c>
-      <c r="B18" s="517" t="s">
+      <c r="B18" s="504" t="s">
         <v>48</v>
       </c>
-      <c r="C18" s="518"/>
-      <c r="D18" s="518"/>
-      <c r="E18" s="518"/>
-      <c r="F18" s="518"/>
-      <c r="G18" s="519"/>
+      <c r="C18" s="505"/>
+      <c r="D18" s="505"/>
+      <c r="E18" s="505"/>
+      <c r="F18" s="505"/>
+      <c r="G18" s="506"/>
       <c r="H18" s="142" t="s">
         <v>44</v>
       </c>
@@ -11173,7 +11173,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="19" spans="1:17" ht="23.25" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="19" spans="1:17" ht="23.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A19" s="61" t="s">
         <v>49</v>
       </c>
@@ -11214,7 +11214,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="20" spans="1:17" ht="23.25" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="20" spans="1:17" ht="23.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A20" s="61" t="s">
         <v>51</v>
       </c>
@@ -11250,7 +11250,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="21" spans="1:17" ht="23.25" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="21" spans="1:17" ht="23.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A21" s="61" t="s">
         <v>53</v>
       </c>
@@ -11286,7 +11286,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="22" spans="1:17" ht="23.25" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="22" spans="1:17" ht="23.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A22" s="61" t="s">
         <v>55</v>
       </c>
@@ -11322,7 +11322,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="23" spans="1:17" ht="23.25" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="23" spans="1:17" ht="23.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A23" s="61" t="s">
         <v>57</v>
       </c>
@@ -11360,32 +11360,32 @@
         <v>2</v>
       </c>
     </row>
-    <row r="24" spans="1:17" ht="25.15" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="24" spans="1:17" ht="25.2" customHeight="1" x14ac:dyDescent="0.25">
       <c r="P24" s="165" t="s">
         <v>135</v>
       </c>
       <c r="Q24" s="163"/>
     </row>
-    <row r="25" spans="1:17" ht="27" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="25" spans="1:17" ht="27" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A25" s="68"/>
-      <c r="B25" s="427" t="s">
+      <c r="B25" s="478" t="s">
         <v>60</v>
       </c>
-      <c r="C25" s="428"/>
-      <c r="D25" s="428"/>
-      <c r="E25" s="428"/>
-      <c r="F25" s="428"/>
-      <c r="G25" s="429"/>
+      <c r="C25" s="479"/>
+      <c r="D25" s="479"/>
+      <c r="E25" s="479"/>
+      <c r="F25" s="479"/>
+      <c r="G25" s="480"/>
       <c r="H25" s="55"/>
-      <c r="I25" s="526" t="b">
+      <c r="I25" s="513" t="b">
         <f>IF(K7=1,J20,IF(K7=2,1/(($J$15/100)/J20+($L$15/100)/L20),IF(K7=3,1/(($J$15/100)/J20+($L$15/100)/L20+(N15/100)/N20))))</f>
         <v>0</v>
       </c>
-      <c r="J25" s="527"/>
-      <c r="K25" s="527"/>
-      <c r="L25" s="527"/>
-      <c r="M25" s="527"/>
-      <c r="N25" s="528"/>
+      <c r="J25" s="514"/>
+      <c r="K25" s="514"/>
+      <c r="L25" s="514"/>
+      <c r="M25" s="514"/>
+      <c r="N25" s="515"/>
       <c r="O25" s="172"/>
       <c r="P25" s="163" t="s">
         <v>20</v>
@@ -11395,77 +11395,89 @@
         <v>#DIV/0!</v>
       </c>
     </row>
-    <row r="26" spans="1:17" ht="25.5" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="26" spans="1:17" ht="25.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A26" s="68"/>
-      <c r="B26" s="427" t="s">
+      <c r="B26" s="478" t="s">
         <v>61</v>
       </c>
-      <c r="C26" s="428"/>
-      <c r="D26" s="428"/>
-      <c r="E26" s="428"/>
-      <c r="F26" s="428"/>
-      <c r="G26" s="429"/>
+      <c r="C26" s="479"/>
+      <c r="D26" s="479"/>
+      <c r="E26" s="479"/>
+      <c r="F26" s="479"/>
+      <c r="G26" s="480"/>
       <c r="H26" s="55"/>
-      <c r="I26" s="526" t="b">
+      <c r="I26" s="513" t="b">
         <f>IF(K7=1,J21,IF(K7=2,1/(($J$15/100)/J21+($L$15/100)/L21),IF(K7=3,1/(($J$15/100)/J21+($L$15/100)/L21+(N15/100)/N21))))</f>
         <v>0</v>
       </c>
-      <c r="J26" s="527"/>
-      <c r="K26" s="527"/>
-      <c r="L26" s="527"/>
-      <c r="M26" s="527"/>
-      <c r="N26" s="528"/>
+      <c r="J26" s="514"/>
+      <c r="K26" s="514"/>
+      <c r="L26" s="514"/>
+      <c r="M26" s="514"/>
+      <c r="N26" s="515"/>
       <c r="O26" s="172"/>
     </row>
-    <row r="27" spans="1:17" ht="27.75" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="27" spans="1:17" ht="27.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A27" s="68"/>
-      <c r="B27" s="427" t="s">
+      <c r="B27" s="478" t="s">
         <v>62</v>
       </c>
-      <c r="C27" s="428"/>
-      <c r="D27" s="428"/>
-      <c r="E27" s="428"/>
-      <c r="F27" s="428"/>
-      <c r="G27" s="429"/>
+      <c r="C27" s="479"/>
+      <c r="D27" s="479"/>
+      <c r="E27" s="479"/>
+      <c r="F27" s="479"/>
+      <c r="G27" s="480"/>
       <c r="H27" s="55"/>
-      <c r="I27" s="526" t="b">
+      <c r="I27" s="513" t="b">
         <f>IF(K7=1,J22,IF(K7=2,1/(($J$15/100)/J22+($L$15/100)/L22),IF(K7=3,1/(($J$15/100)/J22+($L$15/100)/L22+(N15/100)/N22))))</f>
         <v>0</v>
       </c>
-      <c r="J27" s="527"/>
-      <c r="K27" s="527"/>
-      <c r="L27" s="527"/>
-      <c r="M27" s="527"/>
-      <c r="N27" s="528"/>
+      <c r="J27" s="514"/>
+      <c r="K27" s="514"/>
+      <c r="L27" s="514"/>
+      <c r="M27" s="514"/>
+      <c r="N27" s="515"/>
       <c r="O27" s="172"/>
     </row>
-    <row r="28" spans="1:17" ht="22.5" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="28" spans="1:17" ht="22.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A28" s="68"/>
-      <c r="B28" s="427" t="s">
+      <c r="B28" s="478" t="s">
         <v>63</v>
       </c>
-      <c r="C28" s="428"/>
-      <c r="D28" s="428"/>
-      <c r="E28" s="428"/>
-      <c r="F28" s="428"/>
-      <c r="G28" s="429"/>
+      <c r="C28" s="479"/>
+      <c r="D28" s="479"/>
+      <c r="E28" s="479"/>
+      <c r="F28" s="479"/>
+      <c r="G28" s="480"/>
       <c r="H28" s="56" t="s">
         <v>24</v>
       </c>
-      <c r="I28" s="523" t="b">
+      <c r="I28" s="510" t="b">
         <f>IF(K7=1,J23,IF(K7=2,1/(($J$15/100)/J23+($L$15/100)/L23),IF(K7=3,1/(($J$15/100)/J23+($L$15/100)/L23+(N15/100)/N23))))</f>
         <v>0</v>
       </c>
-      <c r="J28" s="524"/>
-      <c r="K28" s="524"/>
-      <c r="L28" s="524"/>
-      <c r="M28" s="524"/>
-      <c r="N28" s="525"/>
+      <c r="J28" s="511"/>
+      <c r="K28" s="511"/>
+      <c r="L28" s="511"/>
+      <c r="M28" s="511"/>
+      <c r="N28" s="512"/>
       <c r="O28" s="152"/>
     </row>
   </sheetData>
   <sheetProtection algorithmName="SHA-512" hashValue="W+ehWvk1+G4fxMwMlFFe24eUcB7dTRS6CSN4hdQEHiO/u8gs+lAQOb/9/FmIcet9iZVIOf5wG+i5LTmEs2xhcA==" saltValue="AwzUmQKx7HBfx5Grx49ElQ==" spinCount="100000" sheet="1" objects="1" scenarios="1"/>
   <mergeCells count="24">
+    <mergeCell ref="A1:N1"/>
+    <mergeCell ref="F15:G15"/>
+    <mergeCell ref="I13:N13"/>
+    <mergeCell ref="D9:E9"/>
+    <mergeCell ref="B9:C9"/>
+    <mergeCell ref="F9:G9"/>
+    <mergeCell ref="I11:J11"/>
+    <mergeCell ref="K11:L11"/>
+    <mergeCell ref="M11:N11"/>
+    <mergeCell ref="A11:G12"/>
+    <mergeCell ref="H11:H12"/>
+    <mergeCell ref="E7:F7"/>
     <mergeCell ref="B17:G17"/>
     <mergeCell ref="B18:G18"/>
     <mergeCell ref="K7:L7"/>
@@ -11478,18 +11490,6 @@
     <mergeCell ref="B25:G25"/>
     <mergeCell ref="B26:G26"/>
     <mergeCell ref="B27:G27"/>
-    <mergeCell ref="A1:N1"/>
-    <mergeCell ref="F15:G15"/>
-    <mergeCell ref="I13:N13"/>
-    <mergeCell ref="D9:E9"/>
-    <mergeCell ref="B9:C9"/>
-    <mergeCell ref="F9:G9"/>
-    <mergeCell ref="I11:J11"/>
-    <mergeCell ref="K11:L11"/>
-    <mergeCell ref="M11:N11"/>
-    <mergeCell ref="A11:G12"/>
-    <mergeCell ref="H11:H12"/>
-    <mergeCell ref="E7:F7"/>
   </mergeCells>
   <conditionalFormatting sqref="F9:G10 O9:O10">
     <cfRule type="containsText" dxfId="0" priority="2" operator="containsText" text="no">
@@ -11520,32 +11520,32 @@
 <file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{3AB8A787-28AE-4F29-9790-1AE86195FD78}">
   <dimension ref="A1:T92"/>
-  <sheetFormatPr baseColWidth="10" defaultColWidth="11.42578125" defaultRowHeight="12.75" x14ac:dyDescent="0.2"/>
+  <sheetFormatPr baseColWidth="10" defaultColWidth="11.44140625" defaultRowHeight="13.2" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="26" style="1" customWidth="1"/>
-    <col min="2" max="2" width="11.5703125" style="1" bestFit="1" customWidth="1"/>
-    <col min="3" max="3" width="12.5703125" style="1" customWidth="1"/>
-    <col min="4" max="4" width="10.140625" style="1" customWidth="1"/>
+    <col min="2" max="2" width="11.5546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="12.5546875" style="1" customWidth="1"/>
+    <col min="4" max="4" width="10.109375" style="1" customWidth="1"/>
     <col min="5" max="6" width="14" style="1" customWidth="1"/>
-    <col min="7" max="7" width="13.7109375" style="1" customWidth="1"/>
-    <col min="8" max="8" width="15.28515625" style="1" customWidth="1"/>
-    <col min="9" max="9" width="9.85546875" style="1" customWidth="1"/>
-    <col min="10" max="10" width="14.42578125" style="1" customWidth="1"/>
-    <col min="11" max="11" width="17.42578125" style="1" customWidth="1"/>
-    <col min="12" max="16384" width="11.42578125" style="1"/>
+    <col min="7" max="7" width="13.6640625" style="1" customWidth="1"/>
+    <col min="8" max="8" width="15.33203125" style="1" customWidth="1"/>
+    <col min="9" max="9" width="9.88671875" style="1" customWidth="1"/>
+    <col min="10" max="10" width="14.44140625" style="1" customWidth="1"/>
+    <col min="11" max="11" width="17.44140625" style="1" customWidth="1"/>
+    <col min="12" max="16384" width="11.44140625" style="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:13" ht="12.75" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A1" s="538"/>
-      <c r="B1" s="541" t="s">
+    <row r="1" spans="1:13" ht="12.75" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A1" s="530"/>
+      <c r="B1" s="533" t="s">
         <v>74</v>
       </c>
-      <c r="C1" s="542"/>
-      <c r="D1" s="542"/>
-      <c r="E1" s="542"/>
-      <c r="F1" s="542"/>
-      <c r="G1" s="542"/>
-      <c r="H1" s="543"/>
+      <c r="C1" s="534"/>
+      <c r="D1" s="534"/>
+      <c r="E1" s="534"/>
+      <c r="F1" s="534"/>
+      <c r="G1" s="534"/>
+      <c r="H1" s="535"/>
       <c r="I1" s="84" t="s">
         <v>75</v>
       </c>
@@ -11553,15 +11553,15 @@
         <v>76</v>
       </c>
     </row>
-    <row r="2" spans="1:13" ht="12.75" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A2" s="539"/>
-      <c r="B2" s="544"/>
-      <c r="C2" s="545"/>
-      <c r="D2" s="545"/>
-      <c r="E2" s="545"/>
-      <c r="F2" s="545"/>
-      <c r="G2" s="545"/>
-      <c r="H2" s="546"/>
+    <row r="2" spans="1:13" ht="12.75" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A2" s="531"/>
+      <c r="B2" s="536"/>
+      <c r="C2" s="537"/>
+      <c r="D2" s="537"/>
+      <c r="E2" s="537"/>
+      <c r="F2" s="537"/>
+      <c r="G2" s="537"/>
+      <c r="H2" s="538"/>
       <c r="I2" s="84" t="s">
         <v>77</v>
       </c>
@@ -11569,15 +11569,15 @@
         <v>3</v>
       </c>
     </row>
-    <row r="3" spans="1:13" ht="12.75" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A3" s="539"/>
-      <c r="B3" s="544"/>
-      <c r="C3" s="545"/>
-      <c r="D3" s="545"/>
-      <c r="E3" s="545"/>
-      <c r="F3" s="545"/>
-      <c r="G3" s="545"/>
-      <c r="H3" s="546"/>
+    <row r="3" spans="1:13" ht="12.75" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A3" s="531"/>
+      <c r="B3" s="536"/>
+      <c r="C3" s="537"/>
+      <c r="D3" s="537"/>
+      <c r="E3" s="537"/>
+      <c r="F3" s="537"/>
+      <c r="G3" s="537"/>
+      <c r="H3" s="538"/>
       <c r="I3" s="84" t="s">
         <v>78</v>
       </c>
@@ -11585,15 +11585,15 @@
         <v>46146</v>
       </c>
     </row>
-    <row r="4" spans="1:13" ht="12.75" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A4" s="540"/>
-      <c r="B4" s="547"/>
-      <c r="C4" s="548"/>
-      <c r="D4" s="548"/>
-      <c r="E4" s="548"/>
-      <c r="F4" s="548"/>
-      <c r="G4" s="548"/>
-      <c r="H4" s="549"/>
+    <row r="4" spans="1:13" ht="12.75" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A4" s="532"/>
+      <c r="B4" s="539"/>
+      <c r="C4" s="540"/>
+      <c r="D4" s="540"/>
+      <c r="E4" s="540"/>
+      <c r="F4" s="540"/>
+      <c r="G4" s="540"/>
+      <c r="H4" s="541"/>
       <c r="I4" s="84" t="s">
         <v>79</v>
       </c>
@@ -11601,7 +11601,7 @@
         <v>80</v>
       </c>
     </row>
-    <row r="6" spans="1:13" ht="21" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="6" spans="1:13" ht="21" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A6" s="237" t="s">
         <v>81</v>
       </c>
@@ -11618,7 +11618,7 @@
       <c r="I6" s="3"/>
       <c r="J6" s="2"/>
     </row>
-    <row r="7" spans="1:13" ht="21" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="7" spans="1:13" ht="21" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A7" s="237" t="s">
         <v>82</v>
       </c>
@@ -11634,7 +11634,7 @@
       <c r="I7" s="3"/>
       <c r="J7" s="2"/>
     </row>
-    <row r="8" spans="1:13" ht="21" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="8" spans="1:13" ht="21" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A8" s="237" t="s">
         <v>83</v>
       </c>
@@ -11650,7 +11650,7 @@
       <c r="I8" s="3"/>
       <c r="J8" s="2"/>
     </row>
-    <row r="9" spans="1:13" ht="21" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="9" spans="1:13" ht="21" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A9" s="240" t="s">
         <v>84</v>
       </c>
@@ -11666,12 +11666,12 @@
       <c r="I9" s="3"/>
       <c r="J9" s="2"/>
     </row>
-    <row r="11" spans="1:13" ht="12" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="11" spans="1:13" ht="12" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A11" s="1" t="s">
         <v>85</v>
       </c>
     </row>
-    <row r="12" spans="1:13" ht="12" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="12" spans="1:13" ht="12" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A12" s="1" t="s">
         <v>86</v>
       </c>
@@ -11679,7 +11679,7 @@
         <v>92</v>
       </c>
     </row>
-    <row r="13" spans="1:13" ht="12" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="13" spans="1:13" ht="12" customHeight="1" x14ac:dyDescent="0.25">
       <c r="F13" s="1" t="s">
         <v>160</v>
       </c>
@@ -11687,7 +11687,7 @@
       <c r="K13" s="109"/>
       <c r="M13" s="109"/>
     </row>
-    <row r="14" spans="1:13" ht="12" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="14" spans="1:13" ht="12" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A14" s="1" t="s">
         <v>90</v>
       </c>
@@ -11696,14 +11696,14 @@
       </c>
       <c r="G14" s="241"/>
     </row>
-    <row r="15" spans="1:13" ht="12" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="15" spans="1:13" ht="12" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A15" s="1" t="s">
         <v>158</v>
       </c>
       <c r="H15" s="241"/>
       <c r="K15" s="111"/>
     </row>
-    <row r="16" spans="1:13" ht="12" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="16" spans="1:13" ht="12" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A16" s="1" t="s">
         <v>159</v>
       </c>
@@ -11712,48 +11712,48 @@
       </c>
       <c r="M16" s="111"/>
     </row>
-    <row r="17" spans="1:13" ht="12" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A17" s="550"/>
-      <c r="B17" s="550"/>
-      <c r="C17" s="550"/>
-      <c r="D17" s="550"/>
-      <c r="E17" s="550"/>
-    </row>
-    <row r="18" spans="1:13" ht="12" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="17" spans="1:13" ht="12" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A17" s="542"/>
+      <c r="B17" s="542"/>
+      <c r="C17" s="542"/>
+      <c r="D17" s="542"/>
+      <c r="E17" s="542"/>
+    </row>
+    <row r="18" spans="1:13" ht="12" customHeight="1" x14ac:dyDescent="0.25">
       <c r="K18" s="111"/>
     </row>
-    <row r="19" spans="1:13" ht="12" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="19" spans="1:13" ht="12" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A19" s="1" t="s">
         <v>91</v>
       </c>
       <c r="M19" s="111"/>
     </row>
-    <row r="20" spans="1:13" ht="12" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="20" spans="1:13" ht="12" customHeight="1" x14ac:dyDescent="0.25">
       <c r="H20" s="241"/>
     </row>
-    <row r="21" spans="1:13" ht="12" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="22" spans="1:13" ht="12" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="23" spans="1:13" ht="12" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="24" spans="1:13" ht="12" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="25" spans="1:13" ht="12" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="26" spans="1:13" ht="12" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="27" spans="1:13" ht="12" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="28" spans="1:13" ht="12" customHeight="1" thickBot="1" x14ac:dyDescent="0.25"/>
-    <row r="29" spans="1:13" ht="18" customHeight="1" thickBot="1" x14ac:dyDescent="0.25">
-      <c r="A29" s="551" t="s">
+    <row r="21" spans="1:13" ht="12" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="22" spans="1:13" ht="12" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="23" spans="1:13" ht="12" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="24" spans="1:13" ht="12" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="25" spans="1:13" ht="12" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="26" spans="1:13" ht="12" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="27" spans="1:13" ht="12" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="28" spans="1:13" ht="12" customHeight="1" thickBot="1" x14ac:dyDescent="0.3"/>
+    <row r="29" spans="1:13" ht="18" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A29" s="543" t="s">
         <v>87</v>
       </c>
-      <c r="B29" s="552"/>
-      <c r="C29" s="552"/>
-      <c r="D29" s="552"/>
-      <c r="E29" s="552"/>
-      <c r="F29" s="552"/>
-      <c r="G29" s="552"/>
-      <c r="H29" s="553"/>
+      <c r="B29" s="544"/>
+      <c r="C29" s="544"/>
+      <c r="D29" s="544"/>
+      <c r="E29" s="544"/>
+      <c r="F29" s="544"/>
+      <c r="G29" s="544"/>
+      <c r="H29" s="545"/>
       <c r="I29" s="88"/>
       <c r="J29" s="88"/>
     </row>
-    <row r="30" spans="1:13" ht="36.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.25">
+    <row r="30" spans="1:13" ht="36.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A30" s="242" t="s">
         <v>94</v>
       </c>
@@ -11781,7 +11781,7 @@
       <c r="I30" s="88"/>
       <c r="J30" s="88"/>
     </row>
-    <row r="31" spans="1:13" ht="18" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="31" spans="1:13" ht="18" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A31" s="246" t="s">
         <v>100</v>
       </c>
@@ -12199,7 +12199,7 @@
       <c r="I42" s="88"/>
       <c r="J42" s="88"/>
     </row>
-    <row r="43" spans="1:15" s="89" customFormat="1" ht="18" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="43" spans="1:15" s="89" customFormat="1" ht="18" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A43" s="258" t="s">
         <v>108</v>
       </c>
@@ -12582,7 +12582,7 @@
       <c r="S55" s="88"/>
       <c r="T55" s="88"/>
     </row>
-    <row r="56" spans="1:20" ht="18" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="56" spans="1:20" ht="18" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A56" s="258" t="s">
         <v>104</v>
       </c>
@@ -12618,7 +12618,7 @@
       <c r="S56" s="88"/>
       <c r="T56" s="88"/>
     </row>
-    <row r="57" spans="1:20" ht="18" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="57" spans="1:20" ht="18" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A57" s="258" t="s">
         <v>108</v>
       </c>
@@ -12655,7 +12655,7 @@
       <c r="S57" s="88"/>
       <c r="T57" s="88"/>
     </row>
-    <row r="58" spans="1:20" ht="18" customHeight="1" thickBot="1" x14ac:dyDescent="0.25">
+    <row r="58" spans="1:20" ht="18" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A58" s="291" t="s">
         <v>114</v>
       </c>
@@ -12693,7 +12693,7 @@
       <c r="S58" s="88"/>
       <c r="T58" s="88"/>
     </row>
-    <row r="59" spans="1:20" ht="18" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="59" spans="1:20" ht="18" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A59" s="271"/>
       <c r="B59" s="272"/>
       <c r="C59" s="273" t="s">
@@ -12719,7 +12719,7 @@
       <c r="S59" s="88"/>
       <c r="T59" s="88"/>
     </row>
-    <row r="60" spans="1:20" ht="18" customHeight="1" thickBot="1" x14ac:dyDescent="0.25">
+    <row r="60" spans="1:20" ht="18" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A60" s="275"/>
       <c r="B60" s="276"/>
       <c r="C60" s="277" t="s">
@@ -12742,7 +12742,7 @@
       <c r="Q60" s="88"/>
       <c r="R60" s="88"/>
     </row>
-    <row r="61" spans="1:20" ht="17.25" customHeight="1" thickBot="1" x14ac:dyDescent="0.25">
+    <row r="61" spans="1:20" ht="17.25" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="K61" s="88"/>
       <c r="L61" s="88"/>
       <c r="M61" s="88"/>
@@ -12752,7 +12752,7 @@
       <c r="Q61" s="88"/>
       <c r="R61" s="88"/>
     </row>
-    <row r="62" spans="1:20" ht="18" customHeight="1" thickBot="1" x14ac:dyDescent="0.25">
+    <row r="62" spans="1:20" ht="18" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A62" s="279"/>
       <c r="B62" s="280"/>
       <c r="C62" s="280"/>
@@ -12772,7 +12772,7 @@
       <c r="Q62" s="88"/>
       <c r="R62" s="88"/>
     </row>
-    <row r="63" spans="1:20" ht="18" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="63" spans="1:20" ht="18" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A63" s="286" t="s">
         <v>116</v>
       </c>
@@ -12795,7 +12795,7 @@
       <c r="Q63" s="88"/>
       <c r="R63" s="88"/>
     </row>
-    <row r="64" spans="1:20" ht="25.5" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="64" spans="1:20" ht="25.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A64" s="251" t="str">
         <f>+DATOS!B17</f>
         <v>Masa de la muestra secada al horno constante</v>
@@ -12837,7 +12837,7 @@
       <c r="Q64" s="88"/>
       <c r="R64" s="88"/>
     </row>
-    <row r="65" spans="1:18" ht="18" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="65" spans="1:18" ht="18" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A65" s="258" t="s">
         <v>102</v>
       </c>
@@ -12872,7 +12872,7 @@
       <c r="Q65" s="88"/>
       <c r="R65" s="88"/>
     </row>
-    <row r="66" spans="1:18" ht="18" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="66" spans="1:18" ht="18" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A66" s="258" t="s">
         <v>104</v>
       </c>
@@ -12900,10 +12900,10 @@
       <c r="I66" s="88"/>
       <c r="J66" s="86"/>
       <c r="K66" s="226"/>
-      <c r="L66" s="537" t="s">
+      <c r="L66" s="529" t="s">
         <v>106</v>
       </c>
-      <c r="M66" s="537"/>
+      <c r="M66" s="529"/>
       <c r="N66" s="230" t="s">
         <v>95</v>
       </c>
@@ -12914,7 +12914,7 @@
       <c r="Q66" s="88"/>
       <c r="R66" s="88"/>
     </row>
-    <row r="67" spans="1:18" ht="18" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="67" spans="1:18" ht="18" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A67" s="258" t="s">
         <v>108</v>
       </c>
@@ -12959,7 +12959,7 @@
       <c r="Q67" s="88"/>
       <c r="R67" s="88"/>
     </row>
-    <row r="68" spans="1:18" ht="18" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="68" spans="1:18" ht="18" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A68" s="251" t="str">
         <f>+DATOS!B19</f>
         <v>Masa aparente de la muestra de prueba sumergida en agua</v>
@@ -13007,7 +13007,7 @@
       <c r="Q68" s="88"/>
       <c r="R68" s="88"/>
     </row>
-    <row r="69" spans="1:18" ht="18" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="69" spans="1:18" ht="18" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A69" s="258" t="s">
         <v>102</v>
       </c>
@@ -13052,7 +13052,7 @@
       <c r="Q69" s="88"/>
       <c r="R69" s="88"/>
     </row>
-    <row r="70" spans="1:18" ht="18" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="70" spans="1:18" ht="18" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A70" s="258" t="s">
         <v>104</v>
       </c>
@@ -13096,7 +13096,7 @@
       <c r="Q70" s="88"/>
       <c r="R70" s="88"/>
     </row>
-    <row r="71" spans="1:18" ht="18" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="71" spans="1:18" ht="18" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A71" s="258" t="s">
         <v>108</v>
       </c>
@@ -13126,7 +13126,7 @@
       <c r="Q71" s="88"/>
       <c r="R71" s="88"/>
     </row>
-    <row r="72" spans="1:18" ht="18" customHeight="1" thickBot="1" x14ac:dyDescent="0.25">
+    <row r="72" spans="1:18" ht="18" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A72" s="291" t="s">
         <v>117</v>
       </c>
@@ -13160,7 +13160,7 @@
       <c r="Q72" s="88"/>
       <c r="R72" s="88"/>
     </row>
-    <row r="73" spans="1:18" ht="18" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="73" spans="1:18" ht="18" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A73" s="271"/>
       <c r="B73" s="272"/>
       <c r="C73" s="273" t="s">
@@ -13182,7 +13182,7 @@
       <c r="Q73" s="88"/>
       <c r="R73" s="88"/>
     </row>
-    <row r="74" spans="1:18" ht="18" customHeight="1" thickBot="1" x14ac:dyDescent="0.25">
+    <row r="74" spans="1:18" ht="18" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A74" s="275"/>
       <c r="B74" s="276"/>
       <c r="C74" s="277" t="s">
@@ -13203,7 +13203,7 @@
       <c r="Q74" s="88"/>
       <c r="R74" s="88"/>
     </row>
-    <row r="75" spans="1:18" ht="18" customHeight="1" thickBot="1" x14ac:dyDescent="0.25">
+    <row r="75" spans="1:18" ht="18" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="K75" s="88"/>
       <c r="N75" s="88"/>
       <c r="O75" s="88"/>
@@ -13211,7 +13211,7 @@
       <c r="Q75" s="88"/>
       <c r="R75" s="88"/>
     </row>
-    <row r="76" spans="1:18" ht="18" customHeight="1" thickBot="1" x14ac:dyDescent="0.25">
+    <row r="76" spans="1:18" ht="18" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A76" s="279"/>
       <c r="B76" s="280"/>
       <c r="C76" s="280"/>
@@ -13229,7 +13229,7 @@
       <c r="Q76" s="88"/>
       <c r="R76" s="88"/>
     </row>
-    <row r="77" spans="1:18" ht="19.5" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="77" spans="1:18" ht="19.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A77" s="286" t="s">
         <v>120</v>
       </c>
@@ -13245,10 +13245,10 @@
       <c r="H77" s="92"/>
       <c r="J77" s="86"/>
       <c r="K77" s="226"/>
-      <c r="L77" s="537" t="s">
+      <c r="L77" s="529" t="s">
         <v>106</v>
       </c>
-      <c r="M77" s="537"/>
+      <c r="M77" s="529"/>
       <c r="N77" s="230" t="s">
         <v>95</v>
       </c>
@@ -13259,7 +13259,7 @@
       <c r="Q77" s="88"/>
       <c r="R77" s="88"/>
     </row>
-    <row r="78" spans="1:18" ht="23.25" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="78" spans="1:18" ht="23.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A78" s="251" t="str">
         <f>+DATOS!B17</f>
         <v>Masa de la muestra secada al horno constante</v>
@@ -13309,7 +13309,7 @@
       <c r="Q78" s="88"/>
       <c r="R78" s="88"/>
     </row>
-    <row r="79" spans="1:18" ht="19.5" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="79" spans="1:18" ht="19.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A79" s="258" t="s">
         <v>102</v>
       </c>
@@ -13352,7 +13352,7 @@
       <c r="Q79" s="88"/>
       <c r="R79" s="88"/>
     </row>
-    <row r="80" spans="1:18" ht="19.5" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="80" spans="1:18" ht="19.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A80" s="258" t="s">
         <v>104</v>
       </c>
@@ -13397,7 +13397,7 @@
       <c r="Q80" s="88"/>
       <c r="R80" s="88"/>
     </row>
-    <row r="81" spans="1:18" ht="19.5" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="81" spans="1:18" ht="19.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A81" s="258" t="s">
         <v>108</v>
       </c>
@@ -13441,7 +13441,7 @@
       <c r="Q81" s="88"/>
       <c r="R81" s="88"/>
     </row>
-    <row r="82" spans="1:18" ht="33.75" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="82" spans="1:18" ht="33.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A82" s="251" t="str">
         <f>+DATOS!B18</f>
         <v>Masa de la muestra de ensayo de superficie seca saturada en el aire</v>
@@ -13483,7 +13483,7 @@
       <c r="Q82" s="88"/>
       <c r="R82" s="88"/>
     </row>
-    <row r="83" spans="1:18" ht="19.5" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="83" spans="1:18" ht="19.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A83" s="258" t="s">
         <v>102</v>
       </c>
@@ -13517,7 +13517,7 @@
       <c r="Q83" s="88"/>
       <c r="R83" s="88"/>
     </row>
-    <row r="84" spans="1:18" ht="19.5" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="84" spans="1:18" ht="19.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A84" s="258" t="s">
         <v>104</v>
       </c>
@@ -13550,7 +13550,7 @@
       <c r="Q84" s="88"/>
       <c r="R84" s="88"/>
     </row>
-    <row r="85" spans="1:18" ht="19.5" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="85" spans="1:18" ht="19.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A85" s="258" t="s">
         <v>108</v>
       </c>
@@ -13583,7 +13583,7 @@
       <c r="Q85" s="88"/>
       <c r="R85" s="88"/>
     </row>
-    <row r="86" spans="1:18" ht="19.5" customHeight="1" thickBot="1" x14ac:dyDescent="0.25">
+    <row r="86" spans="1:18" ht="19.5" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A86" s="291" t="s">
         <v>121</v>
       </c>
@@ -13617,7 +13617,7 @@
       <c r="Q86" s="88"/>
       <c r="R86" s="88"/>
     </row>
-    <row r="87" spans="1:18" ht="19.5" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="87" spans="1:18" ht="19.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A87" s="271"/>
       <c r="B87" s="272"/>
       <c r="C87" s="273" t="s">
@@ -13638,7 +13638,7 @@
       <c r="Q87" s="88"/>
       <c r="R87" s="88"/>
     </row>
-    <row r="88" spans="1:18" ht="19.5" customHeight="1" thickBot="1" x14ac:dyDescent="0.25">
+    <row r="88" spans="1:18" ht="19.5" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A88" s="275"/>
       <c r="B88" s="276"/>
       <c r="C88" s="277" t="s">
@@ -13661,7 +13661,7 @@
       <c r="Q88" s="88"/>
       <c r="R88" s="88"/>
     </row>
-    <row r="89" spans="1:18" x14ac:dyDescent="0.2">
+    <row r="89" spans="1:18" x14ac:dyDescent="0.25">
       <c r="K89" s="88"/>
       <c r="N89" s="88"/>
       <c r="O89" s="88"/>
@@ -13669,23 +13669,23 @@
       <c r="Q89" s="88"/>
       <c r="R89" s="88"/>
     </row>
-    <row r="90" spans="1:18" x14ac:dyDescent="0.2">
+    <row r="90" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A90" s="408" t="s">
         <v>234</v>
       </c>
-      <c r="B90" s="529" t="s">
+      <c r="B90" s="546" t="s">
         <v>235</v>
       </c>
-      <c r="C90" s="530"/>
+      <c r="C90" s="547"/>
       <c r="D90" s="409"/>
-      <c r="E90" s="531" t="s">
+      <c r="E90" s="548" t="s">
         <v>236</v>
       </c>
-      <c r="F90" s="531"/>
-      <c r="G90" s="532" t="s">
+      <c r="F90" s="548"/>
+      <c r="G90" s="549" t="s">
         <v>237</v>
       </c>
-      <c r="H90" s="533"/>
+      <c r="H90" s="550"/>
       <c r="K90" s="88"/>
       <c r="L90" s="88"/>
       <c r="M90" s="88"/>
@@ -13695,7 +13695,7 @@
       <c r="Q90" s="88"/>
       <c r="R90" s="88"/>
     </row>
-    <row r="91" spans="1:18" x14ac:dyDescent="0.2">
+    <row r="91" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A91" s="410"/>
       <c r="B91" s="410"/>
       <c r="C91" s="410"/>
@@ -13713,39 +13713,39 @@
       <c r="Q91" s="88"/>
       <c r="R91" s="88"/>
     </row>
-    <row r="92" spans="1:18" x14ac:dyDescent="0.2">
+    <row r="92" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A92" s="411" t="s">
         <v>238</v>
       </c>
-      <c r="B92" s="534">
+      <c r="B92" s="551">
         <v>44869</v>
       </c>
-      <c r="C92" s="535"/>
+      <c r="C92" s="552"/>
       <c r="D92" s="410"/>
-      <c r="E92" s="536" t="s">
+      <c r="E92" s="553" t="s">
         <v>239</v>
       </c>
-      <c r="F92" s="536"/>
-      <c r="G92" s="534">
+      <c r="F92" s="553"/>
+      <c r="G92" s="551">
         <v>44870</v>
       </c>
-      <c r="H92" s="535"/>
+      <c r="H92" s="552"/>
     </row>
   </sheetData>
   <sheetProtection algorithmName="SHA-512" hashValue="ApM65snLNqIZn0ZN7aX3xHHMa6/iycxbeL9ALdcEGO55MpBWIBtgm+Peub74gkBLbwitrSv+916KjsZEcm4Fhg==" saltValue="UZmsMzzVlYp14ecn1jzsjQ==" spinCount="100000" sheet="1" objects="1" scenarios="1"/>
   <mergeCells count="12">
+    <mergeCell ref="B90:C90"/>
+    <mergeCell ref="E90:F90"/>
+    <mergeCell ref="G90:H90"/>
+    <mergeCell ref="B92:C92"/>
+    <mergeCell ref="E92:F92"/>
+    <mergeCell ref="G92:H92"/>
     <mergeCell ref="L66:M66"/>
     <mergeCell ref="L77:M77"/>
     <mergeCell ref="A1:A4"/>
     <mergeCell ref="B1:H4"/>
     <mergeCell ref="A17:E17"/>
     <mergeCell ref="A29:H29"/>
-    <mergeCell ref="B90:C90"/>
-    <mergeCell ref="E90:F90"/>
-    <mergeCell ref="G90:H90"/>
-    <mergeCell ref="B92:C92"/>
-    <mergeCell ref="E92:F92"/>
-    <mergeCell ref="G92:H92"/>
   </mergeCells>
   <pageMargins left="0.70866141732283472" right="0.31496062992125984" top="0.74803149606299213" bottom="0.55118110236220474" header="0.31496062992125984" footer="0.31496062992125984"/>
   <pageSetup paperSize="9" scale="70" orientation="portrait" r:id="rId1"/>
@@ -13756,26 +13756,26 @@
 <file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0200-000000000000}">
   <dimension ref="B6:I27"/>
-  <sheetFormatPr baseColWidth="10" defaultColWidth="11.42578125" defaultRowHeight="12.75" x14ac:dyDescent="0.2"/>
+  <sheetFormatPr baseColWidth="10" defaultColWidth="11.44140625" defaultRowHeight="13.2" x14ac:dyDescent="0.25"/>
   <cols>
-    <col min="1" max="1" width="5.28515625" style="1" customWidth="1"/>
-    <col min="2" max="2" width="11.42578125" style="1"/>
+    <col min="1" max="1" width="5.33203125" style="1" customWidth="1"/>
+    <col min="2" max="2" width="11.44140625" style="1"/>
     <col min="3" max="4" width="12" style="1" customWidth="1"/>
-    <col min="5" max="7" width="11.42578125" style="1"/>
-    <col min="8" max="8" width="14.42578125" style="1" customWidth="1"/>
-    <col min="9" max="9" width="11.42578125" style="1"/>
-    <col min="10" max="10" width="11.85546875" style="1" customWidth="1"/>
-    <col min="11" max="16384" width="11.42578125" style="1"/>
+    <col min="5" max="7" width="11.44140625" style="1"/>
+    <col min="8" max="8" width="14.44140625" style="1" customWidth="1"/>
+    <col min="9" max="9" width="11.44140625" style="1"/>
+    <col min="10" max="10" width="11.88671875" style="1" customWidth="1"/>
+    <col min="11" max="16384" width="11.44140625" style="1"/>
   </cols>
   <sheetData>
-    <row r="6" spans="2:8" x14ac:dyDescent="0.2">
+    <row r="6" spans="2:8" x14ac:dyDescent="0.25">
       <c r="B6" s="98" t="s">
         <v>64</v>
       </c>
       <c r="C6" s="99"/>
       <c r="D6" s="99"/>
     </row>
-    <row r="7" spans="2:8" x14ac:dyDescent="0.2">
+    <row r="7" spans="2:8" x14ac:dyDescent="0.25">
       <c r="B7" s="78" t="s">
         <v>65</v>
       </c>
@@ -13784,7 +13784,7 @@
       </c>
       <c r="D7" s="101"/>
     </row>
-    <row r="8" spans="2:8" x14ac:dyDescent="0.2">
+    <row r="8" spans="2:8" x14ac:dyDescent="0.25">
       <c r="B8" s="77" t="s">
         <v>66</v>
       </c>
@@ -13795,7 +13795,7 @@
         <v>1.09E-9</v>
       </c>
     </row>
-    <row r="9" spans="2:8" x14ac:dyDescent="0.2">
+    <row r="9" spans="2:8" x14ac:dyDescent="0.25">
       <c r="B9" s="77" t="s">
         <v>67</v>
       </c>
@@ -13804,7 +13804,7 @@
       </c>
       <c r="D9" s="101"/>
     </row>
-    <row r="10" spans="2:8" x14ac:dyDescent="0.2">
+    <row r="10" spans="2:8" x14ac:dyDescent="0.25">
       <c r="B10" s="77" t="s">
         <v>68</v>
       </c>
@@ -13815,7 +13815,7 @@
         <v>44</v>
       </c>
     </row>
-    <row r="11" spans="2:8" x14ac:dyDescent="0.2">
+    <row r="11" spans="2:8" x14ac:dyDescent="0.25">
       <c r="B11" s="77" t="s">
         <v>69</v>
       </c>
@@ -13824,7 +13824,7 @@
       </c>
       <c r="D11" s="101"/>
     </row>
-    <row r="12" spans="2:8" x14ac:dyDescent="0.2">
+    <row r="12" spans="2:8" x14ac:dyDescent="0.25">
       <c r="B12" s="77" t="s">
         <v>178</v>
       </c>
@@ -13833,7 +13833,7 @@
         <v>46132</v>
       </c>
     </row>
-    <row r="13" spans="2:8" ht="16.5" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="13" spans="2:8" ht="16.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B13" s="195" t="s">
         <v>70</v>
       </c>
@@ -13856,7 +13856,7 @@
         <v>15000</v>
       </c>
     </row>
-    <row r="14" spans="2:8" ht="16.5" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="14" spans="2:8" ht="16.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B14" s="317"/>
       <c r="C14" s="312"/>
       <c r="D14" s="314"/>
@@ -13865,11 +13865,11 @@
       <c r="G14" s="314"/>
       <c r="H14" s="314"/>
     </row>
-    <row r="15" spans="2:8" x14ac:dyDescent="0.2">
+    <row r="15" spans="2:8" x14ac:dyDescent="0.25">
       <c r="B15" s="394"/>
       <c r="C15" s="395"/>
     </row>
-    <row r="16" spans="2:8" x14ac:dyDescent="0.2">
+    <row r="16" spans="2:8" x14ac:dyDescent="0.25">
       <c r="B16" s="80"/>
       <c r="C16" s="79" t="s">
         <v>72</v>
@@ -13890,12 +13890,12 @@
         <v>0</v>
       </c>
     </row>
-    <row r="18" spans="2:9" x14ac:dyDescent="0.2">
+    <row r="18" spans="2:9" x14ac:dyDescent="0.25">
       <c r="D18" s="109" t="s">
         <v>73</v>
       </c>
     </row>
-    <row r="20" spans="2:9" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="20" spans="2:9" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="D20" s="81">
         <f>+D13</f>
         <v>500</v>
@@ -13917,7 +13917,7 @@
         <v>15000</v>
       </c>
     </row>
-    <row r="21" spans="2:9" x14ac:dyDescent="0.2">
+    <row r="21" spans="2:9" x14ac:dyDescent="0.25">
       <c r="D21" s="82">
         <f>D16</f>
         <v>0</v>
@@ -13939,12 +13939,12 @@
         <v>0</v>
       </c>
     </row>
-    <row r="22" spans="2:9" x14ac:dyDescent="0.2">
+    <row r="22" spans="2:9" x14ac:dyDescent="0.25">
       <c r="G22" s="83"/>
       <c r="H22" s="83"/>
       <c r="I22" s="83"/>
     </row>
-    <row r="23" spans="2:9" ht="23.25" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="23" spans="2:9" ht="23.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B23" s="555" t="str">
         <f>+DATOS!B17</f>
         <v>Masa de la muestra secada al horno constante</v>
@@ -13964,7 +13964,7 @@
         <v>45</v>
       </c>
     </row>
-    <row r="24" spans="2:9" ht="23.25" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="24" spans="2:9" ht="23.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B24" s="554" t="str">
         <f>+DATOS!B18</f>
         <v>Masa de la muestra de ensayo de superficie seca saturada en el aire</v>
@@ -13984,7 +13984,7 @@
         <v>47</v>
       </c>
     </row>
-    <row r="25" spans="2:9" ht="23.25" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="25" spans="2:9" ht="23.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B25" s="556" t="str">
         <f>+DATOS!B19</f>
         <v>Masa aparente de la muestra de prueba sumergida en agua</v>
@@ -14004,13 +14004,13 @@
         <v>49</v>
       </c>
     </row>
-    <row r="26" spans="2:9" x14ac:dyDescent="0.2">
+    <row r="26" spans="2:9" x14ac:dyDescent="0.25">
       <c r="E26" s="95"/>
       <c r="F26" s="95"/>
       <c r="G26" s="95"/>
       <c r="H26" s="95"/>
     </row>
-    <row r="27" spans="2:9" x14ac:dyDescent="0.2">
+    <row r="27" spans="2:9" x14ac:dyDescent="0.25">
       <c r="D27" s="94"/>
     </row>
   </sheetData>
@@ -14028,1157 +14028,1157 @@
 <file path=xl/worksheets/sheet6.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0400-000000000000}">
   <dimension ref="A1:Y16"/>
-  <sheetFormatPr baseColWidth="10" defaultColWidth="11.42578125" defaultRowHeight="11.25" x14ac:dyDescent="0.2"/>
+  <sheetFormatPr baseColWidth="10" defaultColWidth="11.44140625" defaultRowHeight="10.199999999999999" x14ac:dyDescent="0.2"/>
   <cols>
     <col min="1" max="1" width="25" style="124" customWidth="1"/>
-    <col min="2" max="2" width="9.28515625" style="124" customWidth="1"/>
-    <col min="3" max="4" width="7.5703125" style="124" customWidth="1"/>
+    <col min="2" max="2" width="9.33203125" style="124" customWidth="1"/>
+    <col min="3" max="4" width="7.5546875" style="124" customWidth="1"/>
     <col min="5" max="5" width="2" style="124" customWidth="1"/>
-    <col min="6" max="6" width="22.7109375" style="124" customWidth="1"/>
-    <col min="7" max="9" width="6.7109375" style="124" customWidth="1"/>
+    <col min="6" max="6" width="22.6640625" style="124" customWidth="1"/>
+    <col min="7" max="9" width="6.6640625" style="124" customWidth="1"/>
     <col min="10" max="10" width="3" style="124" customWidth="1"/>
-    <col min="11" max="11" width="20.42578125" style="124" customWidth="1"/>
-    <col min="12" max="14" width="6.7109375" style="124" customWidth="1"/>
-    <col min="15" max="15" width="2.140625" style="124" customWidth="1"/>
-    <col min="16" max="16" width="21.7109375" style="124" customWidth="1"/>
-    <col min="17" max="19" width="5.7109375" style="124" customWidth="1"/>
+    <col min="11" max="11" width="20.44140625" style="124" customWidth="1"/>
+    <col min="12" max="14" width="6.6640625" style="124" customWidth="1"/>
+    <col min="15" max="15" width="2.109375" style="124" customWidth="1"/>
+    <col min="16" max="16" width="21.6640625" style="124" customWidth="1"/>
+    <col min="17" max="19" width="5.6640625" style="124" customWidth="1"/>
     <col min="20" max="20" width="5" style="124" customWidth="1"/>
-    <col min="21" max="21" width="16.5703125" style="124" customWidth="1"/>
-    <col min="22" max="250" width="11.42578125" style="124"/>
+    <col min="21" max="21" width="16.5546875" style="124" customWidth="1"/>
+    <col min="22" max="250" width="11.44140625" style="124"/>
     <col min="251" max="252" width="20" style="124" customWidth="1"/>
-    <col min="253" max="253" width="11.42578125" style="124"/>
-    <col min="254" max="255" width="6.140625" style="124" customWidth="1"/>
+    <col min="253" max="253" width="11.44140625" style="124"/>
+    <col min="254" max="255" width="6.109375" style="124" customWidth="1"/>
     <col min="256" max="256" width="14" style="124" customWidth="1"/>
-    <col min="257" max="257" width="4.42578125" style="124" customWidth="1"/>
-    <col min="258" max="258" width="20.85546875" style="124" customWidth="1"/>
-    <col min="259" max="260" width="11.42578125" style="124"/>
-    <col min="261" max="262" width="4.140625" style="124" customWidth="1"/>
-    <col min="263" max="263" width="11.42578125" style="124"/>
-    <col min="264" max="264" width="19.140625" style="124" customWidth="1"/>
-    <col min="265" max="266" width="11.42578125" style="124"/>
-    <col min="267" max="268" width="4.85546875" style="124" customWidth="1"/>
-    <col min="269" max="269" width="10.85546875" style="124" customWidth="1"/>
-    <col min="270" max="270" width="11.42578125" style="124"/>
+    <col min="257" max="257" width="4.44140625" style="124" customWidth="1"/>
+    <col min="258" max="258" width="20.88671875" style="124" customWidth="1"/>
+    <col min="259" max="260" width="11.44140625" style="124"/>
+    <col min="261" max="262" width="4.109375" style="124" customWidth="1"/>
+    <col min="263" max="263" width="11.44140625" style="124"/>
+    <col min="264" max="264" width="19.109375" style="124" customWidth="1"/>
+    <col min="265" max="266" width="11.44140625" style="124"/>
+    <col min="267" max="268" width="4.88671875" style="124" customWidth="1"/>
+    <col min="269" max="269" width="10.88671875" style="124" customWidth="1"/>
+    <col min="270" max="270" width="11.44140625" style="124"/>
     <col min="271" max="271" width="22" style="124" customWidth="1"/>
-    <col min="272" max="273" width="11.42578125" style="124"/>
+    <col min="272" max="273" width="11.44140625" style="124"/>
     <col min="274" max="275" width="6" style="124" customWidth="1"/>
-    <col min="276" max="506" width="11.42578125" style="124"/>
+    <col min="276" max="506" width="11.44140625" style="124"/>
     <col min="507" max="508" width="20" style="124" customWidth="1"/>
-    <col min="509" max="509" width="11.42578125" style="124"/>
-    <col min="510" max="511" width="6.140625" style="124" customWidth="1"/>
+    <col min="509" max="509" width="11.44140625" style="124"/>
+    <col min="510" max="511" width="6.109375" style="124" customWidth="1"/>
     <col min="512" max="512" width="14" style="124" customWidth="1"/>
-    <col min="513" max="513" width="4.42578125" style="124" customWidth="1"/>
-    <col min="514" max="514" width="20.85546875" style="124" customWidth="1"/>
-    <col min="515" max="516" width="11.42578125" style="124"/>
-    <col min="517" max="518" width="4.140625" style="124" customWidth="1"/>
-    <col min="519" max="519" width="11.42578125" style="124"/>
-    <col min="520" max="520" width="19.140625" style="124" customWidth="1"/>
-    <col min="521" max="522" width="11.42578125" style="124"/>
-    <col min="523" max="524" width="4.85546875" style="124" customWidth="1"/>
-    <col min="525" max="525" width="10.85546875" style="124" customWidth="1"/>
-    <col min="526" max="526" width="11.42578125" style="124"/>
+    <col min="513" max="513" width="4.44140625" style="124" customWidth="1"/>
+    <col min="514" max="514" width="20.88671875" style="124" customWidth="1"/>
+    <col min="515" max="516" width="11.44140625" style="124"/>
+    <col min="517" max="518" width="4.109375" style="124" customWidth="1"/>
+    <col min="519" max="519" width="11.44140625" style="124"/>
+    <col min="520" max="520" width="19.109375" style="124" customWidth="1"/>
+    <col min="521" max="522" width="11.44140625" style="124"/>
+    <col min="523" max="524" width="4.88671875" style="124" customWidth="1"/>
+    <col min="525" max="525" width="10.88671875" style="124" customWidth="1"/>
+    <col min="526" max="526" width="11.44140625" style="124"/>
     <col min="527" max="527" width="22" style="124" customWidth="1"/>
-    <col min="528" max="529" width="11.42578125" style="124"/>
+    <col min="528" max="529" width="11.44140625" style="124"/>
     <col min="530" max="531" width="6" style="124" customWidth="1"/>
-    <col min="532" max="762" width="11.42578125" style="124"/>
+    <col min="532" max="762" width="11.44140625" style="124"/>
     <col min="763" max="764" width="20" style="124" customWidth="1"/>
-    <col min="765" max="765" width="11.42578125" style="124"/>
-    <col min="766" max="767" width="6.140625" style="124" customWidth="1"/>
+    <col min="765" max="765" width="11.44140625" style="124"/>
+    <col min="766" max="767" width="6.109375" style="124" customWidth="1"/>
     <col min="768" max="768" width="14" style="124" customWidth="1"/>
-    <col min="769" max="769" width="4.42578125" style="124" customWidth="1"/>
-    <col min="770" max="770" width="20.85546875" style="124" customWidth="1"/>
-    <col min="771" max="772" width="11.42578125" style="124"/>
-    <col min="773" max="774" width="4.140625" style="124" customWidth="1"/>
-    <col min="775" max="775" width="11.42578125" style="124"/>
-    <col min="776" max="776" width="19.140625" style="124" customWidth="1"/>
-    <col min="777" max="778" width="11.42578125" style="124"/>
-    <col min="779" max="780" width="4.85546875" style="124" customWidth="1"/>
-    <col min="781" max="781" width="10.85546875" style="124" customWidth="1"/>
-    <col min="782" max="782" width="11.42578125" style="124"/>
+    <col min="769" max="769" width="4.44140625" style="124" customWidth="1"/>
+    <col min="770" max="770" width="20.88671875" style="124" customWidth="1"/>
+    <col min="771" max="772" width="11.44140625" style="124"/>
+    <col min="773" max="774" width="4.109375" style="124" customWidth="1"/>
+    <col min="775" max="775" width="11.44140625" style="124"/>
+    <col min="776" max="776" width="19.109375" style="124" customWidth="1"/>
+    <col min="777" max="778" width="11.44140625" style="124"/>
+    <col min="779" max="780" width="4.88671875" style="124" customWidth="1"/>
+    <col min="781" max="781" width="10.88671875" style="124" customWidth="1"/>
+    <col min="782" max="782" width="11.44140625" style="124"/>
     <col min="783" max="783" width="22" style="124" customWidth="1"/>
-    <col min="784" max="785" width="11.42578125" style="124"/>
+    <col min="784" max="785" width="11.44140625" style="124"/>
     <col min="786" max="787" width="6" style="124" customWidth="1"/>
-    <col min="788" max="1018" width="11.42578125" style="124"/>
+    <col min="788" max="1018" width="11.44140625" style="124"/>
     <col min="1019" max="1020" width="20" style="124" customWidth="1"/>
-    <col min="1021" max="1021" width="11.42578125" style="124"/>
-    <col min="1022" max="1023" width="6.140625" style="124" customWidth="1"/>
+    <col min="1021" max="1021" width="11.44140625" style="124"/>
+    <col min="1022" max="1023" width="6.109375" style="124" customWidth="1"/>
     <col min="1024" max="1024" width="14" style="124" customWidth="1"/>
-    <col min="1025" max="1025" width="4.42578125" style="124" customWidth="1"/>
-    <col min="1026" max="1026" width="20.85546875" style="124" customWidth="1"/>
-    <col min="1027" max="1028" width="11.42578125" style="124"/>
-    <col min="1029" max="1030" width="4.140625" style="124" customWidth="1"/>
-    <col min="1031" max="1031" width="11.42578125" style="124"/>
-    <col min="1032" max="1032" width="19.140625" style="124" customWidth="1"/>
-    <col min="1033" max="1034" width="11.42578125" style="124"/>
-    <col min="1035" max="1036" width="4.85546875" style="124" customWidth="1"/>
-    <col min="1037" max="1037" width="10.85546875" style="124" customWidth="1"/>
-    <col min="1038" max="1038" width="11.42578125" style="124"/>
+    <col min="1025" max="1025" width="4.44140625" style="124" customWidth="1"/>
+    <col min="1026" max="1026" width="20.88671875" style="124" customWidth="1"/>
+    <col min="1027" max="1028" width="11.44140625" style="124"/>
+    <col min="1029" max="1030" width="4.109375" style="124" customWidth="1"/>
+    <col min="1031" max="1031" width="11.44140625" style="124"/>
+    <col min="1032" max="1032" width="19.109375" style="124" customWidth="1"/>
+    <col min="1033" max="1034" width="11.44140625" style="124"/>
+    <col min="1035" max="1036" width="4.88671875" style="124" customWidth="1"/>
+    <col min="1037" max="1037" width="10.88671875" style="124" customWidth="1"/>
+    <col min="1038" max="1038" width="11.44140625" style="124"/>
     <col min="1039" max="1039" width="22" style="124" customWidth="1"/>
-    <col min="1040" max="1041" width="11.42578125" style="124"/>
+    <col min="1040" max="1041" width="11.44140625" style="124"/>
     <col min="1042" max="1043" width="6" style="124" customWidth="1"/>
-    <col min="1044" max="1274" width="11.42578125" style="124"/>
+    <col min="1044" max="1274" width="11.44140625" style="124"/>
     <col min="1275" max="1276" width="20" style="124" customWidth="1"/>
-    <col min="1277" max="1277" width="11.42578125" style="124"/>
-    <col min="1278" max="1279" width="6.140625" style="124" customWidth="1"/>
+    <col min="1277" max="1277" width="11.44140625" style="124"/>
+    <col min="1278" max="1279" width="6.109375" style="124" customWidth="1"/>
     <col min="1280" max="1280" width="14" style="124" customWidth="1"/>
-    <col min="1281" max="1281" width="4.42578125" style="124" customWidth="1"/>
-    <col min="1282" max="1282" width="20.85546875" style="124" customWidth="1"/>
-    <col min="1283" max="1284" width="11.42578125" style="124"/>
-    <col min="1285" max="1286" width="4.140625" style="124" customWidth="1"/>
-    <col min="1287" max="1287" width="11.42578125" style="124"/>
-    <col min="1288" max="1288" width="19.140625" style="124" customWidth="1"/>
-    <col min="1289" max="1290" width="11.42578125" style="124"/>
-    <col min="1291" max="1292" width="4.85546875" style="124" customWidth="1"/>
-    <col min="1293" max="1293" width="10.85546875" style="124" customWidth="1"/>
-    <col min="1294" max="1294" width="11.42578125" style="124"/>
+    <col min="1281" max="1281" width="4.44140625" style="124" customWidth="1"/>
+    <col min="1282" max="1282" width="20.88671875" style="124" customWidth="1"/>
+    <col min="1283" max="1284" width="11.44140625" style="124"/>
+    <col min="1285" max="1286" width="4.109375" style="124" customWidth="1"/>
+    <col min="1287" max="1287" width="11.44140625" style="124"/>
+    <col min="1288" max="1288" width="19.109375" style="124" customWidth="1"/>
+    <col min="1289" max="1290" width="11.44140625" style="124"/>
+    <col min="1291" max="1292" width="4.88671875" style="124" customWidth="1"/>
+    <col min="1293" max="1293" width="10.88671875" style="124" customWidth="1"/>
+    <col min="1294" max="1294" width="11.44140625" style="124"/>
     <col min="1295" max="1295" width="22" style="124" customWidth="1"/>
-    <col min="1296" max="1297" width="11.42578125" style="124"/>
+    <col min="1296" max="1297" width="11.44140625" style="124"/>
     <col min="1298" max="1299" width="6" style="124" customWidth="1"/>
-    <col min="1300" max="1530" width="11.42578125" style="124"/>
+    <col min="1300" max="1530" width="11.44140625" style="124"/>
     <col min="1531" max="1532" width="20" style="124" customWidth="1"/>
-    <col min="1533" max="1533" width="11.42578125" style="124"/>
-    <col min="1534" max="1535" width="6.140625" style="124" customWidth="1"/>
+    <col min="1533" max="1533" width="11.44140625" style="124"/>
+    <col min="1534" max="1535" width="6.109375" style="124" customWidth="1"/>
     <col min="1536" max="1536" width="14" style="124" customWidth="1"/>
-    <col min="1537" max="1537" width="4.42578125" style="124" customWidth="1"/>
-    <col min="1538" max="1538" width="20.85546875" style="124" customWidth="1"/>
-    <col min="1539" max="1540" width="11.42578125" style="124"/>
-    <col min="1541" max="1542" width="4.140625" style="124" customWidth="1"/>
-    <col min="1543" max="1543" width="11.42578125" style="124"/>
-    <col min="1544" max="1544" width="19.140625" style="124" customWidth="1"/>
-    <col min="1545" max="1546" width="11.42578125" style="124"/>
-    <col min="1547" max="1548" width="4.85546875" style="124" customWidth="1"/>
-    <col min="1549" max="1549" width="10.85546875" style="124" customWidth="1"/>
-    <col min="1550" max="1550" width="11.42578125" style="124"/>
+    <col min="1537" max="1537" width="4.44140625" style="124" customWidth="1"/>
+    <col min="1538" max="1538" width="20.88671875" style="124" customWidth="1"/>
+    <col min="1539" max="1540" width="11.44140625" style="124"/>
+    <col min="1541" max="1542" width="4.109375" style="124" customWidth="1"/>
+    <col min="1543" max="1543" width="11.44140625" style="124"/>
+    <col min="1544" max="1544" width="19.109375" style="124" customWidth="1"/>
+    <col min="1545" max="1546" width="11.44140625" style="124"/>
+    <col min="1547" max="1548" width="4.88671875" style="124" customWidth="1"/>
+    <col min="1549" max="1549" width="10.88671875" style="124" customWidth="1"/>
+    <col min="1550" max="1550" width="11.44140625" style="124"/>
     <col min="1551" max="1551" width="22" style="124" customWidth="1"/>
-    <col min="1552" max="1553" width="11.42578125" style="124"/>
+    <col min="1552" max="1553" width="11.44140625" style="124"/>
     <col min="1554" max="1555" width="6" style="124" customWidth="1"/>
-    <col min="1556" max="1786" width="11.42578125" style="124"/>
+    <col min="1556" max="1786" width="11.44140625" style="124"/>
     <col min="1787" max="1788" width="20" style="124" customWidth="1"/>
-    <col min="1789" max="1789" width="11.42578125" style="124"/>
-    <col min="1790" max="1791" width="6.140625" style="124" customWidth="1"/>
+    <col min="1789" max="1789" width="11.44140625" style="124"/>
+    <col min="1790" max="1791" width="6.109375" style="124" customWidth="1"/>
     <col min="1792" max="1792" width="14" style="124" customWidth="1"/>
-    <col min="1793" max="1793" width="4.42578125" style="124" customWidth="1"/>
-    <col min="1794" max="1794" width="20.85546875" style="124" customWidth="1"/>
-    <col min="1795" max="1796" width="11.42578125" style="124"/>
-    <col min="1797" max="1798" width="4.140625" style="124" customWidth="1"/>
-    <col min="1799" max="1799" width="11.42578125" style="124"/>
-    <col min="1800" max="1800" width="19.140625" style="124" customWidth="1"/>
-    <col min="1801" max="1802" width="11.42578125" style="124"/>
-    <col min="1803" max="1804" width="4.85546875" style="124" customWidth="1"/>
-    <col min="1805" max="1805" width="10.85546875" style="124" customWidth="1"/>
-    <col min="1806" max="1806" width="11.42578125" style="124"/>
+    <col min="1793" max="1793" width="4.44140625" style="124" customWidth="1"/>
+    <col min="1794" max="1794" width="20.88671875" style="124" customWidth="1"/>
+    <col min="1795" max="1796" width="11.44140625" style="124"/>
+    <col min="1797" max="1798" width="4.109375" style="124" customWidth="1"/>
+    <col min="1799" max="1799" width="11.44140625" style="124"/>
+    <col min="1800" max="1800" width="19.109375" style="124" customWidth="1"/>
+    <col min="1801" max="1802" width="11.44140625" style="124"/>
+    <col min="1803" max="1804" width="4.88671875" style="124" customWidth="1"/>
+    <col min="1805" max="1805" width="10.88671875" style="124" customWidth="1"/>
+    <col min="1806" max="1806" width="11.44140625" style="124"/>
     <col min="1807" max="1807" width="22" style="124" customWidth="1"/>
-    <col min="1808" max="1809" width="11.42578125" style="124"/>
+    <col min="1808" max="1809" width="11.44140625" style="124"/>
     <col min="1810" max="1811" width="6" style="124" customWidth="1"/>
-    <col min="1812" max="2042" width="11.42578125" style="124"/>
+    <col min="1812" max="2042" width="11.44140625" style="124"/>
     <col min="2043" max="2044" width="20" style="124" customWidth="1"/>
-    <col min="2045" max="2045" width="11.42578125" style="124"/>
-    <col min="2046" max="2047" width="6.140625" style="124" customWidth="1"/>
+    <col min="2045" max="2045" width="11.44140625" style="124"/>
+    <col min="2046" max="2047" width="6.109375" style="124" customWidth="1"/>
     <col min="2048" max="2048" width="14" style="124" customWidth="1"/>
-    <col min="2049" max="2049" width="4.42578125" style="124" customWidth="1"/>
-    <col min="2050" max="2050" width="20.85546875" style="124" customWidth="1"/>
-    <col min="2051" max="2052" width="11.42578125" style="124"/>
-    <col min="2053" max="2054" width="4.140625" style="124" customWidth="1"/>
-    <col min="2055" max="2055" width="11.42578125" style="124"/>
-    <col min="2056" max="2056" width="19.140625" style="124" customWidth="1"/>
-    <col min="2057" max="2058" width="11.42578125" style="124"/>
-    <col min="2059" max="2060" width="4.85546875" style="124" customWidth="1"/>
-    <col min="2061" max="2061" width="10.85546875" style="124" customWidth="1"/>
-    <col min="2062" max="2062" width="11.42578125" style="124"/>
+    <col min="2049" max="2049" width="4.44140625" style="124" customWidth="1"/>
+    <col min="2050" max="2050" width="20.88671875" style="124" customWidth="1"/>
+    <col min="2051" max="2052" width="11.44140625" style="124"/>
+    <col min="2053" max="2054" width="4.109375" style="124" customWidth="1"/>
+    <col min="2055" max="2055" width="11.44140625" style="124"/>
+    <col min="2056" max="2056" width="19.109375" style="124" customWidth="1"/>
+    <col min="2057" max="2058" width="11.44140625" style="124"/>
+    <col min="2059" max="2060" width="4.88671875" style="124" customWidth="1"/>
+    <col min="2061" max="2061" width="10.88671875" style="124" customWidth="1"/>
+    <col min="2062" max="2062" width="11.44140625" style="124"/>
     <col min="2063" max="2063" width="22" style="124" customWidth="1"/>
-    <col min="2064" max="2065" width="11.42578125" style="124"/>
+    <col min="2064" max="2065" width="11.44140625" style="124"/>
     <col min="2066" max="2067" width="6" style="124" customWidth="1"/>
-    <col min="2068" max="2298" width="11.42578125" style="124"/>
+    <col min="2068" max="2298" width="11.44140625" style="124"/>
     <col min="2299" max="2300" width="20" style="124" customWidth="1"/>
-    <col min="2301" max="2301" width="11.42578125" style="124"/>
-    <col min="2302" max="2303" width="6.140625" style="124" customWidth="1"/>
+    <col min="2301" max="2301" width="11.44140625" style="124"/>
+    <col min="2302" max="2303" width="6.109375" style="124" customWidth="1"/>
     <col min="2304" max="2304" width="14" style="124" customWidth="1"/>
-    <col min="2305" max="2305" width="4.42578125" style="124" customWidth="1"/>
-    <col min="2306" max="2306" width="20.85546875" style="124" customWidth="1"/>
-    <col min="2307" max="2308" width="11.42578125" style="124"/>
-    <col min="2309" max="2310" width="4.140625" style="124" customWidth="1"/>
-    <col min="2311" max="2311" width="11.42578125" style="124"/>
-    <col min="2312" max="2312" width="19.140625" style="124" customWidth="1"/>
-    <col min="2313" max="2314" width="11.42578125" style="124"/>
-    <col min="2315" max="2316" width="4.85546875" style="124" customWidth="1"/>
-    <col min="2317" max="2317" width="10.85546875" style="124" customWidth="1"/>
-    <col min="2318" max="2318" width="11.42578125" style="124"/>
+    <col min="2305" max="2305" width="4.44140625" style="124" customWidth="1"/>
+    <col min="2306" max="2306" width="20.88671875" style="124" customWidth="1"/>
+    <col min="2307" max="2308" width="11.44140625" style="124"/>
+    <col min="2309" max="2310" width="4.109375" style="124" customWidth="1"/>
+    <col min="2311" max="2311" width="11.44140625" style="124"/>
+    <col min="2312" max="2312" width="19.109375" style="124" customWidth="1"/>
+    <col min="2313" max="2314" width="11.44140625" style="124"/>
+    <col min="2315" max="2316" width="4.88671875" style="124" customWidth="1"/>
+    <col min="2317" max="2317" width="10.88671875" style="124" customWidth="1"/>
+    <col min="2318" max="2318" width="11.44140625" style="124"/>
     <col min="2319" max="2319" width="22" style="124" customWidth="1"/>
-    <col min="2320" max="2321" width="11.42578125" style="124"/>
+    <col min="2320" max="2321" width="11.44140625" style="124"/>
     <col min="2322" max="2323" width="6" style="124" customWidth="1"/>
-    <col min="2324" max="2554" width="11.42578125" style="124"/>
+    <col min="2324" max="2554" width="11.44140625" style="124"/>
     <col min="2555" max="2556" width="20" style="124" customWidth="1"/>
-    <col min="2557" max="2557" width="11.42578125" style="124"/>
-    <col min="2558" max="2559" width="6.140625" style="124" customWidth="1"/>
+    <col min="2557" max="2557" width="11.44140625" style="124"/>
+    <col min="2558" max="2559" width="6.109375" style="124" customWidth="1"/>
     <col min="2560" max="2560" width="14" style="124" customWidth="1"/>
-    <col min="2561" max="2561" width="4.42578125" style="124" customWidth="1"/>
-    <col min="2562" max="2562" width="20.85546875" style="124" customWidth="1"/>
-    <col min="2563" max="2564" width="11.42578125" style="124"/>
-    <col min="2565" max="2566" width="4.140625" style="124" customWidth="1"/>
-    <col min="2567" max="2567" width="11.42578125" style="124"/>
-    <col min="2568" max="2568" width="19.140625" style="124" customWidth="1"/>
-    <col min="2569" max="2570" width="11.42578125" style="124"/>
-    <col min="2571" max="2572" width="4.85546875" style="124" customWidth="1"/>
-    <col min="2573" max="2573" width="10.85546875" style="124" customWidth="1"/>
-    <col min="2574" max="2574" width="11.42578125" style="124"/>
+    <col min="2561" max="2561" width="4.44140625" style="124" customWidth="1"/>
+    <col min="2562" max="2562" width="20.88671875" style="124" customWidth="1"/>
+    <col min="2563" max="2564" width="11.44140625" style="124"/>
+    <col min="2565" max="2566" width="4.109375" style="124" customWidth="1"/>
+    <col min="2567" max="2567" width="11.44140625" style="124"/>
+    <col min="2568" max="2568" width="19.109375" style="124" customWidth="1"/>
+    <col min="2569" max="2570" width="11.44140625" style="124"/>
+    <col min="2571" max="2572" width="4.88671875" style="124" customWidth="1"/>
+    <col min="2573" max="2573" width="10.88671875" style="124" customWidth="1"/>
+    <col min="2574" max="2574" width="11.44140625" style="124"/>
     <col min="2575" max="2575" width="22" style="124" customWidth="1"/>
-    <col min="2576" max="2577" width="11.42578125" style="124"/>
+    <col min="2576" max="2577" width="11.44140625" style="124"/>
     <col min="2578" max="2579" width="6" style="124" customWidth="1"/>
-    <col min="2580" max="2810" width="11.42578125" style="124"/>
+    <col min="2580" max="2810" width="11.44140625" style="124"/>
     <col min="2811" max="2812" width="20" style="124" customWidth="1"/>
-    <col min="2813" max="2813" width="11.42578125" style="124"/>
-    <col min="2814" max="2815" width="6.140625" style="124" customWidth="1"/>
+    <col min="2813" max="2813" width="11.44140625" style="124"/>
+    <col min="2814" max="2815" width="6.109375" style="124" customWidth="1"/>
     <col min="2816" max="2816" width="14" style="124" customWidth="1"/>
-    <col min="2817" max="2817" width="4.42578125" style="124" customWidth="1"/>
-    <col min="2818" max="2818" width="20.85546875" style="124" customWidth="1"/>
-    <col min="2819" max="2820" width="11.42578125" style="124"/>
-    <col min="2821" max="2822" width="4.140625" style="124" customWidth="1"/>
-    <col min="2823" max="2823" width="11.42578125" style="124"/>
-    <col min="2824" max="2824" width="19.140625" style="124" customWidth="1"/>
-    <col min="2825" max="2826" width="11.42578125" style="124"/>
-    <col min="2827" max="2828" width="4.85546875" style="124" customWidth="1"/>
-    <col min="2829" max="2829" width="10.85546875" style="124" customWidth="1"/>
-    <col min="2830" max="2830" width="11.42578125" style="124"/>
+    <col min="2817" max="2817" width="4.44140625" style="124" customWidth="1"/>
+    <col min="2818" max="2818" width="20.88671875" style="124" customWidth="1"/>
+    <col min="2819" max="2820" width="11.44140625" style="124"/>
+    <col min="2821" max="2822" width="4.109375" style="124" customWidth="1"/>
+    <col min="2823" max="2823" width="11.44140625" style="124"/>
+    <col min="2824" max="2824" width="19.109375" style="124" customWidth="1"/>
+    <col min="2825" max="2826" width="11.44140625" style="124"/>
+    <col min="2827" max="2828" width="4.88671875" style="124" customWidth="1"/>
+    <col min="2829" max="2829" width="10.88671875" style="124" customWidth="1"/>
+    <col min="2830" max="2830" width="11.44140625" style="124"/>
     <col min="2831" max="2831" width="22" style="124" customWidth="1"/>
-    <col min="2832" max="2833" width="11.42578125" style="124"/>
+    <col min="2832" max="2833" width="11.44140625" style="124"/>
     <col min="2834" max="2835" width="6" style="124" customWidth="1"/>
-    <col min="2836" max="3066" width="11.42578125" style="124"/>
+    <col min="2836" max="3066" width="11.44140625" style="124"/>
     <col min="3067" max="3068" width="20" style="124" customWidth="1"/>
-    <col min="3069" max="3069" width="11.42578125" style="124"/>
-    <col min="3070" max="3071" width="6.140625" style="124" customWidth="1"/>
+    <col min="3069" max="3069" width="11.44140625" style="124"/>
+    <col min="3070" max="3071" width="6.109375" style="124" customWidth="1"/>
     <col min="3072" max="3072" width="14" style="124" customWidth="1"/>
-    <col min="3073" max="3073" width="4.42578125" style="124" customWidth="1"/>
-    <col min="3074" max="3074" width="20.85546875" style="124" customWidth="1"/>
-    <col min="3075" max="3076" width="11.42578125" style="124"/>
-    <col min="3077" max="3078" width="4.140625" style="124" customWidth="1"/>
-    <col min="3079" max="3079" width="11.42578125" style="124"/>
-    <col min="3080" max="3080" width="19.140625" style="124" customWidth="1"/>
-    <col min="3081" max="3082" width="11.42578125" style="124"/>
-    <col min="3083" max="3084" width="4.85546875" style="124" customWidth="1"/>
-    <col min="3085" max="3085" width="10.85546875" style="124" customWidth="1"/>
-    <col min="3086" max="3086" width="11.42578125" style="124"/>
+    <col min="3073" max="3073" width="4.44140625" style="124" customWidth="1"/>
+    <col min="3074" max="3074" width="20.88671875" style="124" customWidth="1"/>
+    <col min="3075" max="3076" width="11.44140625" style="124"/>
+    <col min="3077" max="3078" width="4.109375" style="124" customWidth="1"/>
+    <col min="3079" max="3079" width="11.44140625" style="124"/>
+    <col min="3080" max="3080" width="19.109375" style="124" customWidth="1"/>
+    <col min="3081" max="3082" width="11.44140625" style="124"/>
+    <col min="3083" max="3084" width="4.88671875" style="124" customWidth="1"/>
+    <col min="3085" max="3085" width="10.88671875" style="124" customWidth="1"/>
+    <col min="3086" max="3086" width="11.44140625" style="124"/>
     <col min="3087" max="3087" width="22" style="124" customWidth="1"/>
-    <col min="3088" max="3089" width="11.42578125" style="124"/>
+    <col min="3088" max="3089" width="11.44140625" style="124"/>
     <col min="3090" max="3091" width="6" style="124" customWidth="1"/>
-    <col min="3092" max="3322" width="11.42578125" style="124"/>
+    <col min="3092" max="3322" width="11.44140625" style="124"/>
     <col min="3323" max="3324" width="20" style="124" customWidth="1"/>
-    <col min="3325" max="3325" width="11.42578125" style="124"/>
-    <col min="3326" max="3327" width="6.140625" style="124" customWidth="1"/>
+    <col min="3325" max="3325" width="11.44140625" style="124"/>
+    <col min="3326" max="3327" width="6.109375" style="124" customWidth="1"/>
     <col min="3328" max="3328" width="14" style="124" customWidth="1"/>
-    <col min="3329" max="3329" width="4.42578125" style="124" customWidth="1"/>
-    <col min="3330" max="3330" width="20.85546875" style="124" customWidth="1"/>
-    <col min="3331" max="3332" width="11.42578125" style="124"/>
-    <col min="3333" max="3334" width="4.140625" style="124" customWidth="1"/>
-    <col min="3335" max="3335" width="11.42578125" style="124"/>
-    <col min="3336" max="3336" width="19.140625" style="124" customWidth="1"/>
-    <col min="3337" max="3338" width="11.42578125" style="124"/>
-    <col min="3339" max="3340" width="4.85546875" style="124" customWidth="1"/>
-    <col min="3341" max="3341" width="10.85546875" style="124" customWidth="1"/>
-    <col min="3342" max="3342" width="11.42578125" style="124"/>
+    <col min="3329" max="3329" width="4.44140625" style="124" customWidth="1"/>
+    <col min="3330" max="3330" width="20.88671875" style="124" customWidth="1"/>
+    <col min="3331" max="3332" width="11.44140625" style="124"/>
+    <col min="3333" max="3334" width="4.109375" style="124" customWidth="1"/>
+    <col min="3335" max="3335" width="11.44140625" style="124"/>
+    <col min="3336" max="3336" width="19.109375" style="124" customWidth="1"/>
+    <col min="3337" max="3338" width="11.44140625" style="124"/>
+    <col min="3339" max="3340" width="4.88671875" style="124" customWidth="1"/>
+    <col min="3341" max="3341" width="10.88671875" style="124" customWidth="1"/>
+    <col min="3342" max="3342" width="11.44140625" style="124"/>
     <col min="3343" max="3343" width="22" style="124" customWidth="1"/>
-    <col min="3344" max="3345" width="11.42578125" style="124"/>
+    <col min="3344" max="3345" width="11.44140625" style="124"/>
     <col min="3346" max="3347" width="6" style="124" customWidth="1"/>
-    <col min="3348" max="3578" width="11.42578125" style="124"/>
+    <col min="3348" max="3578" width="11.44140625" style="124"/>
     <col min="3579" max="3580" width="20" style="124" customWidth="1"/>
-    <col min="3581" max="3581" width="11.42578125" style="124"/>
-    <col min="3582" max="3583" width="6.140625" style="124" customWidth="1"/>
+    <col min="3581" max="3581" width="11.44140625" style="124"/>
+    <col min="3582" max="3583" width="6.109375" style="124" customWidth="1"/>
     <col min="3584" max="3584" width="14" style="124" customWidth="1"/>
-    <col min="3585" max="3585" width="4.42578125" style="124" customWidth="1"/>
-    <col min="3586" max="3586" width="20.85546875" style="124" customWidth="1"/>
-    <col min="3587" max="3588" width="11.42578125" style="124"/>
-    <col min="3589" max="3590" width="4.140625" style="124" customWidth="1"/>
-    <col min="3591" max="3591" width="11.42578125" style="124"/>
-    <col min="3592" max="3592" width="19.140625" style="124" customWidth="1"/>
-    <col min="3593" max="3594" width="11.42578125" style="124"/>
-    <col min="3595" max="3596" width="4.85546875" style="124" customWidth="1"/>
-    <col min="3597" max="3597" width="10.85546875" style="124" customWidth="1"/>
-    <col min="3598" max="3598" width="11.42578125" style="124"/>
+    <col min="3585" max="3585" width="4.44140625" style="124" customWidth="1"/>
+    <col min="3586" max="3586" width="20.88671875" style="124" customWidth="1"/>
+    <col min="3587" max="3588" width="11.44140625" style="124"/>
+    <col min="3589" max="3590" width="4.109375" style="124" customWidth="1"/>
+    <col min="3591" max="3591" width="11.44140625" style="124"/>
+    <col min="3592" max="3592" width="19.109375" style="124" customWidth="1"/>
+    <col min="3593" max="3594" width="11.44140625" style="124"/>
+    <col min="3595" max="3596" width="4.88671875" style="124" customWidth="1"/>
+    <col min="3597" max="3597" width="10.88671875" style="124" customWidth="1"/>
+    <col min="3598" max="3598" width="11.44140625" style="124"/>
     <col min="3599" max="3599" width="22" style="124" customWidth="1"/>
-    <col min="3600" max="3601" width="11.42578125" style="124"/>
+    <col min="3600" max="3601" width="11.44140625" style="124"/>
     <col min="3602" max="3603" width="6" style="124" customWidth="1"/>
-    <col min="3604" max="3834" width="11.42578125" style="124"/>
+    <col min="3604" max="3834" width="11.44140625" style="124"/>
     <col min="3835" max="3836" width="20" style="124" customWidth="1"/>
-    <col min="3837" max="3837" width="11.42578125" style="124"/>
-    <col min="3838" max="3839" width="6.140625" style="124" customWidth="1"/>
+    <col min="3837" max="3837" width="11.44140625" style="124"/>
+    <col min="3838" max="3839" width="6.109375" style="124" customWidth="1"/>
     <col min="3840" max="3840" width="14" style="124" customWidth="1"/>
-    <col min="3841" max="3841" width="4.42578125" style="124" customWidth="1"/>
-    <col min="3842" max="3842" width="20.85546875" style="124" customWidth="1"/>
-    <col min="3843" max="3844" width="11.42578125" style="124"/>
-    <col min="3845" max="3846" width="4.140625" style="124" customWidth="1"/>
-    <col min="3847" max="3847" width="11.42578125" style="124"/>
-    <col min="3848" max="3848" width="19.140625" style="124" customWidth="1"/>
-    <col min="3849" max="3850" width="11.42578125" style="124"/>
-    <col min="3851" max="3852" width="4.85546875" style="124" customWidth="1"/>
-    <col min="3853" max="3853" width="10.85546875" style="124" customWidth="1"/>
-    <col min="3854" max="3854" width="11.42578125" style="124"/>
+    <col min="3841" max="3841" width="4.44140625" style="124" customWidth="1"/>
+    <col min="3842" max="3842" width="20.88671875" style="124" customWidth="1"/>
+    <col min="3843" max="3844" width="11.44140625" style="124"/>
+    <col min="3845" max="3846" width="4.109375" style="124" customWidth="1"/>
+    <col min="3847" max="3847" width="11.44140625" style="124"/>
+    <col min="3848" max="3848" width="19.109375" style="124" customWidth="1"/>
+    <col min="3849" max="3850" width="11.44140625" style="124"/>
+    <col min="3851" max="3852" width="4.88671875" style="124" customWidth="1"/>
+    <col min="3853" max="3853" width="10.88671875" style="124" customWidth="1"/>
+    <col min="3854" max="3854" width="11.44140625" style="124"/>
     <col min="3855" max="3855" width="22" style="124" customWidth="1"/>
-    <col min="3856" max="3857" width="11.42578125" style="124"/>
+    <col min="3856" max="3857" width="11.44140625" style="124"/>
     <col min="3858" max="3859" width="6" style="124" customWidth="1"/>
-    <col min="3860" max="4090" width="11.42578125" style="124"/>
+    <col min="3860" max="4090" width="11.44140625" style="124"/>
     <col min="4091" max="4092" width="20" style="124" customWidth="1"/>
-    <col min="4093" max="4093" width="11.42578125" style="124"/>
-    <col min="4094" max="4095" width="6.140625" style="124" customWidth="1"/>
+    <col min="4093" max="4093" width="11.44140625" style="124"/>
+    <col min="4094" max="4095" width="6.109375" style="124" customWidth="1"/>
     <col min="4096" max="4096" width="14" style="124" customWidth="1"/>
-    <col min="4097" max="4097" width="4.42578125" style="124" customWidth="1"/>
-    <col min="4098" max="4098" width="20.85546875" style="124" customWidth="1"/>
-    <col min="4099" max="4100" width="11.42578125" style="124"/>
-    <col min="4101" max="4102" width="4.140625" style="124" customWidth="1"/>
-    <col min="4103" max="4103" width="11.42578125" style="124"/>
-    <col min="4104" max="4104" width="19.140625" style="124" customWidth="1"/>
-    <col min="4105" max="4106" width="11.42578125" style="124"/>
-    <col min="4107" max="4108" width="4.85546875" style="124" customWidth="1"/>
-    <col min="4109" max="4109" width="10.85546875" style="124" customWidth="1"/>
-    <col min="4110" max="4110" width="11.42578125" style="124"/>
+    <col min="4097" max="4097" width="4.44140625" style="124" customWidth="1"/>
+    <col min="4098" max="4098" width="20.88671875" style="124" customWidth="1"/>
+    <col min="4099" max="4100" width="11.44140625" style="124"/>
+    <col min="4101" max="4102" width="4.109375" style="124" customWidth="1"/>
+    <col min="4103" max="4103" width="11.44140625" style="124"/>
+    <col min="4104" max="4104" width="19.109375" style="124" customWidth="1"/>
+    <col min="4105" max="4106" width="11.44140625" style="124"/>
+    <col min="4107" max="4108" width="4.88671875" style="124" customWidth="1"/>
+    <col min="4109" max="4109" width="10.88671875" style="124" customWidth="1"/>
+    <col min="4110" max="4110" width="11.44140625" style="124"/>
     <col min="4111" max="4111" width="22" style="124" customWidth="1"/>
-    <col min="4112" max="4113" width="11.42578125" style="124"/>
+    <col min="4112" max="4113" width="11.44140625" style="124"/>
     <col min="4114" max="4115" width="6" style="124" customWidth="1"/>
-    <col min="4116" max="4346" width="11.42578125" style="124"/>
+    <col min="4116" max="4346" width="11.44140625" style="124"/>
     <col min="4347" max="4348" width="20" style="124" customWidth="1"/>
-    <col min="4349" max="4349" width="11.42578125" style="124"/>
-    <col min="4350" max="4351" width="6.140625" style="124" customWidth="1"/>
+    <col min="4349" max="4349" width="11.44140625" style="124"/>
+    <col min="4350" max="4351" width="6.109375" style="124" customWidth="1"/>
     <col min="4352" max="4352" width="14" style="124" customWidth="1"/>
-    <col min="4353" max="4353" width="4.42578125" style="124" customWidth="1"/>
-    <col min="4354" max="4354" width="20.85546875" style="124" customWidth="1"/>
-    <col min="4355" max="4356" width="11.42578125" style="124"/>
-    <col min="4357" max="4358" width="4.140625" style="124" customWidth="1"/>
-    <col min="4359" max="4359" width="11.42578125" style="124"/>
-    <col min="4360" max="4360" width="19.140625" style="124" customWidth="1"/>
-    <col min="4361" max="4362" width="11.42578125" style="124"/>
-    <col min="4363" max="4364" width="4.85546875" style="124" customWidth="1"/>
-    <col min="4365" max="4365" width="10.85546875" style="124" customWidth="1"/>
-    <col min="4366" max="4366" width="11.42578125" style="124"/>
+    <col min="4353" max="4353" width="4.44140625" style="124" customWidth="1"/>
+    <col min="4354" max="4354" width="20.88671875" style="124" customWidth="1"/>
+    <col min="4355" max="4356" width="11.44140625" style="124"/>
+    <col min="4357" max="4358" width="4.109375" style="124" customWidth="1"/>
+    <col min="4359" max="4359" width="11.44140625" style="124"/>
+    <col min="4360" max="4360" width="19.109375" style="124" customWidth="1"/>
+    <col min="4361" max="4362" width="11.44140625" style="124"/>
+    <col min="4363" max="4364" width="4.88671875" style="124" customWidth="1"/>
+    <col min="4365" max="4365" width="10.88671875" style="124" customWidth="1"/>
+    <col min="4366" max="4366" width="11.44140625" style="124"/>
     <col min="4367" max="4367" width="22" style="124" customWidth="1"/>
-    <col min="4368" max="4369" width="11.42578125" style="124"/>
+    <col min="4368" max="4369" width="11.44140625" style="124"/>
     <col min="4370" max="4371" width="6" style="124" customWidth="1"/>
-    <col min="4372" max="4602" width="11.42578125" style="124"/>
+    <col min="4372" max="4602" width="11.44140625" style="124"/>
     <col min="4603" max="4604" width="20" style="124" customWidth="1"/>
-    <col min="4605" max="4605" width="11.42578125" style="124"/>
-    <col min="4606" max="4607" width="6.140625" style="124" customWidth="1"/>
+    <col min="4605" max="4605" width="11.44140625" style="124"/>
+    <col min="4606" max="4607" width="6.109375" style="124" customWidth="1"/>
     <col min="4608" max="4608" width="14" style="124" customWidth="1"/>
-    <col min="4609" max="4609" width="4.42578125" style="124" customWidth="1"/>
-    <col min="4610" max="4610" width="20.85546875" style="124" customWidth="1"/>
-    <col min="4611" max="4612" width="11.42578125" style="124"/>
-    <col min="4613" max="4614" width="4.140625" style="124" customWidth="1"/>
-    <col min="4615" max="4615" width="11.42578125" style="124"/>
-    <col min="4616" max="4616" width="19.140625" style="124" customWidth="1"/>
-    <col min="4617" max="4618" width="11.42578125" style="124"/>
-    <col min="4619" max="4620" width="4.85546875" style="124" customWidth="1"/>
-    <col min="4621" max="4621" width="10.85546875" style="124" customWidth="1"/>
-    <col min="4622" max="4622" width="11.42578125" style="124"/>
+    <col min="4609" max="4609" width="4.44140625" style="124" customWidth="1"/>
+    <col min="4610" max="4610" width="20.88671875" style="124" customWidth="1"/>
+    <col min="4611" max="4612" width="11.44140625" style="124"/>
+    <col min="4613" max="4614" width="4.109375" style="124" customWidth="1"/>
+    <col min="4615" max="4615" width="11.44140625" style="124"/>
+    <col min="4616" max="4616" width="19.109375" style="124" customWidth="1"/>
+    <col min="4617" max="4618" width="11.44140625" style="124"/>
+    <col min="4619" max="4620" width="4.88671875" style="124" customWidth="1"/>
+    <col min="4621" max="4621" width="10.88671875" style="124" customWidth="1"/>
+    <col min="4622" max="4622" width="11.44140625" style="124"/>
     <col min="4623" max="4623" width="22" style="124" customWidth="1"/>
-    <col min="4624" max="4625" width="11.42578125" style="124"/>
+    <col min="4624" max="4625" width="11.44140625" style="124"/>
     <col min="4626" max="4627" width="6" style="124" customWidth="1"/>
-    <col min="4628" max="4858" width="11.42578125" style="124"/>
+    <col min="4628" max="4858" width="11.44140625" style="124"/>
     <col min="4859" max="4860" width="20" style="124" customWidth="1"/>
-    <col min="4861" max="4861" width="11.42578125" style="124"/>
-    <col min="4862" max="4863" width="6.140625" style="124" customWidth="1"/>
+    <col min="4861" max="4861" width="11.44140625" style="124"/>
+    <col min="4862" max="4863" width="6.109375" style="124" customWidth="1"/>
     <col min="4864" max="4864" width="14" style="124" customWidth="1"/>
-    <col min="4865" max="4865" width="4.42578125" style="124" customWidth="1"/>
-    <col min="4866" max="4866" width="20.85546875" style="124" customWidth="1"/>
-    <col min="4867" max="4868" width="11.42578125" style="124"/>
-    <col min="4869" max="4870" width="4.140625" style="124" customWidth="1"/>
-    <col min="4871" max="4871" width="11.42578125" style="124"/>
-    <col min="4872" max="4872" width="19.140625" style="124" customWidth="1"/>
-    <col min="4873" max="4874" width="11.42578125" style="124"/>
-    <col min="4875" max="4876" width="4.85546875" style="124" customWidth="1"/>
-    <col min="4877" max="4877" width="10.85546875" style="124" customWidth="1"/>
-    <col min="4878" max="4878" width="11.42578125" style="124"/>
+    <col min="4865" max="4865" width="4.44140625" style="124" customWidth="1"/>
+    <col min="4866" max="4866" width="20.88671875" style="124" customWidth="1"/>
+    <col min="4867" max="4868" width="11.44140625" style="124"/>
+    <col min="4869" max="4870" width="4.109375" style="124" customWidth="1"/>
+    <col min="4871" max="4871" width="11.44140625" style="124"/>
+    <col min="4872" max="4872" width="19.109375" style="124" customWidth="1"/>
+    <col min="4873" max="4874" width="11.44140625" style="124"/>
+    <col min="4875" max="4876" width="4.88671875" style="124" customWidth="1"/>
+    <col min="4877" max="4877" width="10.88671875" style="124" customWidth="1"/>
+    <col min="4878" max="4878" width="11.44140625" style="124"/>
     <col min="4879" max="4879" width="22" style="124" customWidth="1"/>
-    <col min="4880" max="4881" width="11.42578125" style="124"/>
+    <col min="4880" max="4881" width="11.44140625" style="124"/>
     <col min="4882" max="4883" width="6" style="124" customWidth="1"/>
-    <col min="4884" max="5114" width="11.42578125" style="124"/>
+    <col min="4884" max="5114" width="11.44140625" style="124"/>
     <col min="5115" max="5116" width="20" style="124" customWidth="1"/>
-    <col min="5117" max="5117" width="11.42578125" style="124"/>
-    <col min="5118" max="5119" width="6.140625" style="124" customWidth="1"/>
+    <col min="5117" max="5117" width="11.44140625" style="124"/>
+    <col min="5118" max="5119" width="6.109375" style="124" customWidth="1"/>
     <col min="5120" max="5120" width="14" style="124" customWidth="1"/>
-    <col min="5121" max="5121" width="4.42578125" style="124" customWidth="1"/>
-    <col min="5122" max="5122" width="20.85546875" style="124" customWidth="1"/>
-    <col min="5123" max="5124" width="11.42578125" style="124"/>
-    <col min="5125" max="5126" width="4.140625" style="124" customWidth="1"/>
-    <col min="5127" max="5127" width="11.42578125" style="124"/>
-    <col min="5128" max="5128" width="19.140625" style="124" customWidth="1"/>
-    <col min="5129" max="5130" width="11.42578125" style="124"/>
-    <col min="5131" max="5132" width="4.85546875" style="124" customWidth="1"/>
-    <col min="5133" max="5133" width="10.85546875" style="124" customWidth="1"/>
-    <col min="5134" max="5134" width="11.42578125" style="124"/>
+    <col min="5121" max="5121" width="4.44140625" style="124" customWidth="1"/>
+    <col min="5122" max="5122" width="20.88671875" style="124" customWidth="1"/>
+    <col min="5123" max="5124" width="11.44140625" style="124"/>
+    <col min="5125" max="5126" width="4.109375" style="124" customWidth="1"/>
+    <col min="5127" max="5127" width="11.44140625" style="124"/>
+    <col min="5128" max="5128" width="19.109375" style="124" customWidth="1"/>
+    <col min="5129" max="5130" width="11.44140625" style="124"/>
+    <col min="5131" max="5132" width="4.88671875" style="124" customWidth="1"/>
+    <col min="5133" max="5133" width="10.88671875" style="124" customWidth="1"/>
+    <col min="5134" max="5134" width="11.44140625" style="124"/>
     <col min="5135" max="5135" width="22" style="124" customWidth="1"/>
-    <col min="5136" max="5137" width="11.42578125" style="124"/>
+    <col min="5136" max="5137" width="11.44140625" style="124"/>
     <col min="5138" max="5139" width="6" style="124" customWidth="1"/>
-    <col min="5140" max="5370" width="11.42578125" style="124"/>
+    <col min="5140" max="5370" width="11.44140625" style="124"/>
     <col min="5371" max="5372" width="20" style="124" customWidth="1"/>
-    <col min="5373" max="5373" width="11.42578125" style="124"/>
-    <col min="5374" max="5375" width="6.140625" style="124" customWidth="1"/>
+    <col min="5373" max="5373" width="11.44140625" style="124"/>
+    <col min="5374" max="5375" width="6.109375" style="124" customWidth="1"/>
     <col min="5376" max="5376" width="14" style="124" customWidth="1"/>
-    <col min="5377" max="5377" width="4.42578125" style="124" customWidth="1"/>
-    <col min="5378" max="5378" width="20.85546875" style="124" customWidth="1"/>
-    <col min="5379" max="5380" width="11.42578125" style="124"/>
-    <col min="5381" max="5382" width="4.140625" style="124" customWidth="1"/>
-    <col min="5383" max="5383" width="11.42578125" style="124"/>
-    <col min="5384" max="5384" width="19.140625" style="124" customWidth="1"/>
-    <col min="5385" max="5386" width="11.42578125" style="124"/>
-    <col min="5387" max="5388" width="4.85546875" style="124" customWidth="1"/>
-    <col min="5389" max="5389" width="10.85546875" style="124" customWidth="1"/>
-    <col min="5390" max="5390" width="11.42578125" style="124"/>
+    <col min="5377" max="5377" width="4.44140625" style="124" customWidth="1"/>
+    <col min="5378" max="5378" width="20.88671875" style="124" customWidth="1"/>
+    <col min="5379" max="5380" width="11.44140625" style="124"/>
+    <col min="5381" max="5382" width="4.109375" style="124" customWidth="1"/>
+    <col min="5383" max="5383" width="11.44140625" style="124"/>
+    <col min="5384" max="5384" width="19.109375" style="124" customWidth="1"/>
+    <col min="5385" max="5386" width="11.44140625" style="124"/>
+    <col min="5387" max="5388" width="4.88671875" style="124" customWidth="1"/>
+    <col min="5389" max="5389" width="10.88671875" style="124" customWidth="1"/>
+    <col min="5390" max="5390" width="11.44140625" style="124"/>
     <col min="5391" max="5391" width="22" style="124" customWidth="1"/>
-    <col min="5392" max="5393" width="11.42578125" style="124"/>
+    <col min="5392" max="5393" width="11.44140625" style="124"/>
     <col min="5394" max="5395" width="6" style="124" customWidth="1"/>
-    <col min="5396" max="5626" width="11.42578125" style="124"/>
+    <col min="5396" max="5626" width="11.44140625" style="124"/>
     <col min="5627" max="5628" width="20" style="124" customWidth="1"/>
-    <col min="5629" max="5629" width="11.42578125" style="124"/>
-    <col min="5630" max="5631" width="6.140625" style="124" customWidth="1"/>
+    <col min="5629" max="5629" width="11.44140625" style="124"/>
+    <col min="5630" max="5631" width="6.109375" style="124" customWidth="1"/>
     <col min="5632" max="5632" width="14" style="124" customWidth="1"/>
-    <col min="5633" max="5633" width="4.42578125" style="124" customWidth="1"/>
-    <col min="5634" max="5634" width="20.85546875" style="124" customWidth="1"/>
-    <col min="5635" max="5636" width="11.42578125" style="124"/>
-    <col min="5637" max="5638" width="4.140625" style="124" customWidth="1"/>
-    <col min="5639" max="5639" width="11.42578125" style="124"/>
-    <col min="5640" max="5640" width="19.140625" style="124" customWidth="1"/>
-    <col min="5641" max="5642" width="11.42578125" style="124"/>
-    <col min="5643" max="5644" width="4.85546875" style="124" customWidth="1"/>
-    <col min="5645" max="5645" width="10.85546875" style="124" customWidth="1"/>
-    <col min="5646" max="5646" width="11.42578125" style="124"/>
+    <col min="5633" max="5633" width="4.44140625" style="124" customWidth="1"/>
+    <col min="5634" max="5634" width="20.88671875" style="124" customWidth="1"/>
+    <col min="5635" max="5636" width="11.44140625" style="124"/>
+    <col min="5637" max="5638" width="4.109375" style="124" customWidth="1"/>
+    <col min="5639" max="5639" width="11.44140625" style="124"/>
+    <col min="5640" max="5640" width="19.109375" style="124" customWidth="1"/>
+    <col min="5641" max="5642" width="11.44140625" style="124"/>
+    <col min="5643" max="5644" width="4.88671875" style="124" customWidth="1"/>
+    <col min="5645" max="5645" width="10.88671875" style="124" customWidth="1"/>
+    <col min="5646" max="5646" width="11.44140625" style="124"/>
     <col min="5647" max="5647" width="22" style="124" customWidth="1"/>
-    <col min="5648" max="5649" width="11.42578125" style="124"/>
+    <col min="5648" max="5649" width="11.44140625" style="124"/>
     <col min="5650" max="5651" width="6" style="124" customWidth="1"/>
-    <col min="5652" max="5882" width="11.42578125" style="124"/>
+    <col min="5652" max="5882" width="11.44140625" style="124"/>
     <col min="5883" max="5884" width="20" style="124" customWidth="1"/>
-    <col min="5885" max="5885" width="11.42578125" style="124"/>
-    <col min="5886" max="5887" width="6.140625" style="124" customWidth="1"/>
+    <col min="5885" max="5885" width="11.44140625" style="124"/>
+    <col min="5886" max="5887" width="6.109375" style="124" customWidth="1"/>
     <col min="5888" max="5888" width="14" style="124" customWidth="1"/>
-    <col min="5889" max="5889" width="4.42578125" style="124" customWidth="1"/>
-    <col min="5890" max="5890" width="20.85546875" style="124" customWidth="1"/>
-    <col min="5891" max="5892" width="11.42578125" style="124"/>
-    <col min="5893" max="5894" width="4.140625" style="124" customWidth="1"/>
-    <col min="5895" max="5895" width="11.42578125" style="124"/>
-    <col min="5896" max="5896" width="19.140625" style="124" customWidth="1"/>
-    <col min="5897" max="5898" width="11.42578125" style="124"/>
-    <col min="5899" max="5900" width="4.85546875" style="124" customWidth="1"/>
-    <col min="5901" max="5901" width="10.85546875" style="124" customWidth="1"/>
-    <col min="5902" max="5902" width="11.42578125" style="124"/>
+    <col min="5889" max="5889" width="4.44140625" style="124" customWidth="1"/>
+    <col min="5890" max="5890" width="20.88671875" style="124" customWidth="1"/>
+    <col min="5891" max="5892" width="11.44140625" style="124"/>
+    <col min="5893" max="5894" width="4.109375" style="124" customWidth="1"/>
+    <col min="5895" max="5895" width="11.44140625" style="124"/>
+    <col min="5896" max="5896" width="19.109375" style="124" customWidth="1"/>
+    <col min="5897" max="5898" width="11.44140625" style="124"/>
+    <col min="5899" max="5900" width="4.88671875" style="124" customWidth="1"/>
+    <col min="5901" max="5901" width="10.88671875" style="124" customWidth="1"/>
+    <col min="5902" max="5902" width="11.44140625" style="124"/>
     <col min="5903" max="5903" width="22" style="124" customWidth="1"/>
-    <col min="5904" max="5905" width="11.42578125" style="124"/>
+    <col min="5904" max="5905" width="11.44140625" style="124"/>
     <col min="5906" max="5907" width="6" style="124" customWidth="1"/>
-    <col min="5908" max="6138" width="11.42578125" style="124"/>
+    <col min="5908" max="6138" width="11.44140625" style="124"/>
     <col min="6139" max="6140" width="20" style="124" customWidth="1"/>
-    <col min="6141" max="6141" width="11.42578125" style="124"/>
-    <col min="6142" max="6143" width="6.140625" style="124" customWidth="1"/>
+    <col min="6141" max="6141" width="11.44140625" style="124"/>
+    <col min="6142" max="6143" width="6.109375" style="124" customWidth="1"/>
     <col min="6144" max="6144" width="14" style="124" customWidth="1"/>
-    <col min="6145" max="6145" width="4.42578125" style="124" customWidth="1"/>
-    <col min="6146" max="6146" width="20.85546875" style="124" customWidth="1"/>
-    <col min="6147" max="6148" width="11.42578125" style="124"/>
-    <col min="6149" max="6150" width="4.140625" style="124" customWidth="1"/>
-    <col min="6151" max="6151" width="11.42578125" style="124"/>
-    <col min="6152" max="6152" width="19.140625" style="124" customWidth="1"/>
-    <col min="6153" max="6154" width="11.42578125" style="124"/>
-    <col min="6155" max="6156" width="4.85546875" style="124" customWidth="1"/>
-    <col min="6157" max="6157" width="10.85546875" style="124" customWidth="1"/>
-    <col min="6158" max="6158" width="11.42578125" style="124"/>
+    <col min="6145" max="6145" width="4.44140625" style="124" customWidth="1"/>
+    <col min="6146" max="6146" width="20.88671875" style="124" customWidth="1"/>
+    <col min="6147" max="6148" width="11.44140625" style="124"/>
+    <col min="6149" max="6150" width="4.109375" style="124" customWidth="1"/>
+    <col min="6151" max="6151" width="11.44140625" style="124"/>
+    <col min="6152" max="6152" width="19.109375" style="124" customWidth="1"/>
+    <col min="6153" max="6154" width="11.44140625" style="124"/>
+    <col min="6155" max="6156" width="4.88671875" style="124" customWidth="1"/>
+    <col min="6157" max="6157" width="10.88671875" style="124" customWidth="1"/>
+    <col min="6158" max="6158" width="11.44140625" style="124"/>
     <col min="6159" max="6159" width="22" style="124" customWidth="1"/>
-    <col min="6160" max="6161" width="11.42578125" style="124"/>
+    <col min="6160" max="6161" width="11.44140625" style="124"/>
     <col min="6162" max="6163" width="6" style="124" customWidth="1"/>
-    <col min="6164" max="6394" width="11.42578125" style="124"/>
+    <col min="6164" max="6394" width="11.44140625" style="124"/>
     <col min="6395" max="6396" width="20" style="124" customWidth="1"/>
-    <col min="6397" max="6397" width="11.42578125" style="124"/>
-    <col min="6398" max="6399" width="6.140625" style="124" customWidth="1"/>
+    <col min="6397" max="6397" width="11.44140625" style="124"/>
+    <col min="6398" max="6399" width="6.109375" style="124" customWidth="1"/>
     <col min="6400" max="6400" width="14" style="124" customWidth="1"/>
-    <col min="6401" max="6401" width="4.42578125" style="124" customWidth="1"/>
-    <col min="6402" max="6402" width="20.85546875" style="124" customWidth="1"/>
-    <col min="6403" max="6404" width="11.42578125" style="124"/>
-    <col min="6405" max="6406" width="4.140625" style="124" customWidth="1"/>
-    <col min="6407" max="6407" width="11.42578125" style="124"/>
-    <col min="6408" max="6408" width="19.140625" style="124" customWidth="1"/>
-    <col min="6409" max="6410" width="11.42578125" style="124"/>
-    <col min="6411" max="6412" width="4.85546875" style="124" customWidth="1"/>
-    <col min="6413" max="6413" width="10.85546875" style="124" customWidth="1"/>
-    <col min="6414" max="6414" width="11.42578125" style="124"/>
+    <col min="6401" max="6401" width="4.44140625" style="124" customWidth="1"/>
+    <col min="6402" max="6402" width="20.88671875" style="124" customWidth="1"/>
+    <col min="6403" max="6404" width="11.44140625" style="124"/>
+    <col min="6405" max="6406" width="4.109375" style="124" customWidth="1"/>
+    <col min="6407" max="6407" width="11.44140625" style="124"/>
+    <col min="6408" max="6408" width="19.109375" style="124" customWidth="1"/>
+    <col min="6409" max="6410" width="11.44140625" style="124"/>
+    <col min="6411" max="6412" width="4.88671875" style="124" customWidth="1"/>
+    <col min="6413" max="6413" width="10.88671875" style="124" customWidth="1"/>
+    <col min="6414" max="6414" width="11.44140625" style="124"/>
     <col min="6415" max="6415" width="22" style="124" customWidth="1"/>
-    <col min="6416" max="6417" width="11.42578125" style="124"/>
+    <col min="6416" max="6417" width="11.44140625" style="124"/>
     <col min="6418" max="6419" width="6" style="124" customWidth="1"/>
-    <col min="6420" max="6650" width="11.42578125" style="124"/>
+    <col min="6420" max="6650" width="11.44140625" style="124"/>
     <col min="6651" max="6652" width="20" style="124" customWidth="1"/>
-    <col min="6653" max="6653" width="11.42578125" style="124"/>
-    <col min="6654" max="6655" width="6.140625" style="124" customWidth="1"/>
+    <col min="6653" max="6653" width="11.44140625" style="124"/>
+    <col min="6654" max="6655" width="6.109375" style="124" customWidth="1"/>
     <col min="6656" max="6656" width="14" style="124" customWidth="1"/>
-    <col min="6657" max="6657" width="4.42578125" style="124" customWidth="1"/>
-    <col min="6658" max="6658" width="20.85546875" style="124" customWidth="1"/>
-    <col min="6659" max="6660" width="11.42578125" style="124"/>
-    <col min="6661" max="6662" width="4.140625" style="124" customWidth="1"/>
-    <col min="6663" max="6663" width="11.42578125" style="124"/>
-    <col min="6664" max="6664" width="19.140625" style="124" customWidth="1"/>
-    <col min="6665" max="6666" width="11.42578125" style="124"/>
-    <col min="6667" max="6668" width="4.85546875" style="124" customWidth="1"/>
-    <col min="6669" max="6669" width="10.85546875" style="124" customWidth="1"/>
-    <col min="6670" max="6670" width="11.42578125" style="124"/>
+    <col min="6657" max="6657" width="4.44140625" style="124" customWidth="1"/>
+    <col min="6658" max="6658" width="20.88671875" style="124" customWidth="1"/>
+    <col min="6659" max="6660" width="11.44140625" style="124"/>
+    <col min="6661" max="6662" width="4.109375" style="124" customWidth="1"/>
+    <col min="6663" max="6663" width="11.44140625" style="124"/>
+    <col min="6664" max="6664" width="19.109375" style="124" customWidth="1"/>
+    <col min="6665" max="6666" width="11.44140625" style="124"/>
+    <col min="6667" max="6668" width="4.88671875" style="124" customWidth="1"/>
+    <col min="6669" max="6669" width="10.88671875" style="124" customWidth="1"/>
+    <col min="6670" max="6670" width="11.44140625" style="124"/>
     <col min="6671" max="6671" width="22" style="124" customWidth="1"/>
-    <col min="6672" max="6673" width="11.42578125" style="124"/>
+    <col min="6672" max="6673" width="11.44140625" style="124"/>
     <col min="6674" max="6675" width="6" style="124" customWidth="1"/>
-    <col min="6676" max="6906" width="11.42578125" style="124"/>
+    <col min="6676" max="6906" width="11.44140625" style="124"/>
     <col min="6907" max="6908" width="20" style="124" customWidth="1"/>
-    <col min="6909" max="6909" width="11.42578125" style="124"/>
-    <col min="6910" max="6911" width="6.140625" style="124" customWidth="1"/>
+    <col min="6909" max="6909" width="11.44140625" style="124"/>
+    <col min="6910" max="6911" width="6.109375" style="124" customWidth="1"/>
     <col min="6912" max="6912" width="14" style="124" customWidth="1"/>
-    <col min="6913" max="6913" width="4.42578125" style="124" customWidth="1"/>
-    <col min="6914" max="6914" width="20.85546875" style="124" customWidth="1"/>
-    <col min="6915" max="6916" width="11.42578125" style="124"/>
-    <col min="6917" max="6918" width="4.140625" style="124" customWidth="1"/>
-    <col min="6919" max="6919" width="11.42578125" style="124"/>
-    <col min="6920" max="6920" width="19.140625" style="124" customWidth="1"/>
-    <col min="6921" max="6922" width="11.42578125" style="124"/>
-    <col min="6923" max="6924" width="4.85546875" style="124" customWidth="1"/>
-    <col min="6925" max="6925" width="10.85546875" style="124" customWidth="1"/>
-    <col min="6926" max="6926" width="11.42578125" style="124"/>
+    <col min="6913" max="6913" width="4.44140625" style="124" customWidth="1"/>
+    <col min="6914" max="6914" width="20.88671875" style="124" customWidth="1"/>
+    <col min="6915" max="6916" width="11.44140625" style="124"/>
+    <col min="6917" max="6918" width="4.109375" style="124" customWidth="1"/>
+    <col min="6919" max="6919" width="11.44140625" style="124"/>
+    <col min="6920" max="6920" width="19.109375" style="124" customWidth="1"/>
+    <col min="6921" max="6922" width="11.44140625" style="124"/>
+    <col min="6923" max="6924" width="4.88671875" style="124" customWidth="1"/>
+    <col min="6925" max="6925" width="10.88671875" style="124" customWidth="1"/>
+    <col min="6926" max="6926" width="11.44140625" style="124"/>
     <col min="6927" max="6927" width="22" style="124" customWidth="1"/>
-    <col min="6928" max="6929" width="11.42578125" style="124"/>
+    <col min="6928" max="6929" width="11.44140625" style="124"/>
     <col min="6930" max="6931" width="6" style="124" customWidth="1"/>
-    <col min="6932" max="7162" width="11.42578125" style="124"/>
+    <col min="6932" max="7162" width="11.44140625" style="124"/>
     <col min="7163" max="7164" width="20" style="124" customWidth="1"/>
-    <col min="7165" max="7165" width="11.42578125" style="124"/>
-    <col min="7166" max="7167" width="6.140625" style="124" customWidth="1"/>
+    <col min="7165" max="7165" width="11.44140625" style="124"/>
+    <col min="7166" max="7167" width="6.109375" style="124" customWidth="1"/>
     <col min="7168" max="7168" width="14" style="124" customWidth="1"/>
-    <col min="7169" max="7169" width="4.42578125" style="124" customWidth="1"/>
-    <col min="7170" max="7170" width="20.85546875" style="124" customWidth="1"/>
-    <col min="7171" max="7172" width="11.42578125" style="124"/>
-    <col min="7173" max="7174" width="4.140625" style="124" customWidth="1"/>
-    <col min="7175" max="7175" width="11.42578125" style="124"/>
-    <col min="7176" max="7176" width="19.140625" style="124" customWidth="1"/>
-    <col min="7177" max="7178" width="11.42578125" style="124"/>
-    <col min="7179" max="7180" width="4.85546875" style="124" customWidth="1"/>
-    <col min="7181" max="7181" width="10.85546875" style="124" customWidth="1"/>
-    <col min="7182" max="7182" width="11.42578125" style="124"/>
+    <col min="7169" max="7169" width="4.44140625" style="124" customWidth="1"/>
+    <col min="7170" max="7170" width="20.88671875" style="124" customWidth="1"/>
+    <col min="7171" max="7172" width="11.44140625" style="124"/>
+    <col min="7173" max="7174" width="4.109375" style="124" customWidth="1"/>
+    <col min="7175" max="7175" width="11.44140625" style="124"/>
+    <col min="7176" max="7176" width="19.109375" style="124" customWidth="1"/>
+    <col min="7177" max="7178" width="11.44140625" style="124"/>
+    <col min="7179" max="7180" width="4.88671875" style="124" customWidth="1"/>
+    <col min="7181" max="7181" width="10.88671875" style="124" customWidth="1"/>
+    <col min="7182" max="7182" width="11.44140625" style="124"/>
     <col min="7183" max="7183" width="22" style="124" customWidth="1"/>
-    <col min="7184" max="7185" width="11.42578125" style="124"/>
+    <col min="7184" max="7185" width="11.44140625" style="124"/>
     <col min="7186" max="7187" width="6" style="124" customWidth="1"/>
-    <col min="7188" max="7418" width="11.42578125" style="124"/>
+    <col min="7188" max="7418" width="11.44140625" style="124"/>
     <col min="7419" max="7420" width="20" style="124" customWidth="1"/>
-    <col min="7421" max="7421" width="11.42578125" style="124"/>
-    <col min="7422" max="7423" width="6.140625" style="124" customWidth="1"/>
+    <col min="7421" max="7421" width="11.44140625" style="124"/>
+    <col min="7422" max="7423" width="6.109375" style="124" customWidth="1"/>
     <col min="7424" max="7424" width="14" style="124" customWidth="1"/>
-    <col min="7425" max="7425" width="4.42578125" style="124" customWidth="1"/>
-    <col min="7426" max="7426" width="20.85546875" style="124" customWidth="1"/>
-    <col min="7427" max="7428" width="11.42578125" style="124"/>
-    <col min="7429" max="7430" width="4.140625" style="124" customWidth="1"/>
-    <col min="7431" max="7431" width="11.42578125" style="124"/>
-    <col min="7432" max="7432" width="19.140625" style="124" customWidth="1"/>
-    <col min="7433" max="7434" width="11.42578125" style="124"/>
-    <col min="7435" max="7436" width="4.85546875" style="124" customWidth="1"/>
-    <col min="7437" max="7437" width="10.85546875" style="124" customWidth="1"/>
-    <col min="7438" max="7438" width="11.42578125" style="124"/>
+    <col min="7425" max="7425" width="4.44140625" style="124" customWidth="1"/>
+    <col min="7426" max="7426" width="20.88671875" style="124" customWidth="1"/>
+    <col min="7427" max="7428" width="11.44140625" style="124"/>
+    <col min="7429" max="7430" width="4.109375" style="124" customWidth="1"/>
+    <col min="7431" max="7431" width="11.44140625" style="124"/>
+    <col min="7432" max="7432" width="19.109375" style="124" customWidth="1"/>
+    <col min="7433" max="7434" width="11.44140625" style="124"/>
+    <col min="7435" max="7436" width="4.88671875" style="124" customWidth="1"/>
+    <col min="7437" max="7437" width="10.88671875" style="124" customWidth="1"/>
+    <col min="7438" max="7438" width="11.44140625" style="124"/>
     <col min="7439" max="7439" width="22" style="124" customWidth="1"/>
-    <col min="7440" max="7441" width="11.42578125" style="124"/>
+    <col min="7440" max="7441" width="11.44140625" style="124"/>
     <col min="7442" max="7443" width="6" style="124" customWidth="1"/>
-    <col min="7444" max="7674" width="11.42578125" style="124"/>
+    <col min="7444" max="7674" width="11.44140625" style="124"/>
     <col min="7675" max="7676" width="20" style="124" customWidth="1"/>
-    <col min="7677" max="7677" width="11.42578125" style="124"/>
-    <col min="7678" max="7679" width="6.140625" style="124" customWidth="1"/>
+    <col min="7677" max="7677" width="11.44140625" style="124"/>
+    <col min="7678" max="7679" width="6.109375" style="124" customWidth="1"/>
     <col min="7680" max="7680" width="14" style="124" customWidth="1"/>
-    <col min="7681" max="7681" width="4.42578125" style="124" customWidth="1"/>
-    <col min="7682" max="7682" width="20.85546875" style="124" customWidth="1"/>
-    <col min="7683" max="7684" width="11.42578125" style="124"/>
-    <col min="7685" max="7686" width="4.140625" style="124" customWidth="1"/>
-    <col min="7687" max="7687" width="11.42578125" style="124"/>
-    <col min="7688" max="7688" width="19.140625" style="124" customWidth="1"/>
-    <col min="7689" max="7690" width="11.42578125" style="124"/>
-    <col min="7691" max="7692" width="4.85546875" style="124" customWidth="1"/>
-    <col min="7693" max="7693" width="10.85546875" style="124" customWidth="1"/>
-    <col min="7694" max="7694" width="11.42578125" style="124"/>
+    <col min="7681" max="7681" width="4.44140625" style="124" customWidth="1"/>
+    <col min="7682" max="7682" width="20.88671875" style="124" customWidth="1"/>
+    <col min="7683" max="7684" width="11.44140625" style="124"/>
+    <col min="7685" max="7686" width="4.109375" style="124" customWidth="1"/>
+    <col min="7687" max="7687" width="11.44140625" style="124"/>
+    <col min="7688" max="7688" width="19.109375" style="124" customWidth="1"/>
+    <col min="7689" max="7690" width="11.44140625" style="124"/>
+    <col min="7691" max="7692" width="4.88671875" style="124" customWidth="1"/>
+    <col min="7693" max="7693" width="10.88671875" style="124" customWidth="1"/>
+    <col min="7694" max="7694" width="11.44140625" style="124"/>
     <col min="7695" max="7695" width="22" style="124" customWidth="1"/>
-    <col min="7696" max="7697" width="11.42578125" style="124"/>
+    <col min="7696" max="7697" width="11.44140625" style="124"/>
     <col min="7698" max="7699" width="6" style="124" customWidth="1"/>
-    <col min="7700" max="7930" width="11.42578125" style="124"/>
+    <col min="7700" max="7930" width="11.44140625" style="124"/>
     <col min="7931" max="7932" width="20" style="124" customWidth="1"/>
-    <col min="7933" max="7933" width="11.42578125" style="124"/>
-    <col min="7934" max="7935" width="6.140625" style="124" customWidth="1"/>
+    <col min="7933" max="7933" width="11.44140625" style="124"/>
+    <col min="7934" max="7935" width="6.109375" style="124" customWidth="1"/>
     <col min="7936" max="7936" width="14" style="124" customWidth="1"/>
-    <col min="7937" max="7937" width="4.42578125" style="124" customWidth="1"/>
-    <col min="7938" max="7938" width="20.85546875" style="124" customWidth="1"/>
-    <col min="7939" max="7940" width="11.42578125" style="124"/>
-    <col min="7941" max="7942" width="4.140625" style="124" customWidth="1"/>
-    <col min="7943" max="7943" width="11.42578125" style="124"/>
-    <col min="7944" max="7944" width="19.140625" style="124" customWidth="1"/>
-    <col min="7945" max="7946" width="11.42578125" style="124"/>
-    <col min="7947" max="7948" width="4.85546875" style="124" customWidth="1"/>
-    <col min="7949" max="7949" width="10.85546875" style="124" customWidth="1"/>
-    <col min="7950" max="7950" width="11.42578125" style="124"/>
+    <col min="7937" max="7937" width="4.44140625" style="124" customWidth="1"/>
+    <col min="7938" max="7938" width="20.88671875" style="124" customWidth="1"/>
+    <col min="7939" max="7940" width="11.44140625" style="124"/>
+    <col min="7941" max="7942" width="4.109375" style="124" customWidth="1"/>
+    <col min="7943" max="7943" width="11.44140625" style="124"/>
+    <col min="7944" max="7944" width="19.109375" style="124" customWidth="1"/>
+    <col min="7945" max="7946" width="11.44140625" style="124"/>
+    <col min="7947" max="7948" width="4.88671875" style="124" customWidth="1"/>
+    <col min="7949" max="7949" width="10.88671875" style="124" customWidth="1"/>
+    <col min="7950" max="7950" width="11.44140625" style="124"/>
     <col min="7951" max="7951" width="22" style="124" customWidth="1"/>
-    <col min="7952" max="7953" width="11.42578125" style="124"/>
+    <col min="7952" max="7953" width="11.44140625" style="124"/>
     <col min="7954" max="7955" width="6" style="124" customWidth="1"/>
-    <col min="7956" max="8186" width="11.42578125" style="124"/>
+    <col min="7956" max="8186" width="11.44140625" style="124"/>
     <col min="8187" max="8188" width="20" style="124" customWidth="1"/>
-    <col min="8189" max="8189" width="11.42578125" style="124"/>
-    <col min="8190" max="8191" width="6.140625" style="124" customWidth="1"/>
+    <col min="8189" max="8189" width="11.44140625" style="124"/>
+    <col min="8190" max="8191" width="6.109375" style="124" customWidth="1"/>
     <col min="8192" max="8192" width="14" style="124" customWidth="1"/>
-    <col min="8193" max="8193" width="4.42578125" style="124" customWidth="1"/>
-    <col min="8194" max="8194" width="20.85546875" style="124" customWidth="1"/>
-    <col min="8195" max="8196" width="11.42578125" style="124"/>
-    <col min="8197" max="8198" width="4.140625" style="124" customWidth="1"/>
-    <col min="8199" max="8199" width="11.42578125" style="124"/>
-    <col min="8200" max="8200" width="19.140625" style="124" customWidth="1"/>
-    <col min="8201" max="8202" width="11.42578125" style="124"/>
-    <col min="8203" max="8204" width="4.85546875" style="124" customWidth="1"/>
-    <col min="8205" max="8205" width="10.85546875" style="124" customWidth="1"/>
-    <col min="8206" max="8206" width="11.42578125" style="124"/>
+    <col min="8193" max="8193" width="4.44140625" style="124" customWidth="1"/>
+    <col min="8194" max="8194" width="20.88671875" style="124" customWidth="1"/>
+    <col min="8195" max="8196" width="11.44140625" style="124"/>
+    <col min="8197" max="8198" width="4.109375" style="124" customWidth="1"/>
+    <col min="8199" max="8199" width="11.44140625" style="124"/>
+    <col min="8200" max="8200" width="19.109375" style="124" customWidth="1"/>
+    <col min="8201" max="8202" width="11.44140625" style="124"/>
+    <col min="8203" max="8204" width="4.88671875" style="124" customWidth="1"/>
+    <col min="8205" max="8205" width="10.88671875" style="124" customWidth="1"/>
+    <col min="8206" max="8206" width="11.44140625" style="124"/>
     <col min="8207" max="8207" width="22" style="124" customWidth="1"/>
-    <col min="8208" max="8209" width="11.42578125" style="124"/>
+    <col min="8208" max="8209" width="11.44140625" style="124"/>
     <col min="8210" max="8211" width="6" style="124" customWidth="1"/>
-    <col min="8212" max="8442" width="11.42578125" style="124"/>
+    <col min="8212" max="8442" width="11.44140625" style="124"/>
     <col min="8443" max="8444" width="20" style="124" customWidth="1"/>
-    <col min="8445" max="8445" width="11.42578125" style="124"/>
-    <col min="8446" max="8447" width="6.140625" style="124" customWidth="1"/>
+    <col min="8445" max="8445" width="11.44140625" style="124"/>
+    <col min="8446" max="8447" width="6.109375" style="124" customWidth="1"/>
     <col min="8448" max="8448" width="14" style="124" customWidth="1"/>
-    <col min="8449" max="8449" width="4.42578125" style="124" customWidth="1"/>
-    <col min="8450" max="8450" width="20.85546875" style="124" customWidth="1"/>
-    <col min="8451" max="8452" width="11.42578125" style="124"/>
-    <col min="8453" max="8454" width="4.140625" style="124" customWidth="1"/>
-    <col min="8455" max="8455" width="11.42578125" style="124"/>
-    <col min="8456" max="8456" width="19.140625" style="124" customWidth="1"/>
-    <col min="8457" max="8458" width="11.42578125" style="124"/>
-    <col min="8459" max="8460" width="4.85546875" style="124" customWidth="1"/>
-    <col min="8461" max="8461" width="10.85546875" style="124" customWidth="1"/>
-    <col min="8462" max="8462" width="11.42578125" style="124"/>
+    <col min="8449" max="8449" width="4.44140625" style="124" customWidth="1"/>
+    <col min="8450" max="8450" width="20.88671875" style="124" customWidth="1"/>
+    <col min="8451" max="8452" width="11.44140625" style="124"/>
+    <col min="8453" max="8454" width="4.109375" style="124" customWidth="1"/>
+    <col min="8455" max="8455" width="11.44140625" style="124"/>
+    <col min="8456" max="8456" width="19.109375" style="124" customWidth="1"/>
+    <col min="8457" max="8458" width="11.44140625" style="124"/>
+    <col min="8459" max="8460" width="4.88671875" style="124" customWidth="1"/>
+    <col min="8461" max="8461" width="10.88671875" style="124" customWidth="1"/>
+    <col min="8462" max="8462" width="11.44140625" style="124"/>
     <col min="8463" max="8463" width="22" style="124" customWidth="1"/>
-    <col min="8464" max="8465" width="11.42578125" style="124"/>
+    <col min="8464" max="8465" width="11.44140625" style="124"/>
     <col min="8466" max="8467" width="6" style="124" customWidth="1"/>
-    <col min="8468" max="8698" width="11.42578125" style="124"/>
+    <col min="8468" max="8698" width="11.44140625" style="124"/>
     <col min="8699" max="8700" width="20" style="124" customWidth="1"/>
-    <col min="8701" max="8701" width="11.42578125" style="124"/>
-    <col min="8702" max="8703" width="6.140625" style="124" customWidth="1"/>
+    <col min="8701" max="8701" width="11.44140625" style="124"/>
+    <col min="8702" max="8703" width="6.109375" style="124" customWidth="1"/>
     <col min="8704" max="8704" width="14" style="124" customWidth="1"/>
-    <col min="8705" max="8705" width="4.42578125" style="124" customWidth="1"/>
-    <col min="8706" max="8706" width="20.85546875" style="124" customWidth="1"/>
-    <col min="8707" max="8708" width="11.42578125" style="124"/>
-    <col min="8709" max="8710" width="4.140625" style="124" customWidth="1"/>
-    <col min="8711" max="8711" width="11.42578125" style="124"/>
-    <col min="8712" max="8712" width="19.140625" style="124" customWidth="1"/>
-    <col min="8713" max="8714" width="11.42578125" style="124"/>
-    <col min="8715" max="8716" width="4.85546875" style="124" customWidth="1"/>
-    <col min="8717" max="8717" width="10.85546875" style="124" customWidth="1"/>
-    <col min="8718" max="8718" width="11.42578125" style="124"/>
+    <col min="8705" max="8705" width="4.44140625" style="124" customWidth="1"/>
+    <col min="8706" max="8706" width="20.88671875" style="124" customWidth="1"/>
+    <col min="8707" max="8708" width="11.44140625" style="124"/>
+    <col min="8709" max="8710" width="4.109375" style="124" customWidth="1"/>
+    <col min="8711" max="8711" width="11.44140625" style="124"/>
+    <col min="8712" max="8712" width="19.109375" style="124" customWidth="1"/>
+    <col min="8713" max="8714" width="11.44140625" style="124"/>
+    <col min="8715" max="8716" width="4.88671875" style="124" customWidth="1"/>
+    <col min="8717" max="8717" width="10.88671875" style="124" customWidth="1"/>
+    <col min="8718" max="8718" width="11.44140625" style="124"/>
     <col min="8719" max="8719" width="22" style="124" customWidth="1"/>
-    <col min="8720" max="8721" width="11.42578125" style="124"/>
+    <col min="8720" max="8721" width="11.44140625" style="124"/>
     <col min="8722" max="8723" width="6" style="124" customWidth="1"/>
-    <col min="8724" max="8954" width="11.42578125" style="124"/>
+    <col min="8724" max="8954" width="11.44140625" style="124"/>
     <col min="8955" max="8956" width="20" style="124" customWidth="1"/>
-    <col min="8957" max="8957" width="11.42578125" style="124"/>
-    <col min="8958" max="8959" width="6.140625" style="124" customWidth="1"/>
+    <col min="8957" max="8957" width="11.44140625" style="124"/>
+    <col min="8958" max="8959" width="6.109375" style="124" customWidth="1"/>
     <col min="8960" max="8960" width="14" style="124" customWidth="1"/>
-    <col min="8961" max="8961" width="4.42578125" style="124" customWidth="1"/>
-    <col min="8962" max="8962" width="20.85546875" style="124" customWidth="1"/>
-    <col min="8963" max="8964" width="11.42578125" style="124"/>
-    <col min="8965" max="8966" width="4.140625" style="124" customWidth="1"/>
-    <col min="8967" max="8967" width="11.42578125" style="124"/>
-    <col min="8968" max="8968" width="19.140625" style="124" customWidth="1"/>
-    <col min="8969" max="8970" width="11.42578125" style="124"/>
-    <col min="8971" max="8972" width="4.85546875" style="124" customWidth="1"/>
-    <col min="8973" max="8973" width="10.85546875" style="124" customWidth="1"/>
-    <col min="8974" max="8974" width="11.42578125" style="124"/>
+    <col min="8961" max="8961" width="4.44140625" style="124" customWidth="1"/>
+    <col min="8962" max="8962" width="20.88671875" style="124" customWidth="1"/>
+    <col min="8963" max="8964" width="11.44140625" style="124"/>
+    <col min="8965" max="8966" width="4.109375" style="124" customWidth="1"/>
+    <col min="8967" max="8967" width="11.44140625" style="124"/>
+    <col min="8968" max="8968" width="19.109375" style="124" customWidth="1"/>
+    <col min="8969" max="8970" width="11.44140625" style="124"/>
+    <col min="8971" max="8972" width="4.88671875" style="124" customWidth="1"/>
+    <col min="8973" max="8973" width="10.88671875" style="124" customWidth="1"/>
+    <col min="8974" max="8974" width="11.44140625" style="124"/>
     <col min="8975" max="8975" width="22" style="124" customWidth="1"/>
-    <col min="8976" max="8977" width="11.42578125" style="124"/>
+    <col min="8976" max="8977" width="11.44140625" style="124"/>
     <col min="8978" max="8979" width="6" style="124" customWidth="1"/>
-    <col min="8980" max="9210" width="11.42578125" style="124"/>
+    <col min="8980" max="9210" width="11.44140625" style="124"/>
     <col min="9211" max="9212" width="20" style="124" customWidth="1"/>
-    <col min="9213" max="9213" width="11.42578125" style="124"/>
-    <col min="9214" max="9215" width="6.140625" style="124" customWidth="1"/>
+    <col min="9213" max="9213" width="11.44140625" style="124"/>
+    <col min="9214" max="9215" width="6.109375" style="124" customWidth="1"/>
     <col min="9216" max="9216" width="14" style="124" customWidth="1"/>
-    <col min="9217" max="9217" width="4.42578125" style="124" customWidth="1"/>
-    <col min="9218" max="9218" width="20.85546875" style="124" customWidth="1"/>
-    <col min="9219" max="9220" width="11.42578125" style="124"/>
-    <col min="9221" max="9222" width="4.140625" style="124" customWidth="1"/>
-    <col min="9223" max="9223" width="11.42578125" style="124"/>
-    <col min="9224" max="9224" width="19.140625" style="124" customWidth="1"/>
-    <col min="9225" max="9226" width="11.42578125" style="124"/>
-    <col min="9227" max="9228" width="4.85546875" style="124" customWidth="1"/>
-    <col min="9229" max="9229" width="10.85546875" style="124" customWidth="1"/>
-    <col min="9230" max="9230" width="11.42578125" style="124"/>
+    <col min="9217" max="9217" width="4.44140625" style="124" customWidth="1"/>
+    <col min="9218" max="9218" width="20.88671875" style="124" customWidth="1"/>
+    <col min="9219" max="9220" width="11.44140625" style="124"/>
+    <col min="9221" max="9222" width="4.109375" style="124" customWidth="1"/>
+    <col min="9223" max="9223" width="11.44140625" style="124"/>
+    <col min="9224" max="9224" width="19.109375" style="124" customWidth="1"/>
+    <col min="9225" max="9226" width="11.44140625" style="124"/>
+    <col min="9227" max="9228" width="4.88671875" style="124" customWidth="1"/>
+    <col min="9229" max="9229" width="10.88671875" style="124" customWidth="1"/>
+    <col min="9230" max="9230" width="11.44140625" style="124"/>
     <col min="9231" max="9231" width="22" style="124" customWidth="1"/>
-    <col min="9232" max="9233" width="11.42578125" style="124"/>
+    <col min="9232" max="9233" width="11.44140625" style="124"/>
     <col min="9234" max="9235" width="6" style="124" customWidth="1"/>
-    <col min="9236" max="9466" width="11.42578125" style="124"/>
+    <col min="9236" max="9466" width="11.44140625" style="124"/>
     <col min="9467" max="9468" width="20" style="124" customWidth="1"/>
-    <col min="9469" max="9469" width="11.42578125" style="124"/>
-    <col min="9470" max="9471" width="6.140625" style="124" customWidth="1"/>
+    <col min="9469" max="9469" width="11.44140625" style="124"/>
+    <col min="9470" max="9471" width="6.109375" style="124" customWidth="1"/>
     <col min="9472" max="9472" width="14" style="124" customWidth="1"/>
-    <col min="9473" max="9473" width="4.42578125" style="124" customWidth="1"/>
-    <col min="9474" max="9474" width="20.85546875" style="124" customWidth="1"/>
-    <col min="9475" max="9476" width="11.42578125" style="124"/>
-    <col min="9477" max="9478" width="4.140625" style="124" customWidth="1"/>
-    <col min="9479" max="9479" width="11.42578125" style="124"/>
-    <col min="9480" max="9480" width="19.140625" style="124" customWidth="1"/>
-    <col min="9481" max="9482" width="11.42578125" style="124"/>
-    <col min="9483" max="9484" width="4.85546875" style="124" customWidth="1"/>
-    <col min="9485" max="9485" width="10.85546875" style="124" customWidth="1"/>
-    <col min="9486" max="9486" width="11.42578125" style="124"/>
+    <col min="9473" max="9473" width="4.44140625" style="124" customWidth="1"/>
+    <col min="9474" max="9474" width="20.88671875" style="124" customWidth="1"/>
+    <col min="9475" max="9476" width="11.44140625" style="124"/>
+    <col min="9477" max="9478" width="4.109375" style="124" customWidth="1"/>
+    <col min="9479" max="9479" width="11.44140625" style="124"/>
+    <col min="9480" max="9480" width="19.109375" style="124" customWidth="1"/>
+    <col min="9481" max="9482" width="11.44140625" style="124"/>
+    <col min="9483" max="9484" width="4.88671875" style="124" customWidth="1"/>
+    <col min="9485" max="9485" width="10.88671875" style="124" customWidth="1"/>
+    <col min="9486" max="9486" width="11.44140625" style="124"/>
     <col min="9487" max="9487" width="22" style="124" customWidth="1"/>
-    <col min="9488" max="9489" width="11.42578125" style="124"/>
+    <col min="9488" max="9489" width="11.44140625" style="124"/>
     <col min="9490" max="9491" width="6" style="124" customWidth="1"/>
-    <col min="9492" max="9722" width="11.42578125" style="124"/>
+    <col min="9492" max="9722" width="11.44140625" style="124"/>
     <col min="9723" max="9724" width="20" style="124" customWidth="1"/>
-    <col min="9725" max="9725" width="11.42578125" style="124"/>
-    <col min="9726" max="9727" width="6.140625" style="124" customWidth="1"/>
+    <col min="9725" max="9725" width="11.44140625" style="124"/>
+    <col min="9726" max="9727" width="6.109375" style="124" customWidth="1"/>
     <col min="9728" max="9728" width="14" style="124" customWidth="1"/>
-    <col min="9729" max="9729" width="4.42578125" style="124" customWidth="1"/>
-    <col min="9730" max="9730" width="20.85546875" style="124" customWidth="1"/>
-    <col min="9731" max="9732" width="11.42578125" style="124"/>
-    <col min="9733" max="9734" width="4.140625" style="124" customWidth="1"/>
-    <col min="9735" max="9735" width="11.42578125" style="124"/>
-    <col min="9736" max="9736" width="19.140625" style="124" customWidth="1"/>
-    <col min="9737" max="9738" width="11.42578125" style="124"/>
-    <col min="9739" max="9740" width="4.85546875" style="124" customWidth="1"/>
-    <col min="9741" max="9741" width="10.85546875" style="124" customWidth="1"/>
-    <col min="9742" max="9742" width="11.42578125" style="124"/>
+    <col min="9729" max="9729" width="4.44140625" style="124" customWidth="1"/>
+    <col min="9730" max="9730" width="20.88671875" style="124" customWidth="1"/>
+    <col min="9731" max="9732" width="11.44140625" style="124"/>
+    <col min="9733" max="9734" width="4.109375" style="124" customWidth="1"/>
+    <col min="9735" max="9735" width="11.44140625" style="124"/>
+    <col min="9736" max="9736" width="19.109375" style="124" customWidth="1"/>
+    <col min="9737" max="9738" width="11.44140625" style="124"/>
+    <col min="9739" max="9740" width="4.88671875" style="124" customWidth="1"/>
+    <col min="9741" max="9741" width="10.88671875" style="124" customWidth="1"/>
+    <col min="9742" max="9742" width="11.44140625" style="124"/>
     <col min="9743" max="9743" width="22" style="124" customWidth="1"/>
-    <col min="9744" max="9745" width="11.42578125" style="124"/>
+    <col min="9744" max="9745" width="11.44140625" style="124"/>
     <col min="9746" max="9747" width="6" style="124" customWidth="1"/>
-    <col min="9748" max="9978" width="11.42578125" style="124"/>
+    <col min="9748" max="9978" width="11.44140625" style="124"/>
     <col min="9979" max="9980" width="20" style="124" customWidth="1"/>
-    <col min="9981" max="9981" width="11.42578125" style="124"/>
-    <col min="9982" max="9983" width="6.140625" style="124" customWidth="1"/>
+    <col min="9981" max="9981" width="11.44140625" style="124"/>
+    <col min="9982" max="9983" width="6.109375" style="124" customWidth="1"/>
     <col min="9984" max="9984" width="14" style="124" customWidth="1"/>
-    <col min="9985" max="9985" width="4.42578125" style="124" customWidth="1"/>
-    <col min="9986" max="9986" width="20.85546875" style="124" customWidth="1"/>
-    <col min="9987" max="9988" width="11.42578125" style="124"/>
-    <col min="9989" max="9990" width="4.140625" style="124" customWidth="1"/>
-    <col min="9991" max="9991" width="11.42578125" style="124"/>
-    <col min="9992" max="9992" width="19.140625" style="124" customWidth="1"/>
-    <col min="9993" max="9994" width="11.42578125" style="124"/>
-    <col min="9995" max="9996" width="4.85546875" style="124" customWidth="1"/>
-    <col min="9997" max="9997" width="10.85546875" style="124" customWidth="1"/>
-    <col min="9998" max="9998" width="11.42578125" style="124"/>
+    <col min="9985" max="9985" width="4.44140625" style="124" customWidth="1"/>
+    <col min="9986" max="9986" width="20.88671875" style="124" customWidth="1"/>
+    <col min="9987" max="9988" width="11.44140625" style="124"/>
+    <col min="9989" max="9990" width="4.109375" style="124" customWidth="1"/>
+    <col min="9991" max="9991" width="11.44140625" style="124"/>
+    <col min="9992" max="9992" width="19.109375" style="124" customWidth="1"/>
+    <col min="9993" max="9994" width="11.44140625" style="124"/>
+    <col min="9995" max="9996" width="4.88671875" style="124" customWidth="1"/>
+    <col min="9997" max="9997" width="10.88671875" style="124" customWidth="1"/>
+    <col min="9998" max="9998" width="11.44140625" style="124"/>
     <col min="9999" max="9999" width="22" style="124" customWidth="1"/>
-    <col min="10000" max="10001" width="11.42578125" style="124"/>
+    <col min="10000" max="10001" width="11.44140625" style="124"/>
     <col min="10002" max="10003" width="6" style="124" customWidth="1"/>
-    <col min="10004" max="10234" width="11.42578125" style="124"/>
+    <col min="10004" max="10234" width="11.44140625" style="124"/>
     <col min="10235" max="10236" width="20" style="124" customWidth="1"/>
-    <col min="10237" max="10237" width="11.42578125" style="124"/>
-    <col min="10238" max="10239" width="6.140625" style="124" customWidth="1"/>
+    <col min="10237" max="10237" width="11.44140625" style="124"/>
+    <col min="10238" max="10239" width="6.109375" style="124" customWidth="1"/>
     <col min="10240" max="10240" width="14" style="124" customWidth="1"/>
-    <col min="10241" max="10241" width="4.42578125" style="124" customWidth="1"/>
-    <col min="10242" max="10242" width="20.85546875" style="124" customWidth="1"/>
-    <col min="10243" max="10244" width="11.42578125" style="124"/>
-    <col min="10245" max="10246" width="4.140625" style="124" customWidth="1"/>
-    <col min="10247" max="10247" width="11.42578125" style="124"/>
-    <col min="10248" max="10248" width="19.140625" style="124" customWidth="1"/>
-    <col min="10249" max="10250" width="11.42578125" style="124"/>
-    <col min="10251" max="10252" width="4.85546875" style="124" customWidth="1"/>
-    <col min="10253" max="10253" width="10.85546875" style="124" customWidth="1"/>
-    <col min="10254" max="10254" width="11.42578125" style="124"/>
+    <col min="10241" max="10241" width="4.44140625" style="124" customWidth="1"/>
+    <col min="10242" max="10242" width="20.88671875" style="124" customWidth="1"/>
+    <col min="10243" max="10244" width="11.44140625" style="124"/>
+    <col min="10245" max="10246" width="4.109375" style="124" customWidth="1"/>
+    <col min="10247" max="10247" width="11.44140625" style="124"/>
+    <col min="10248" max="10248" width="19.109375" style="124" customWidth="1"/>
+    <col min="10249" max="10250" width="11.44140625" style="124"/>
+    <col min="10251" max="10252" width="4.88671875" style="124" customWidth="1"/>
+    <col min="10253" max="10253" width="10.88671875" style="124" customWidth="1"/>
+    <col min="10254" max="10254" width="11.44140625" style="124"/>
     <col min="10255" max="10255" width="22" style="124" customWidth="1"/>
-    <col min="10256" max="10257" width="11.42578125" style="124"/>
+    <col min="10256" max="10257" width="11.44140625" style="124"/>
     <col min="10258" max="10259" width="6" style="124" customWidth="1"/>
-    <col min="10260" max="10490" width="11.42578125" style="124"/>
+    <col min="10260" max="10490" width="11.44140625" style="124"/>
     <col min="10491" max="10492" width="20" style="124" customWidth="1"/>
-    <col min="10493" max="10493" width="11.42578125" style="124"/>
-    <col min="10494" max="10495" width="6.140625" style="124" customWidth="1"/>
+    <col min="10493" max="10493" width="11.44140625" style="124"/>
+    <col min="10494" max="10495" width="6.109375" style="124" customWidth="1"/>
     <col min="10496" max="10496" width="14" style="124" customWidth="1"/>
-    <col min="10497" max="10497" width="4.42578125" style="124" customWidth="1"/>
-    <col min="10498" max="10498" width="20.85546875" style="124" customWidth="1"/>
-    <col min="10499" max="10500" width="11.42578125" style="124"/>
-    <col min="10501" max="10502" width="4.140625" style="124" customWidth="1"/>
-    <col min="10503" max="10503" width="11.42578125" style="124"/>
-    <col min="10504" max="10504" width="19.140625" style="124" customWidth="1"/>
-    <col min="10505" max="10506" width="11.42578125" style="124"/>
-    <col min="10507" max="10508" width="4.85546875" style="124" customWidth="1"/>
-    <col min="10509" max="10509" width="10.85546875" style="124" customWidth="1"/>
-    <col min="10510" max="10510" width="11.42578125" style="124"/>
+    <col min="10497" max="10497" width="4.44140625" style="124" customWidth="1"/>
+    <col min="10498" max="10498" width="20.88671875" style="124" customWidth="1"/>
+    <col min="10499" max="10500" width="11.44140625" style="124"/>
+    <col min="10501" max="10502" width="4.109375" style="124" customWidth="1"/>
+    <col min="10503" max="10503" width="11.44140625" style="124"/>
+    <col min="10504" max="10504" width="19.109375" style="124" customWidth="1"/>
+    <col min="10505" max="10506" width="11.44140625" style="124"/>
+    <col min="10507" max="10508" width="4.88671875" style="124" customWidth="1"/>
+    <col min="10509" max="10509" width="10.88671875" style="124" customWidth="1"/>
+    <col min="10510" max="10510" width="11.44140625" style="124"/>
     <col min="10511" max="10511" width="22" style="124" customWidth="1"/>
-    <col min="10512" max="10513" width="11.42578125" style="124"/>
+    <col min="10512" max="10513" width="11.44140625" style="124"/>
     <col min="10514" max="10515" width="6" style="124" customWidth="1"/>
-    <col min="10516" max="10746" width="11.42578125" style="124"/>
+    <col min="10516" max="10746" width="11.44140625" style="124"/>
     <col min="10747" max="10748" width="20" style="124" customWidth="1"/>
-    <col min="10749" max="10749" width="11.42578125" style="124"/>
-    <col min="10750" max="10751" width="6.140625" style="124" customWidth="1"/>
+    <col min="10749" max="10749" width="11.44140625" style="124"/>
+    <col min="10750" max="10751" width="6.109375" style="124" customWidth="1"/>
     <col min="10752" max="10752" width="14" style="124" customWidth="1"/>
-    <col min="10753" max="10753" width="4.42578125" style="124" customWidth="1"/>
-    <col min="10754" max="10754" width="20.85546875" style="124" customWidth="1"/>
-    <col min="10755" max="10756" width="11.42578125" style="124"/>
-    <col min="10757" max="10758" width="4.140625" style="124" customWidth="1"/>
-    <col min="10759" max="10759" width="11.42578125" style="124"/>
-    <col min="10760" max="10760" width="19.140625" style="124" customWidth="1"/>
-    <col min="10761" max="10762" width="11.42578125" style="124"/>
-    <col min="10763" max="10764" width="4.85546875" style="124" customWidth="1"/>
-    <col min="10765" max="10765" width="10.85546875" style="124" customWidth="1"/>
-    <col min="10766" max="10766" width="11.42578125" style="124"/>
+    <col min="10753" max="10753" width="4.44140625" style="124" customWidth="1"/>
+    <col min="10754" max="10754" width="20.88671875" style="124" customWidth="1"/>
+    <col min="10755" max="10756" width="11.44140625" style="124"/>
+    <col min="10757" max="10758" width="4.109375" style="124" customWidth="1"/>
+    <col min="10759" max="10759" width="11.44140625" style="124"/>
+    <col min="10760" max="10760" width="19.109375" style="124" customWidth="1"/>
+    <col min="10761" max="10762" width="11.44140625" style="124"/>
+    <col min="10763" max="10764" width="4.88671875" style="124" customWidth="1"/>
+    <col min="10765" max="10765" width="10.88671875" style="124" customWidth="1"/>
+    <col min="10766" max="10766" width="11.44140625" style="124"/>
     <col min="10767" max="10767" width="22" style="124" customWidth="1"/>
-    <col min="10768" max="10769" width="11.42578125" style="124"/>
+    <col min="10768" max="10769" width="11.44140625" style="124"/>
     <col min="10770" max="10771" width="6" style="124" customWidth="1"/>
-    <col min="10772" max="11002" width="11.42578125" style="124"/>
+    <col min="10772" max="11002" width="11.44140625" style="124"/>
     <col min="11003" max="11004" width="20" style="124" customWidth="1"/>
-    <col min="11005" max="11005" width="11.42578125" style="124"/>
-    <col min="11006" max="11007" width="6.140625" style="124" customWidth="1"/>
+    <col min="11005" max="11005" width="11.44140625" style="124"/>
+    <col min="11006" max="11007" width="6.109375" style="124" customWidth="1"/>
     <col min="11008" max="11008" width="14" style="124" customWidth="1"/>
-    <col min="11009" max="11009" width="4.42578125" style="124" customWidth="1"/>
-    <col min="11010" max="11010" width="20.85546875" style="124" customWidth="1"/>
-    <col min="11011" max="11012" width="11.42578125" style="124"/>
-    <col min="11013" max="11014" width="4.140625" style="124" customWidth="1"/>
-    <col min="11015" max="11015" width="11.42578125" style="124"/>
-    <col min="11016" max="11016" width="19.140625" style="124" customWidth="1"/>
-    <col min="11017" max="11018" width="11.42578125" style="124"/>
-    <col min="11019" max="11020" width="4.85546875" style="124" customWidth="1"/>
-    <col min="11021" max="11021" width="10.85546875" style="124" customWidth="1"/>
-    <col min="11022" max="11022" width="11.42578125" style="124"/>
+    <col min="11009" max="11009" width="4.44140625" style="124" customWidth="1"/>
+    <col min="11010" max="11010" width="20.88671875" style="124" customWidth="1"/>
+    <col min="11011" max="11012" width="11.44140625" style="124"/>
+    <col min="11013" max="11014" width="4.109375" style="124" customWidth="1"/>
+    <col min="11015" max="11015" width="11.44140625" style="124"/>
+    <col min="11016" max="11016" width="19.109375" style="124" customWidth="1"/>
+    <col min="11017" max="11018" width="11.44140625" style="124"/>
+    <col min="11019" max="11020" width="4.88671875" style="124" customWidth="1"/>
+    <col min="11021" max="11021" width="10.88671875" style="124" customWidth="1"/>
+    <col min="11022" max="11022" width="11.44140625" style="124"/>
     <col min="11023" max="11023" width="22" style="124" customWidth="1"/>
-    <col min="11024" max="11025" width="11.42578125" style="124"/>
+    <col min="11024" max="11025" width="11.44140625" style="124"/>
     <col min="11026" max="11027" width="6" style="124" customWidth="1"/>
-    <col min="11028" max="11258" width="11.42578125" style="124"/>
+    <col min="11028" max="11258" width="11.44140625" style="124"/>
     <col min="11259" max="11260" width="20" style="124" customWidth="1"/>
-    <col min="11261" max="11261" width="11.42578125" style="124"/>
-    <col min="11262" max="11263" width="6.140625" style="124" customWidth="1"/>
+    <col min="11261" max="11261" width="11.44140625" style="124"/>
+    <col min="11262" max="11263" width="6.109375" style="124" customWidth="1"/>
     <col min="11264" max="11264" width="14" style="124" customWidth="1"/>
-    <col min="11265" max="11265" width="4.42578125" style="124" customWidth="1"/>
-    <col min="11266" max="11266" width="20.85546875" style="124" customWidth="1"/>
-    <col min="11267" max="11268" width="11.42578125" style="124"/>
-    <col min="11269" max="11270" width="4.140625" style="124" customWidth="1"/>
-    <col min="11271" max="11271" width="11.42578125" style="124"/>
-    <col min="11272" max="11272" width="19.140625" style="124" customWidth="1"/>
-    <col min="11273" max="11274" width="11.42578125" style="124"/>
-    <col min="11275" max="11276" width="4.85546875" style="124" customWidth="1"/>
-    <col min="11277" max="11277" width="10.85546875" style="124" customWidth="1"/>
-    <col min="11278" max="11278" width="11.42578125" style="124"/>
+    <col min="11265" max="11265" width="4.44140625" style="124" customWidth="1"/>
+    <col min="11266" max="11266" width="20.88671875" style="124" customWidth="1"/>
+    <col min="11267" max="11268" width="11.44140625" style="124"/>
+    <col min="11269" max="11270" width="4.109375" style="124" customWidth="1"/>
+    <col min="11271" max="11271" width="11.44140625" style="124"/>
+    <col min="11272" max="11272" width="19.109375" style="124" customWidth="1"/>
+    <col min="11273" max="11274" width="11.44140625" style="124"/>
+    <col min="11275" max="11276" width="4.88671875" style="124" customWidth="1"/>
+    <col min="11277" max="11277" width="10.88671875" style="124" customWidth="1"/>
+    <col min="11278" max="11278" width="11.44140625" style="124"/>
     <col min="11279" max="11279" width="22" style="124" customWidth="1"/>
-    <col min="11280" max="11281" width="11.42578125" style="124"/>
+    <col min="11280" max="11281" width="11.44140625" style="124"/>
     <col min="11282" max="11283" width="6" style="124" customWidth="1"/>
-    <col min="11284" max="11514" width="11.42578125" style="124"/>
+    <col min="11284" max="11514" width="11.44140625" style="124"/>
     <col min="11515" max="11516" width="20" style="124" customWidth="1"/>
-    <col min="11517" max="11517" width="11.42578125" style="124"/>
-    <col min="11518" max="11519" width="6.140625" style="124" customWidth="1"/>
+    <col min="11517" max="11517" width="11.44140625" style="124"/>
+    <col min="11518" max="11519" width="6.109375" style="124" customWidth="1"/>
     <col min="11520" max="11520" width="14" style="124" customWidth="1"/>
-    <col min="11521" max="11521" width="4.42578125" style="124" customWidth="1"/>
-    <col min="11522" max="11522" width="20.85546875" style="124" customWidth="1"/>
-    <col min="11523" max="11524" width="11.42578125" style="124"/>
-    <col min="11525" max="11526" width="4.140625" style="124" customWidth="1"/>
-    <col min="11527" max="11527" width="11.42578125" style="124"/>
-    <col min="11528" max="11528" width="19.140625" style="124" customWidth="1"/>
-    <col min="11529" max="11530" width="11.42578125" style="124"/>
-    <col min="11531" max="11532" width="4.85546875" style="124" customWidth="1"/>
-    <col min="11533" max="11533" width="10.85546875" style="124" customWidth="1"/>
-    <col min="11534" max="11534" width="11.42578125" style="124"/>
+    <col min="11521" max="11521" width="4.44140625" style="124" customWidth="1"/>
+    <col min="11522" max="11522" width="20.88671875" style="124" customWidth="1"/>
+    <col min="11523" max="11524" width="11.44140625" style="124"/>
+    <col min="11525" max="11526" width="4.109375" style="124" customWidth="1"/>
+    <col min="11527" max="11527" width="11.44140625" style="124"/>
+    <col min="11528" max="11528" width="19.109375" style="124" customWidth="1"/>
+    <col min="11529" max="11530" width="11.44140625" style="124"/>
+    <col min="11531" max="11532" width="4.88671875" style="124" customWidth="1"/>
+    <col min="11533" max="11533" width="10.88671875" style="124" customWidth="1"/>
+    <col min="11534" max="11534" width="11.44140625" style="124"/>
     <col min="11535" max="11535" width="22" style="124" customWidth="1"/>
-    <col min="11536" max="11537" width="11.42578125" style="124"/>
+    <col min="11536" max="11537" width="11.44140625" style="124"/>
     <col min="11538" max="11539" width="6" style="124" customWidth="1"/>
-    <col min="11540" max="11770" width="11.42578125" style="124"/>
+    <col min="11540" max="11770" width="11.44140625" style="124"/>
     <col min="11771" max="11772" width="20" style="124" customWidth="1"/>
-    <col min="11773" max="11773" width="11.42578125" style="124"/>
-    <col min="11774" max="11775" width="6.140625" style="124" customWidth="1"/>
+    <col min="11773" max="11773" width="11.44140625" style="124"/>
+    <col min="11774" max="11775" width="6.109375" style="124" customWidth="1"/>
     <col min="11776" max="11776" width="14" style="124" customWidth="1"/>
-    <col min="11777" max="11777" width="4.42578125" style="124" customWidth="1"/>
-    <col min="11778" max="11778" width="20.85546875" style="124" customWidth="1"/>
-    <col min="11779" max="11780" width="11.42578125" style="124"/>
-    <col min="11781" max="11782" width="4.140625" style="124" customWidth="1"/>
-    <col min="11783" max="11783" width="11.42578125" style="124"/>
-    <col min="11784" max="11784" width="19.140625" style="124" customWidth="1"/>
-    <col min="11785" max="11786" width="11.42578125" style="124"/>
-    <col min="11787" max="11788" width="4.85546875" style="124" customWidth="1"/>
-    <col min="11789" max="11789" width="10.85546875" style="124" customWidth="1"/>
-    <col min="11790" max="11790" width="11.42578125" style="124"/>
+    <col min="11777" max="11777" width="4.44140625" style="124" customWidth="1"/>
+    <col min="11778" max="11778" width="20.88671875" style="124" customWidth="1"/>
+    <col min="11779" max="11780" width="11.44140625" style="124"/>
+    <col min="11781" max="11782" width="4.109375" style="124" customWidth="1"/>
+    <col min="11783" max="11783" width="11.44140625" style="124"/>
+    <col min="11784" max="11784" width="19.109375" style="124" customWidth="1"/>
+    <col min="11785" max="11786" width="11.44140625" style="124"/>
+    <col min="11787" max="11788" width="4.88671875" style="124" customWidth="1"/>
+    <col min="11789" max="11789" width="10.88671875" style="124" customWidth="1"/>
+    <col min="11790" max="11790" width="11.44140625" style="124"/>
     <col min="11791" max="11791" width="22" style="124" customWidth="1"/>
-    <col min="11792" max="11793" width="11.42578125" style="124"/>
+    <col min="11792" max="11793" width="11.44140625" style="124"/>
     <col min="11794" max="11795" width="6" style="124" customWidth="1"/>
-    <col min="11796" max="12026" width="11.42578125" style="124"/>
+    <col min="11796" max="12026" width="11.44140625" style="124"/>
     <col min="12027" max="12028" width="20" style="124" customWidth="1"/>
-    <col min="12029" max="12029" width="11.42578125" style="124"/>
-    <col min="12030" max="12031" width="6.140625" style="124" customWidth="1"/>
+    <col min="12029" max="12029" width="11.44140625" style="124"/>
+    <col min="12030" max="12031" width="6.109375" style="124" customWidth="1"/>
     <col min="12032" max="12032" width="14" style="124" customWidth="1"/>
-    <col min="12033" max="12033" width="4.42578125" style="124" customWidth="1"/>
-    <col min="12034" max="12034" width="20.85546875" style="124" customWidth="1"/>
-    <col min="12035" max="12036" width="11.42578125" style="124"/>
-    <col min="12037" max="12038" width="4.140625" style="124" customWidth="1"/>
-    <col min="12039" max="12039" width="11.42578125" style="124"/>
-    <col min="12040" max="12040" width="19.140625" style="124" customWidth="1"/>
-    <col min="12041" max="12042" width="11.42578125" style="124"/>
-    <col min="12043" max="12044" width="4.85546875" style="124" customWidth="1"/>
-    <col min="12045" max="12045" width="10.85546875" style="124" customWidth="1"/>
-    <col min="12046" max="12046" width="11.42578125" style="124"/>
+    <col min="12033" max="12033" width="4.44140625" style="124" customWidth="1"/>
+    <col min="12034" max="12034" width="20.88671875" style="124" customWidth="1"/>
+    <col min="12035" max="12036" width="11.44140625" style="124"/>
+    <col min="12037" max="12038" width="4.109375" style="124" customWidth="1"/>
+    <col min="12039" max="12039" width="11.44140625" style="124"/>
+    <col min="12040" max="12040" width="19.109375" style="124" customWidth="1"/>
+    <col min="12041" max="12042" width="11.44140625" style="124"/>
+    <col min="12043" max="12044" width="4.88671875" style="124" customWidth="1"/>
+    <col min="12045" max="12045" width="10.88671875" style="124" customWidth="1"/>
+    <col min="12046" max="12046" width="11.44140625" style="124"/>
     <col min="12047" max="12047" width="22" style="124" customWidth="1"/>
-    <col min="12048" max="12049" width="11.42578125" style="124"/>
+    <col min="12048" max="12049" width="11.44140625" style="124"/>
     <col min="12050" max="12051" width="6" style="124" customWidth="1"/>
-    <col min="12052" max="12282" width="11.42578125" style="124"/>
+    <col min="12052" max="12282" width="11.44140625" style="124"/>
     <col min="12283" max="12284" width="20" style="124" customWidth="1"/>
-    <col min="12285" max="12285" width="11.42578125" style="124"/>
-    <col min="12286" max="12287" width="6.140625" style="124" customWidth="1"/>
+    <col min="12285" max="12285" width="11.44140625" style="124"/>
+    <col min="12286" max="12287" width="6.109375" style="124" customWidth="1"/>
     <col min="12288" max="12288" width="14" style="124" customWidth="1"/>
-    <col min="12289" max="12289" width="4.42578125" style="124" customWidth="1"/>
-    <col min="12290" max="12290" width="20.85546875" style="124" customWidth="1"/>
-    <col min="12291" max="12292" width="11.42578125" style="124"/>
-    <col min="12293" max="12294" width="4.140625" style="124" customWidth="1"/>
-    <col min="12295" max="12295" width="11.42578125" style="124"/>
-    <col min="12296" max="12296" width="19.140625" style="124" customWidth="1"/>
-    <col min="12297" max="12298" width="11.42578125" style="124"/>
-    <col min="12299" max="12300" width="4.85546875" style="124" customWidth="1"/>
-    <col min="12301" max="12301" width="10.85546875" style="124" customWidth="1"/>
-    <col min="12302" max="12302" width="11.42578125" style="124"/>
+    <col min="12289" max="12289" width="4.44140625" style="124" customWidth="1"/>
+    <col min="12290" max="12290" width="20.88671875" style="124" customWidth="1"/>
+    <col min="12291" max="12292" width="11.44140625" style="124"/>
+    <col min="12293" max="12294" width="4.109375" style="124" customWidth="1"/>
+    <col min="12295" max="12295" width="11.44140625" style="124"/>
+    <col min="12296" max="12296" width="19.109375" style="124" customWidth="1"/>
+    <col min="12297" max="12298" width="11.44140625" style="124"/>
+    <col min="12299" max="12300" width="4.88671875" style="124" customWidth="1"/>
+    <col min="12301" max="12301" width="10.88671875" style="124" customWidth="1"/>
+    <col min="12302" max="12302" width="11.44140625" style="124"/>
     <col min="12303" max="12303" width="22" style="124" customWidth="1"/>
-    <col min="12304" max="12305" width="11.42578125" style="124"/>
+    <col min="12304" max="12305" width="11.44140625" style="124"/>
     <col min="12306" max="12307" width="6" style="124" customWidth="1"/>
-    <col min="12308" max="12538" width="11.42578125" style="124"/>
+    <col min="12308" max="12538" width="11.44140625" style="124"/>
     <col min="12539" max="12540" width="20" style="124" customWidth="1"/>
-    <col min="12541" max="12541" width="11.42578125" style="124"/>
-    <col min="12542" max="12543" width="6.140625" style="124" customWidth="1"/>
+    <col min="12541" max="12541" width="11.44140625" style="124"/>
+    <col min="12542" max="12543" width="6.109375" style="124" customWidth="1"/>
     <col min="12544" max="12544" width="14" style="124" customWidth="1"/>
-    <col min="12545" max="12545" width="4.42578125" style="124" customWidth="1"/>
-    <col min="12546" max="12546" width="20.85546875" style="124" customWidth="1"/>
-    <col min="12547" max="12548" width="11.42578125" style="124"/>
-    <col min="12549" max="12550" width="4.140625" style="124" customWidth="1"/>
-    <col min="12551" max="12551" width="11.42578125" style="124"/>
-    <col min="12552" max="12552" width="19.140625" style="124" customWidth="1"/>
-    <col min="12553" max="12554" width="11.42578125" style="124"/>
-    <col min="12555" max="12556" width="4.85546875" style="124" customWidth="1"/>
-    <col min="12557" max="12557" width="10.85546875" style="124" customWidth="1"/>
-    <col min="12558" max="12558" width="11.42578125" style="124"/>
+    <col min="12545" max="12545" width="4.44140625" style="124" customWidth="1"/>
+    <col min="12546" max="12546" width="20.88671875" style="124" customWidth="1"/>
+    <col min="12547" max="12548" width="11.44140625" style="124"/>
+    <col min="12549" max="12550" width="4.109375" style="124" customWidth="1"/>
+    <col min="12551" max="12551" width="11.44140625" style="124"/>
+    <col min="12552" max="12552" width="19.109375" style="124" customWidth="1"/>
+    <col min="12553" max="12554" width="11.44140625" style="124"/>
+    <col min="12555" max="12556" width="4.88671875" style="124" customWidth="1"/>
+    <col min="12557" max="12557" width="10.88671875" style="124" customWidth="1"/>
+    <col min="12558" max="12558" width="11.44140625" style="124"/>
     <col min="12559" max="12559" width="22" style="124" customWidth="1"/>
-    <col min="12560" max="12561" width="11.42578125" style="124"/>
+    <col min="12560" max="12561" width="11.44140625" style="124"/>
     <col min="12562" max="12563" width="6" style="124" customWidth="1"/>
-    <col min="12564" max="12794" width="11.42578125" style="124"/>
+    <col min="12564" max="12794" width="11.44140625" style="124"/>
     <col min="12795" max="12796" width="20" style="124" customWidth="1"/>
-    <col min="12797" max="12797" width="11.42578125" style="124"/>
-    <col min="12798" max="12799" width="6.140625" style="124" customWidth="1"/>
+    <col min="12797" max="12797" width="11.44140625" style="124"/>
+    <col min="12798" max="12799" width="6.109375" style="124" customWidth="1"/>
     <col min="12800" max="12800" width="14" style="124" customWidth="1"/>
-    <col min="12801" max="12801" width="4.42578125" style="124" customWidth="1"/>
-    <col min="12802" max="12802" width="20.85546875" style="124" customWidth="1"/>
-    <col min="12803" max="12804" width="11.42578125" style="124"/>
-    <col min="12805" max="12806" width="4.140625" style="124" customWidth="1"/>
-    <col min="12807" max="12807" width="11.42578125" style="124"/>
-    <col min="12808" max="12808" width="19.140625" style="124" customWidth="1"/>
-    <col min="12809" max="12810" width="11.42578125" style="124"/>
-    <col min="12811" max="12812" width="4.85546875" style="124" customWidth="1"/>
-    <col min="12813" max="12813" width="10.85546875" style="124" customWidth="1"/>
-    <col min="12814" max="12814" width="11.42578125" style="124"/>
+    <col min="12801" max="12801" width="4.44140625" style="124" customWidth="1"/>
+    <col min="12802" max="12802" width="20.88671875" style="124" customWidth="1"/>
+    <col min="12803" max="12804" width="11.44140625" style="124"/>
+    <col min="12805" max="12806" width="4.109375" style="124" customWidth="1"/>
+    <col min="12807" max="12807" width="11.44140625" style="124"/>
+    <col min="12808" max="12808" width="19.109375" style="124" customWidth="1"/>
+    <col min="12809" max="12810" width="11.44140625" style="124"/>
+    <col min="12811" max="12812" width="4.88671875" style="124" customWidth="1"/>
+    <col min="12813" max="12813" width="10.88671875" style="124" customWidth="1"/>
+    <col min="12814" max="12814" width="11.44140625" style="124"/>
     <col min="12815" max="12815" width="22" style="124" customWidth="1"/>
-    <col min="12816" max="12817" width="11.42578125" style="124"/>
+    <col min="12816" max="12817" width="11.44140625" style="124"/>
     <col min="12818" max="12819" width="6" style="124" customWidth="1"/>
-    <col min="12820" max="13050" width="11.42578125" style="124"/>
+    <col min="12820" max="13050" width="11.44140625" style="124"/>
     <col min="13051" max="13052" width="20" style="124" customWidth="1"/>
-    <col min="13053" max="13053" width="11.42578125" style="124"/>
-    <col min="13054" max="13055" width="6.140625" style="124" customWidth="1"/>
+    <col min="13053" max="13053" width="11.44140625" style="124"/>
+    <col min="13054" max="13055" width="6.109375" style="124" customWidth="1"/>
     <col min="13056" max="13056" width="14" style="124" customWidth="1"/>
-    <col min="13057" max="13057" width="4.42578125" style="124" customWidth="1"/>
-    <col min="13058" max="13058" width="20.85546875" style="124" customWidth="1"/>
-    <col min="13059" max="13060" width="11.42578125" style="124"/>
-    <col min="13061" max="13062" width="4.140625" style="124" customWidth="1"/>
-    <col min="13063" max="13063" width="11.42578125" style="124"/>
-    <col min="13064" max="13064" width="19.140625" style="124" customWidth="1"/>
-    <col min="13065" max="13066" width="11.42578125" style="124"/>
-    <col min="13067" max="13068" width="4.85546875" style="124" customWidth="1"/>
-    <col min="13069" max="13069" width="10.85546875" style="124" customWidth="1"/>
-    <col min="13070" max="13070" width="11.42578125" style="124"/>
+    <col min="13057" max="13057" width="4.44140625" style="124" customWidth="1"/>
+    <col min="13058" max="13058" width="20.88671875" style="124" customWidth="1"/>
+    <col min="13059" max="13060" width="11.44140625" style="124"/>
+    <col min="13061" max="13062" width="4.109375" style="124" customWidth="1"/>
+    <col min="13063" max="13063" width="11.44140625" style="124"/>
+    <col min="13064" max="13064" width="19.109375" style="124" customWidth="1"/>
+    <col min="13065" max="13066" width="11.44140625" style="124"/>
+    <col min="13067" max="13068" width="4.88671875" style="124" customWidth="1"/>
+    <col min="13069" max="13069" width="10.88671875" style="124" customWidth="1"/>
+    <col min="13070" max="13070" width="11.44140625" style="124"/>
     <col min="13071" max="13071" width="22" style="124" customWidth="1"/>
-    <col min="13072" max="13073" width="11.42578125" style="124"/>
+    <col min="13072" max="13073" width="11.44140625" style="124"/>
     <col min="13074" max="13075" width="6" style="124" customWidth="1"/>
-    <col min="13076" max="13306" width="11.42578125" style="124"/>
+    <col min="13076" max="13306" width="11.44140625" style="124"/>
     <col min="13307" max="13308" width="20" style="124" customWidth="1"/>
-    <col min="13309" max="13309" width="11.42578125" style="124"/>
-    <col min="13310" max="13311" width="6.140625" style="124" customWidth="1"/>
+    <col min="13309" max="13309" width="11.44140625" style="124"/>
+    <col min="13310" max="13311" width="6.109375" style="124" customWidth="1"/>
     <col min="13312" max="13312" width="14" style="124" customWidth="1"/>
-    <col min="13313" max="13313" width="4.42578125" style="124" customWidth="1"/>
-    <col min="13314" max="13314" width="20.85546875" style="124" customWidth="1"/>
-    <col min="13315" max="13316" width="11.42578125" style="124"/>
-    <col min="13317" max="13318" width="4.140625" style="124" customWidth="1"/>
-    <col min="13319" max="13319" width="11.42578125" style="124"/>
-    <col min="13320" max="13320" width="19.140625" style="124" customWidth="1"/>
-    <col min="13321" max="13322" width="11.42578125" style="124"/>
-    <col min="13323" max="13324" width="4.85546875" style="124" customWidth="1"/>
-    <col min="13325" max="13325" width="10.85546875" style="124" customWidth="1"/>
-    <col min="13326" max="13326" width="11.42578125" style="124"/>
+    <col min="13313" max="13313" width="4.44140625" style="124" customWidth="1"/>
+    <col min="13314" max="13314" width="20.88671875" style="124" customWidth="1"/>
+    <col min="13315" max="13316" width="11.44140625" style="124"/>
+    <col min="13317" max="13318" width="4.109375" style="124" customWidth="1"/>
+    <col min="13319" max="13319" width="11.44140625" style="124"/>
+    <col min="13320" max="13320" width="19.109375" style="124" customWidth="1"/>
+    <col min="13321" max="13322" width="11.44140625" style="124"/>
+    <col min="13323" max="13324" width="4.88671875" style="124" customWidth="1"/>
+    <col min="13325" max="13325" width="10.88671875" style="124" customWidth="1"/>
+    <col min="13326" max="13326" width="11.44140625" style="124"/>
     <col min="13327" max="13327" width="22" style="124" customWidth="1"/>
-    <col min="13328" max="13329" width="11.42578125" style="124"/>
+    <col min="13328" max="13329" width="11.44140625" style="124"/>
     <col min="13330" max="13331" width="6" style="124" customWidth="1"/>
-    <col min="13332" max="13562" width="11.42578125" style="124"/>
+    <col min="13332" max="13562" width="11.44140625" style="124"/>
     <col min="13563" max="13564" width="20" style="124" customWidth="1"/>
-    <col min="13565" max="13565" width="11.42578125" style="124"/>
-    <col min="13566" max="13567" width="6.140625" style="124" customWidth="1"/>
+    <col min="13565" max="13565" width="11.44140625" style="124"/>
+    <col min="13566" max="13567" width="6.109375" style="124" customWidth="1"/>
     <col min="13568" max="13568" width="14" style="124" customWidth="1"/>
-    <col min="13569" max="13569" width="4.42578125" style="124" customWidth="1"/>
-    <col min="13570" max="13570" width="20.85546875" style="124" customWidth="1"/>
-    <col min="13571" max="13572" width="11.42578125" style="124"/>
-    <col min="13573" max="13574" width="4.140625" style="124" customWidth="1"/>
-    <col min="13575" max="13575" width="11.42578125" style="124"/>
-    <col min="13576" max="13576" width="19.140625" style="124" customWidth="1"/>
-    <col min="13577" max="13578" width="11.42578125" style="124"/>
-    <col min="13579" max="13580" width="4.85546875" style="124" customWidth="1"/>
-    <col min="13581" max="13581" width="10.85546875" style="124" customWidth="1"/>
-    <col min="13582" max="13582" width="11.42578125" style="124"/>
+    <col min="13569" max="13569" width="4.44140625" style="124" customWidth="1"/>
+    <col min="13570" max="13570" width="20.88671875" style="124" customWidth="1"/>
+    <col min="13571" max="13572" width="11.44140625" style="124"/>
+    <col min="13573" max="13574" width="4.109375" style="124" customWidth="1"/>
+    <col min="13575" max="13575" width="11.44140625" style="124"/>
+    <col min="13576" max="13576" width="19.109375" style="124" customWidth="1"/>
+    <col min="13577" max="13578" width="11.44140625" style="124"/>
+    <col min="13579" max="13580" width="4.88671875" style="124" customWidth="1"/>
+    <col min="13581" max="13581" width="10.88671875" style="124" customWidth="1"/>
+    <col min="13582" max="13582" width="11.44140625" style="124"/>
     <col min="13583" max="13583" width="22" style="124" customWidth="1"/>
-    <col min="13584" max="13585" width="11.42578125" style="124"/>
+    <col min="13584" max="13585" width="11.44140625" style="124"/>
     <col min="13586" max="13587" width="6" style="124" customWidth="1"/>
-    <col min="13588" max="13818" width="11.42578125" style="124"/>
+    <col min="13588" max="13818" width="11.44140625" style="124"/>
     <col min="13819" max="13820" width="20" style="124" customWidth="1"/>
-    <col min="13821" max="13821" width="11.42578125" style="124"/>
-    <col min="13822" max="13823" width="6.140625" style="124" customWidth="1"/>
+    <col min="13821" max="13821" width="11.44140625" style="124"/>
+    <col min="13822" max="13823" width="6.109375" style="124" customWidth="1"/>
     <col min="13824" max="13824" width="14" style="124" customWidth="1"/>
-    <col min="13825" max="13825" width="4.42578125" style="124" customWidth="1"/>
-    <col min="13826" max="13826" width="20.85546875" style="124" customWidth="1"/>
-    <col min="13827" max="13828" width="11.42578125" style="124"/>
-    <col min="13829" max="13830" width="4.140625" style="124" customWidth="1"/>
-    <col min="13831" max="13831" width="11.42578125" style="124"/>
-    <col min="13832" max="13832" width="19.140625" style="124" customWidth="1"/>
-    <col min="13833" max="13834" width="11.42578125" style="124"/>
-    <col min="13835" max="13836" width="4.85546875" style="124" customWidth="1"/>
-    <col min="13837" max="13837" width="10.85546875" style="124" customWidth="1"/>
-    <col min="13838" max="13838" width="11.42578125" style="124"/>
+    <col min="13825" max="13825" width="4.44140625" style="124" customWidth="1"/>
+    <col min="13826" max="13826" width="20.88671875" style="124" customWidth="1"/>
+    <col min="13827" max="13828" width="11.44140625" style="124"/>
+    <col min="13829" max="13830" width="4.109375" style="124" customWidth="1"/>
+    <col min="13831" max="13831" width="11.44140625" style="124"/>
+    <col min="13832" max="13832" width="19.109375" style="124" customWidth="1"/>
+    <col min="13833" max="13834" width="11.44140625" style="124"/>
+    <col min="13835" max="13836" width="4.88671875" style="124" customWidth="1"/>
+    <col min="13837" max="13837" width="10.88671875" style="124" customWidth="1"/>
+    <col min="13838" max="13838" width="11.44140625" style="124"/>
     <col min="13839" max="13839" width="22" style="124" customWidth="1"/>
-    <col min="13840" max="13841" width="11.42578125" style="124"/>
+    <col min="13840" max="13841" width="11.44140625" style="124"/>
     <col min="13842" max="13843" width="6" style="124" customWidth="1"/>
-    <col min="13844" max="14074" width="11.42578125" style="124"/>
+    <col min="13844" max="14074" width="11.44140625" style="124"/>
     <col min="14075" max="14076" width="20" style="124" customWidth="1"/>
-    <col min="14077" max="14077" width="11.42578125" style="124"/>
-    <col min="14078" max="14079" width="6.140625" style="124" customWidth="1"/>
+    <col min="14077" max="14077" width="11.44140625" style="124"/>
+    <col min="14078" max="14079" width="6.109375" style="124" customWidth="1"/>
     <col min="14080" max="14080" width="14" style="124" customWidth="1"/>
-    <col min="14081" max="14081" width="4.42578125" style="124" customWidth="1"/>
-    <col min="14082" max="14082" width="20.85546875" style="124" customWidth="1"/>
-    <col min="14083" max="14084" width="11.42578125" style="124"/>
-    <col min="14085" max="14086" width="4.140625" style="124" customWidth="1"/>
-    <col min="14087" max="14087" width="11.42578125" style="124"/>
-    <col min="14088" max="14088" width="19.140625" style="124" customWidth="1"/>
-    <col min="14089" max="14090" width="11.42578125" style="124"/>
-    <col min="14091" max="14092" width="4.85546875" style="124" customWidth="1"/>
-    <col min="14093" max="14093" width="10.85546875" style="124" customWidth="1"/>
-    <col min="14094" max="14094" width="11.42578125" style="124"/>
+    <col min="14081" max="14081" width="4.44140625" style="124" customWidth="1"/>
+    <col min="14082" max="14082" width="20.88671875" style="124" customWidth="1"/>
+    <col min="14083" max="14084" width="11.44140625" style="124"/>
+    <col min="14085" max="14086" width="4.109375" style="124" customWidth="1"/>
+    <col min="14087" max="14087" width="11.44140625" style="124"/>
+    <col min="14088" max="14088" width="19.109375" style="124" customWidth="1"/>
+    <col min="14089" max="14090" width="11.44140625" style="124"/>
+    <col min="14091" max="14092" width="4.88671875" style="124" customWidth="1"/>
+    <col min="14093" max="14093" width="10.88671875" style="124" customWidth="1"/>
+    <col min="14094" max="14094" width="11.44140625" style="124"/>
     <col min="14095" max="14095" width="22" style="124" customWidth="1"/>
-    <col min="14096" max="14097" width="11.42578125" style="124"/>
+    <col min="14096" max="14097" width="11.44140625" style="124"/>
     <col min="14098" max="14099" width="6" style="124" customWidth="1"/>
-    <col min="14100" max="14330" width="11.42578125" style="124"/>
+    <col min="14100" max="14330" width="11.44140625" style="124"/>
     <col min="14331" max="14332" width="20" style="124" customWidth="1"/>
-    <col min="14333" max="14333" width="11.42578125" style="124"/>
-    <col min="14334" max="14335" width="6.140625" style="124" customWidth="1"/>
+    <col min="14333" max="14333" width="11.44140625" style="124"/>
+    <col min="14334" max="14335" width="6.109375" style="124" customWidth="1"/>
     <col min="14336" max="14336" width="14" style="124" customWidth="1"/>
-    <col min="14337" max="14337" width="4.42578125" style="124" customWidth="1"/>
-    <col min="14338" max="14338" width="20.85546875" style="124" customWidth="1"/>
-    <col min="14339" max="14340" width="11.42578125" style="124"/>
-    <col min="14341" max="14342" width="4.140625" style="124" customWidth="1"/>
-    <col min="14343" max="14343" width="11.42578125" style="124"/>
-    <col min="14344" max="14344" width="19.140625" style="124" customWidth="1"/>
-    <col min="14345" max="14346" width="11.42578125" style="124"/>
-    <col min="14347" max="14348" width="4.85546875" style="124" customWidth="1"/>
-    <col min="14349" max="14349" width="10.85546875" style="124" customWidth="1"/>
-    <col min="14350" max="14350" width="11.42578125" style="124"/>
+    <col min="14337" max="14337" width="4.44140625" style="124" customWidth="1"/>
+    <col min="14338" max="14338" width="20.88671875" style="124" customWidth="1"/>
+    <col min="14339" max="14340" width="11.44140625" style="124"/>
+    <col min="14341" max="14342" width="4.109375" style="124" customWidth="1"/>
+    <col min="14343" max="14343" width="11.44140625" style="124"/>
+    <col min="14344" max="14344" width="19.109375" style="124" customWidth="1"/>
+    <col min="14345" max="14346" width="11.44140625" style="124"/>
+    <col min="14347" max="14348" width="4.88671875" style="124" customWidth="1"/>
+    <col min="14349" max="14349" width="10.88671875" style="124" customWidth="1"/>
+    <col min="14350" max="14350" width="11.44140625" style="124"/>
     <col min="14351" max="14351" width="22" style="124" customWidth="1"/>
-    <col min="14352" max="14353" width="11.42578125" style="124"/>
+    <col min="14352" max="14353" width="11.44140625" style="124"/>
     <col min="14354" max="14355" width="6" style="124" customWidth="1"/>
-    <col min="14356" max="14586" width="11.42578125" style="124"/>
+    <col min="14356" max="14586" width="11.44140625" style="124"/>
     <col min="14587" max="14588" width="20" style="124" customWidth="1"/>
-    <col min="14589" max="14589" width="11.42578125" style="124"/>
-    <col min="14590" max="14591" width="6.140625" style="124" customWidth="1"/>
+    <col min="14589" max="14589" width="11.44140625" style="124"/>
+    <col min="14590" max="14591" width="6.109375" style="124" customWidth="1"/>
     <col min="14592" max="14592" width="14" style="124" customWidth="1"/>
-    <col min="14593" max="14593" width="4.42578125" style="124" customWidth="1"/>
-    <col min="14594" max="14594" width="20.85546875" style="124" customWidth="1"/>
-    <col min="14595" max="14596" width="11.42578125" style="124"/>
-    <col min="14597" max="14598" width="4.140625" style="124" customWidth="1"/>
-    <col min="14599" max="14599" width="11.42578125" style="124"/>
-    <col min="14600" max="14600" width="19.140625" style="124" customWidth="1"/>
-    <col min="14601" max="14602" width="11.42578125" style="124"/>
-    <col min="14603" max="14604" width="4.85546875" style="124" customWidth="1"/>
-    <col min="14605" max="14605" width="10.85546875" style="124" customWidth="1"/>
-    <col min="14606" max="14606" width="11.42578125" style="124"/>
+    <col min="14593" max="14593" width="4.44140625" style="124" customWidth="1"/>
+    <col min="14594" max="14594" width="20.88671875" style="124" customWidth="1"/>
+    <col min="14595" max="14596" width="11.44140625" style="124"/>
+    <col min="14597" max="14598" width="4.109375" style="124" customWidth="1"/>
+    <col min="14599" max="14599" width="11.44140625" style="124"/>
+    <col min="14600" max="14600" width="19.109375" style="124" customWidth="1"/>
+    <col min="14601" max="14602" width="11.44140625" style="124"/>
+    <col min="14603" max="14604" width="4.88671875" style="124" customWidth="1"/>
+    <col min="14605" max="14605" width="10.88671875" style="124" customWidth="1"/>
+    <col min="14606" max="14606" width="11.44140625" style="124"/>
     <col min="14607" max="14607" width="22" style="124" customWidth="1"/>
-    <col min="14608" max="14609" width="11.42578125" style="124"/>
+    <col min="14608" max="14609" width="11.44140625" style="124"/>
     <col min="14610" max="14611" width="6" style="124" customWidth="1"/>
-    <col min="14612" max="14842" width="11.42578125" style="124"/>
+    <col min="14612" max="14842" width="11.44140625" style="124"/>
     <col min="14843" max="14844" width="20" style="124" customWidth="1"/>
-    <col min="14845" max="14845" width="11.42578125" style="124"/>
-    <col min="14846" max="14847" width="6.140625" style="124" customWidth="1"/>
+    <col min="14845" max="14845" width="11.44140625" style="124"/>
+    <col min="14846" max="14847" width="6.109375" style="124" customWidth="1"/>
     <col min="14848" max="14848" width="14" style="124" customWidth="1"/>
-    <col min="14849" max="14849" width="4.42578125" style="124" customWidth="1"/>
-    <col min="14850" max="14850" width="20.85546875" style="124" customWidth="1"/>
-    <col min="14851" max="14852" width="11.42578125" style="124"/>
-    <col min="14853" max="14854" width="4.140625" style="124" customWidth="1"/>
-    <col min="14855" max="14855" width="11.42578125" style="124"/>
-    <col min="14856" max="14856" width="19.140625" style="124" customWidth="1"/>
-    <col min="14857" max="14858" width="11.42578125" style="124"/>
-    <col min="14859" max="14860" width="4.85546875" style="124" customWidth="1"/>
-    <col min="14861" max="14861" width="10.85546875" style="124" customWidth="1"/>
-    <col min="14862" max="14862" width="11.42578125" style="124"/>
+    <col min="14849" max="14849" width="4.44140625" style="124" customWidth="1"/>
+    <col min="14850" max="14850" width="20.88671875" style="124" customWidth="1"/>
+    <col min="14851" max="14852" width="11.44140625" style="124"/>
+    <col min="14853" max="14854" width="4.109375" style="124" customWidth="1"/>
+    <col min="14855" max="14855" width="11.44140625" style="124"/>
+    <col min="14856" max="14856" width="19.109375" style="124" customWidth="1"/>
+    <col min="14857" max="14858" width="11.44140625" style="124"/>
+    <col min="14859" max="14860" width="4.88671875" style="124" customWidth="1"/>
+    <col min="14861" max="14861" width="10.88671875" style="124" customWidth="1"/>
+    <col min="14862" max="14862" width="11.44140625" style="124"/>
     <col min="14863" max="14863" width="22" style="124" customWidth="1"/>
-    <col min="14864" max="14865" width="11.42578125" style="124"/>
+    <col min="14864" max="14865" width="11.44140625" style="124"/>
     <col min="14866" max="14867" width="6" style="124" customWidth="1"/>
-    <col min="14868" max="15098" width="11.42578125" style="124"/>
+    <col min="14868" max="15098" width="11.44140625" style="124"/>
     <col min="15099" max="15100" width="20" style="124" customWidth="1"/>
-    <col min="15101" max="15101" width="11.42578125" style="124"/>
-    <col min="15102" max="15103" width="6.140625" style="124" customWidth="1"/>
+    <col min="15101" max="15101" width="11.44140625" style="124"/>
+    <col min="15102" max="15103" width="6.109375" style="124" customWidth="1"/>
     <col min="15104" max="15104" width="14" style="124" customWidth="1"/>
-    <col min="15105" max="15105" width="4.42578125" style="124" customWidth="1"/>
-    <col min="15106" max="15106" width="20.85546875" style="124" customWidth="1"/>
-    <col min="15107" max="15108" width="11.42578125" style="124"/>
-    <col min="15109" max="15110" width="4.140625" style="124" customWidth="1"/>
-    <col min="15111" max="15111" width="11.42578125" style="124"/>
-    <col min="15112" max="15112" width="19.140625" style="124" customWidth="1"/>
-    <col min="15113" max="15114" width="11.42578125" style="124"/>
-    <col min="15115" max="15116" width="4.85546875" style="124" customWidth="1"/>
-    <col min="15117" max="15117" width="10.85546875" style="124" customWidth="1"/>
-    <col min="15118" max="15118" width="11.42578125" style="124"/>
+    <col min="15105" max="15105" width="4.44140625" style="124" customWidth="1"/>
+    <col min="15106" max="15106" width="20.88671875" style="124" customWidth="1"/>
+    <col min="15107" max="15108" width="11.44140625" style="124"/>
+    <col min="15109" max="15110" width="4.109375" style="124" customWidth="1"/>
+    <col min="15111" max="15111" width="11.44140625" style="124"/>
+    <col min="15112" max="15112" width="19.109375" style="124" customWidth="1"/>
+    <col min="15113" max="15114" width="11.44140625" style="124"/>
+    <col min="15115" max="15116" width="4.88671875" style="124" customWidth="1"/>
+    <col min="15117" max="15117" width="10.88671875" style="124" customWidth="1"/>
+    <col min="15118" max="15118" width="11.44140625" style="124"/>
     <col min="15119" max="15119" width="22" style="124" customWidth="1"/>
-    <col min="15120" max="15121" width="11.42578125" style="124"/>
+    <col min="15120" max="15121" width="11.44140625" style="124"/>
     <col min="15122" max="15123" width="6" style="124" customWidth="1"/>
-    <col min="15124" max="15354" width="11.42578125" style="124"/>
+    <col min="15124" max="15354" width="11.44140625" style="124"/>
     <col min="15355" max="15356" width="20" style="124" customWidth="1"/>
-    <col min="15357" max="15357" width="11.42578125" style="124"/>
-    <col min="15358" max="15359" width="6.140625" style="124" customWidth="1"/>
+    <col min="15357" max="15357" width="11.44140625" style="124"/>
+    <col min="15358" max="15359" width="6.109375" style="124" customWidth="1"/>
     <col min="15360" max="15360" width="14" style="124" customWidth="1"/>
-    <col min="15361" max="15361" width="4.42578125" style="124" customWidth="1"/>
-    <col min="15362" max="15362" width="20.85546875" style="124" customWidth="1"/>
-    <col min="15363" max="15364" width="11.42578125" style="124"/>
-    <col min="15365" max="15366" width="4.140625" style="124" customWidth="1"/>
-    <col min="15367" max="15367" width="11.42578125" style="124"/>
-    <col min="15368" max="15368" width="19.140625" style="124" customWidth="1"/>
-    <col min="15369" max="15370" width="11.42578125" style="124"/>
-    <col min="15371" max="15372" width="4.85546875" style="124" customWidth="1"/>
-    <col min="15373" max="15373" width="10.85546875" style="124" customWidth="1"/>
-    <col min="15374" max="15374" width="11.42578125" style="124"/>
+    <col min="15361" max="15361" width="4.44140625" style="124" customWidth="1"/>
+    <col min="15362" max="15362" width="20.88671875" style="124" customWidth="1"/>
+    <col min="15363" max="15364" width="11.44140625" style="124"/>
+    <col min="15365" max="15366" width="4.109375" style="124" customWidth="1"/>
+    <col min="15367" max="15367" width="11.44140625" style="124"/>
+    <col min="15368" max="15368" width="19.109375" style="124" customWidth="1"/>
+    <col min="15369" max="15370" width="11.44140625" style="124"/>
+    <col min="15371" max="15372" width="4.88671875" style="124" customWidth="1"/>
+    <col min="15373" max="15373" width="10.88671875" style="124" customWidth="1"/>
+    <col min="15374" max="15374" width="11.44140625" style="124"/>
     <col min="15375" max="15375" width="22" style="124" customWidth="1"/>
-    <col min="15376" max="15377" width="11.42578125" style="124"/>
+    <col min="15376" max="15377" width="11.44140625" style="124"/>
     <col min="15378" max="15379" width="6" style="124" customWidth="1"/>
-    <col min="15380" max="15610" width="11.42578125" style="124"/>
+    <col min="15380" max="15610" width="11.44140625" style="124"/>
     <col min="15611" max="15612" width="20" style="124" customWidth="1"/>
-    <col min="15613" max="15613" width="11.42578125" style="124"/>
-    <col min="15614" max="15615" width="6.140625" style="124" customWidth="1"/>
+    <col min="15613" max="15613" width="11.44140625" style="124"/>
+    <col min="15614" max="15615" width="6.109375" style="124" customWidth="1"/>
     <col min="15616" max="15616" width="14" style="124" customWidth="1"/>
-    <col min="15617" max="15617" width="4.42578125" style="124" customWidth="1"/>
-    <col min="15618" max="15618" width="20.85546875" style="124" customWidth="1"/>
-    <col min="15619" max="15620" width="11.42578125" style="124"/>
-    <col min="15621" max="15622" width="4.140625" style="124" customWidth="1"/>
-    <col min="15623" max="15623" width="11.42578125" style="124"/>
-    <col min="15624" max="15624" width="19.140625" style="124" customWidth="1"/>
-    <col min="15625" max="15626" width="11.42578125" style="124"/>
-    <col min="15627" max="15628" width="4.85546875" style="124" customWidth="1"/>
-    <col min="15629" max="15629" width="10.85546875" style="124" customWidth="1"/>
-    <col min="15630" max="15630" width="11.42578125" style="124"/>
+    <col min="15617" max="15617" width="4.44140625" style="124" customWidth="1"/>
+    <col min="15618" max="15618" width="20.88671875" style="124" customWidth="1"/>
+    <col min="15619" max="15620" width="11.44140625" style="124"/>
+    <col min="15621" max="15622" width="4.109375" style="124" customWidth="1"/>
+    <col min="15623" max="15623" width="11.44140625" style="124"/>
+    <col min="15624" max="15624" width="19.109375" style="124" customWidth="1"/>
+    <col min="15625" max="15626" width="11.44140625" style="124"/>
+    <col min="15627" max="15628" width="4.88671875" style="124" customWidth="1"/>
+    <col min="15629" max="15629" width="10.88671875" style="124" customWidth="1"/>
+    <col min="15630" max="15630" width="11.44140625" style="124"/>
     <col min="15631" max="15631" width="22" style="124" customWidth="1"/>
-    <col min="15632" max="15633" width="11.42578125" style="124"/>
+    <col min="15632" max="15633" width="11.44140625" style="124"/>
     <col min="15634" max="15635" width="6" style="124" customWidth="1"/>
-    <col min="15636" max="15866" width="11.42578125" style="124"/>
+    <col min="15636" max="15866" width="11.44140625" style="124"/>
     <col min="15867" max="15868" width="20" style="124" customWidth="1"/>
-    <col min="15869" max="15869" width="11.42578125" style="124"/>
-    <col min="15870" max="15871" width="6.140625" style="124" customWidth="1"/>
+    <col min="15869" max="15869" width="11.44140625" style="124"/>
+    <col min="15870" max="15871" width="6.109375" style="124" customWidth="1"/>
     <col min="15872" max="15872" width="14" style="124" customWidth="1"/>
-    <col min="15873" max="15873" width="4.42578125" style="124" customWidth="1"/>
-    <col min="15874" max="15874" width="20.85546875" style="124" customWidth="1"/>
-    <col min="15875" max="15876" width="11.42578125" style="124"/>
-    <col min="15877" max="15878" width="4.140625" style="124" customWidth="1"/>
-    <col min="15879" max="15879" width="11.42578125" style="124"/>
-    <col min="15880" max="15880" width="19.140625" style="124" customWidth="1"/>
-    <col min="15881" max="15882" width="11.42578125" style="124"/>
-    <col min="15883" max="15884" width="4.85546875" style="124" customWidth="1"/>
-    <col min="15885" max="15885" width="10.85546875" style="124" customWidth="1"/>
-    <col min="15886" max="15886" width="11.42578125" style="124"/>
+    <col min="15873" max="15873" width="4.44140625" style="124" customWidth="1"/>
+    <col min="15874" max="15874" width="20.88671875" style="124" customWidth="1"/>
+    <col min="15875" max="15876" width="11.44140625" style="124"/>
+    <col min="15877" max="15878" width="4.109375" style="124" customWidth="1"/>
+    <col min="15879" max="15879" width="11.44140625" style="124"/>
+    <col min="15880" max="15880" width="19.109375" style="124" customWidth="1"/>
+    <col min="15881" max="15882" width="11.44140625" style="124"/>
+    <col min="15883" max="15884" width="4.88671875" style="124" customWidth="1"/>
+    <col min="15885" max="15885" width="10.88671875" style="124" customWidth="1"/>
+    <col min="15886" max="15886" width="11.44140625" style="124"/>
     <col min="15887" max="15887" width="22" style="124" customWidth="1"/>
-    <col min="15888" max="15889" width="11.42578125" style="124"/>
+    <col min="15888" max="15889" width="11.44140625" style="124"/>
     <col min="15890" max="15891" width="6" style="124" customWidth="1"/>
-    <col min="15892" max="16122" width="11.42578125" style="124"/>
+    <col min="15892" max="16122" width="11.44140625" style="124"/>
     <col min="16123" max="16124" width="20" style="124" customWidth="1"/>
-    <col min="16125" max="16125" width="11.42578125" style="124"/>
-    <col min="16126" max="16127" width="6.140625" style="124" customWidth="1"/>
+    <col min="16125" max="16125" width="11.44140625" style="124"/>
+    <col min="16126" max="16127" width="6.109375" style="124" customWidth="1"/>
     <col min="16128" max="16128" width="14" style="124" customWidth="1"/>
-    <col min="16129" max="16129" width="4.42578125" style="124" customWidth="1"/>
-    <col min="16130" max="16130" width="20.85546875" style="124" customWidth="1"/>
-    <col min="16131" max="16132" width="11.42578125" style="124"/>
-    <col min="16133" max="16134" width="4.140625" style="124" customWidth="1"/>
-    <col min="16135" max="16135" width="11.42578125" style="124"/>
-    <col min="16136" max="16136" width="19.140625" style="124" customWidth="1"/>
-    <col min="16137" max="16138" width="11.42578125" style="124"/>
-    <col min="16139" max="16140" width="4.85546875" style="124" customWidth="1"/>
-    <col min="16141" max="16141" width="10.85546875" style="124" customWidth="1"/>
-    <col min="16142" max="16142" width="11.42578125" style="124"/>
+    <col min="16129" max="16129" width="4.44140625" style="124" customWidth="1"/>
+    <col min="16130" max="16130" width="20.88671875" style="124" customWidth="1"/>
+    <col min="16131" max="16132" width="11.44140625" style="124"/>
+    <col min="16133" max="16134" width="4.109375" style="124" customWidth="1"/>
+    <col min="16135" max="16135" width="11.44140625" style="124"/>
+    <col min="16136" max="16136" width="19.109375" style="124" customWidth="1"/>
+    <col min="16137" max="16138" width="11.44140625" style="124"/>
+    <col min="16139" max="16140" width="4.88671875" style="124" customWidth="1"/>
+    <col min="16141" max="16141" width="10.88671875" style="124" customWidth="1"/>
+    <col min="16142" max="16142" width="11.44140625" style="124"/>
     <col min="16143" max="16143" width="22" style="124" customWidth="1"/>
-    <col min="16144" max="16145" width="11.42578125" style="124"/>
+    <col min="16144" max="16145" width="11.44140625" style="124"/>
     <col min="16146" max="16147" width="6" style="124" customWidth="1"/>
-    <col min="16148" max="16384" width="11.42578125" style="124"/>
+    <col min="16148" max="16384" width="11.44140625" style="124"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:25" ht="4.5" customHeight="1" x14ac:dyDescent="0.2"/>
